--- a/04_Figures/F06_prediction/modules/T2/enet/c_data/results.xlsx
+++ b/04_Figures/F06_prediction/modules/T2/enet/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -152,6 +152,9 @@
     <t xml:space="preserve">ME_blue</t>
   </si>
   <si>
+    <t xml:space="preserve">ME_brown</t>
+  </si>
+  <si>
     <t xml:space="preserve">ME_green</t>
   </si>
   <si>
@@ -164,22 +167,16 @@
     <t xml:space="preserve">ME_pink</t>
   </si>
   <si>
+    <t xml:space="preserve">ME_purple</t>
+  </si>
+  <si>
     <t xml:space="preserve">ME_red</t>
   </si>
   <si>
-    <t xml:space="preserve">ME_salmon</t>
+    <t xml:space="preserve">ME_turquoise</t>
   </si>
   <si>
-    <t xml:space="preserve">ME_tan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_purple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_turquoise</t>
+    <t xml:space="preserve">ME_yellow</t>
   </si>
 </sst>
 </file>
@@ -566,7 +563,7 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -599,7 +596,7 @@
         <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G3" t="n">
         <v>200</v>
@@ -611,16 +608,16 @@
         <v>-1</v>
       </c>
       <c r="J3" t="n">
-        <v>0.427860696517413</v>
+        <v>0.398009950248756</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.411754126170993</v>
+        <v>-0.908714315224501</v>
       </c>
       <c r="M3" t="n">
-        <v>0.853141372372279</v>
+        <v>2.71601510695074</v>
       </c>
     </row>
     <row r="4">
@@ -640,16 +637,16 @@
         <v>15</v>
       </c>
       <c r="F4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.819825065551163</v>
+        <v>-0.147959183673469</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.996428571428571</v>
+        <v>-1</v>
       </c>
       <c r="J4"/>
       <c r="K4"/>
@@ -673,28 +670,28 @@
         <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G5" t="n">
         <v>200</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.819825065551163</v>
+        <v>-0.147959183673469</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.996428571428571</v>
+        <v>-1</v>
       </c>
       <c r="J5" t="n">
-        <v>0.890547263681592</v>
+        <v>0.194029850746269</v>
       </c>
       <c r="K5" t="n">
-        <v>0.572139303482587</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.435555975858826</v>
+        <v>-0.889746018795049</v>
       </c>
       <c r="M5" t="n">
-        <v>0.749621015707864</v>
+        <v>2.91216668205906</v>
       </c>
     </row>
     <row r="6">
@@ -714,16 +711,16 @@
         <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.801991435424045</v>
+        <v>-3.53755494733586</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.996428571428571</v>
+        <v>-1</v>
       </c>
       <c r="J6"/>
       <c r="K6"/>
@@ -747,28 +744,28 @@
         <v>15</v>
       </c>
       <c r="F7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G7" t="n">
         <v>200</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.801991435424045</v>
+        <v>-3.53755494733586</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.996428571428571</v>
+        <v>-1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.940298507462687</v>
+        <v>0.950248756218905</v>
       </c>
       <c r="K7" t="n">
-        <v>0.45273631840796</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.315769295203494</v>
+        <v>-0.897792869512081</v>
       </c>
       <c r="M7" t="n">
-        <v>0.646488076302387</v>
+        <v>3.19412696904101</v>
       </c>
     </row>
     <row r="8">
@@ -788,16 +785,16 @@
         <v>15</v>
       </c>
       <c r="F8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.316178906233496</v>
+        <v>0.2160515511346</v>
       </c>
       <c r="I8" t="n">
-        <v>0.603571428571428</v>
+        <v>0.296428571428571</v>
       </c>
       <c r="J8"/>
       <c r="K8"/>
@@ -821,28 +818,28 @@
         <v>15</v>
       </c>
       <c r="F9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G9" t="n">
         <v>200</v>
       </c>
       <c r="H9" t="n">
-        <v>0.316178906233496</v>
+        <v>0.2160515511346</v>
       </c>
       <c r="I9" t="n">
-        <v>0.603571428571428</v>
+        <v>0.296428571428571</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0149253731343284</v>
+        <v>0.0199004975124378</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0099502487562189</v>
+        <v>0.0348258706467662</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.398362561335027</v>
+        <v>-0.976827376630532</v>
       </c>
       <c r="M9" t="n">
-        <v>0.634275002961039</v>
+        <v>2.9426978925868</v>
       </c>
     </row>
     <row r="10">
@@ -862,16 +859,16 @@
         <v>15</v>
       </c>
       <c r="F10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.159519421822142</v>
+        <v>-0.175939216680344</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.988350744592826</v>
+        <v>-0.954269684434453</v>
       </c>
       <c r="J10"/>
       <c r="K10"/>
@@ -895,28 +892,28 @@
         <v>15</v>
       </c>
       <c r="F11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G11" t="n">
         <v>200</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.159519421822142</v>
+        <v>-0.175939216680344</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.988350744592826</v>
+        <v>-0.954269684434453</v>
       </c>
       <c r="J11" t="n">
-        <v>0.472636815920398</v>
+        <v>0.517412935323383</v>
       </c>
       <c r="K11" t="n">
-        <v>0.492537313432836</v>
+        <v>0.402985074626866</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.388512794067432</v>
+        <v>-0.785958649888084</v>
       </c>
       <c r="M11" t="n">
-        <v>0.594285508334936</v>
+        <v>2.98118743031352</v>
       </c>
     </row>
     <row r="12">
@@ -936,13 +933,13 @@
         <v>14</v>
       </c>
       <c r="F12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.271720970174606</v>
       </c>
       <c r="I12" t="n">
         <v>-1</v>
@@ -969,28 +966,28 @@
         <v>14</v>
       </c>
       <c r="F13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G13" t="n">
         <v>200</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.271720970174606</v>
       </c>
       <c r="I13" t="n">
         <v>-1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.36318407960199</v>
+        <v>0.537313432835821</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.373278338720352</v>
+        <v>-1.17284176601161</v>
       </c>
       <c r="M13" t="n">
-        <v>0.944494759195755</v>
+        <v>3.93927273817812</v>
       </c>
     </row>
   </sheetData>
@@ -1023,7 +1020,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.894506840685408</v>
+        <v>-1.3283032347755</v>
       </c>
     </row>
     <row r="3">
@@ -1034,7 +1031,7 @@
         <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.178336567240714</v>
+        <v>-0.303448244974903</v>
       </c>
     </row>
     <row r="4">
@@ -1045,7 +1042,7 @@
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.704011857888367</v>
       </c>
     </row>
     <row r="5">
@@ -1067,7 +1064,7 @@
         <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.200022129912849</v>
+        <v>-0.27823538805895</v>
       </c>
     </row>
     <row r="7">
@@ -1078,7 +1075,7 @@
         <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.5995731015589</v>
+        <v>-0.451327569538656</v>
       </c>
     </row>
     <row r="8">
@@ -1089,7 +1086,7 @@
         <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.224892831471898</v>
+        <v>-0.228063527505602</v>
       </c>
     </row>
     <row r="9">
@@ -1100,7 +1097,7 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.39991518431791</v>
+        <v>-0.424417732103275</v>
       </c>
     </row>
     <row r="10">
@@ -1122,7 +1119,7 @@
         <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.154128081217757</v>
+        <v>-0.166721839879574</v>
       </c>
     </row>
     <row r="12">
@@ -1133,7 +1130,7 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.534495483480706</v>
       </c>
     </row>
     <row r="13">
@@ -1144,7 +1141,7 @@
         <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.186661008852699</v>
+        <v>-0.302195138391744</v>
       </c>
     </row>
     <row r="14">
@@ -1155,7 +1152,7 @@
         <v>16</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.225193833776005</v>
+        <v>-0.556153771640865</v>
       </c>
     </row>
     <row r="15">
@@ -1188,7 +1185,7 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.123056010603013</v>
+        <v>-0.151465486235555</v>
       </c>
     </row>
     <row r="18">
@@ -1199,7 +1196,7 @@
         <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.401698773203403</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="19">
@@ -1210,7 +1207,7 @@
         <v>16</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.225320562561</v>
+        <v>-0.285661709826862</v>
       </c>
     </row>
     <row r="20">
@@ -1221,7 +1218,7 @@
         <v>16</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.351318320615412</v>
+        <v>-1.65008129164425</v>
       </c>
     </row>
     <row r="21">
@@ -1232,7 +1229,7 @@
         <v>16</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.416368866952093</v>
       </c>
     </row>
     <row r="22">
@@ -1243,7 +1240,7 @@
         <v>16</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.465188677733161</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="23">
@@ -1254,7 +1251,7 @@
         <v>16</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.891967965468228</v>
+        <v>-1.38251623168052</v>
       </c>
     </row>
     <row r="24">
@@ -1265,7 +1262,7 @@
         <v>16</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.320285325166144</v>
+        <v>-5.58230914477314</v>
       </c>
     </row>
     <row r="25">
@@ -1287,7 +1284,7 @@
         <v>16</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.416877878236783</v>
+        <v>0.290018419897722</v>
       </c>
     </row>
     <row r="27">
@@ -1309,7 +1306,7 @@
         <v>16</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.221360913886838</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="29">
@@ -1320,7 +1317,7 @@
         <v>16</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.186517072932154</v>
+        <v>-0.177081516691474</v>
       </c>
     </row>
     <row r="30">
@@ -1331,7 +1328,7 @@
         <v>16</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.207414183369771</v>
       </c>
     </row>
     <row r="31">
@@ -1342,7 +1339,7 @@
         <v>16</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.274177703699383</v>
+        <v>-0.253705259565372</v>
       </c>
     </row>
     <row r="32">
@@ -1375,7 +1372,7 @@
         <v>16</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.401148285617277</v>
+        <v>-0.217783652191682</v>
       </c>
     </row>
     <row r="35">
@@ -1386,7 +1383,7 @@
         <v>16</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.484657660994181</v>
+        <v>-0.32168956570162</v>
       </c>
     </row>
     <row r="36">
@@ -1397,7 +1394,7 @@
         <v>16</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.142130176975067</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="37">
@@ -1452,7 +1449,7 @@
         <v>16</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.230277859415957</v>
+        <v>-0.352138618552977</v>
       </c>
     </row>
     <row r="42">
@@ -1496,7 +1493,7 @@
         <v>16</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.186613256127362</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="46">
@@ -1507,7 +1504,7 @@
         <v>16</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.249888069393656</v>
       </c>
     </row>
     <row r="47">
@@ -1518,7 +1515,7 @@
         <v>16</v>
       </c>
       <c r="C47" t="n">
-        <v>-2.05136809265276</v>
+        <v>-1.31785883858603</v>
       </c>
     </row>
     <row r="48">
@@ -1529,7 +1526,7 @@
         <v>16</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.453857961480561</v>
+        <v>-0.272920155045676</v>
       </c>
     </row>
     <row r="49">
@@ -1540,7 +1537,7 @@
         <v>16</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.478317117455183</v>
+        <v>-0.309984457939685</v>
       </c>
     </row>
     <row r="50">
@@ -1551,7 +1548,7 @@
         <v>16</v>
       </c>
       <c r="C50" t="n">
-        <v>-2.77267195979072</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="51">
@@ -1562,7 +1559,7 @@
         <v>16</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.194057684620827</v>
+        <v>-0.200335663787997</v>
       </c>
     </row>
     <row r="52">
@@ -1573,7 +1570,7 @@
         <v>16</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.282546023372405</v>
       </c>
     </row>
     <row r="53">
@@ -1584,7 +1581,7 @@
         <v>16</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.766215773620706</v>
+        <v>-0.664000790812217</v>
       </c>
     </row>
     <row r="54">
@@ -1595,7 +1592,7 @@
         <v>16</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.36474993179482</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="55">
@@ -1606,7 +1603,7 @@
         <v>16</v>
       </c>
       <c r="C55" t="n">
-        <v>-1.41164418056351</v>
+        <v>-2.08136816327334</v>
       </c>
     </row>
     <row r="56">
@@ -1617,7 +1614,7 @@
         <v>16</v>
       </c>
       <c r="C56" t="n">
-        <v>-1.19510211605519</v>
+        <v>-4.10256541749322</v>
       </c>
     </row>
     <row r="57">
@@ -1628,7 +1625,7 @@
         <v>16</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.342464040212886</v>
       </c>
     </row>
     <row r="58">
@@ -1650,7 +1647,7 @@
         <v>16</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.14795918367347</v>
+        <v>-16.3226878749983</v>
       </c>
     </row>
     <row r="60">
@@ -1661,7 +1658,7 @@
         <v>16</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.350980817357486</v>
+        <v>-0.11983952974195</v>
       </c>
     </row>
     <row r="61">
@@ -1683,7 +1680,7 @@
         <v>16</v>
       </c>
       <c r="C62" t="n">
-        <v>-10.3466963312814</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="63">
@@ -1694,7 +1691,7 @@
         <v>16</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.266193539288589</v>
+        <v>-1.69351583239271</v>
       </c>
     </row>
     <row r="64">
@@ -1705,7 +1702,7 @@
         <v>16</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.408719111986352</v>
+        <v>-0.412845182451828</v>
       </c>
     </row>
     <row r="65">
@@ -1738,7 +1735,7 @@
         <v>16</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.219888576640661</v>
+        <v>-0.658108597218342</v>
       </c>
     </row>
     <row r="68">
@@ -1749,7 +1746,7 @@
         <v>16</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.41416476420622</v>
       </c>
     </row>
     <row r="69">
@@ -1760,7 +1757,7 @@
         <v>16</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.175720302200832</v>
+        <v>-0.538966470159925</v>
       </c>
     </row>
     <row r="70">
@@ -1771,7 +1768,7 @@
         <v>16</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.236444857253992</v>
+        <v>-0.769956040993735</v>
       </c>
     </row>
     <row r="71">
@@ -1782,7 +1779,7 @@
         <v>16</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.214492278827269</v>
+        <v>-2.84042097322796</v>
       </c>
     </row>
     <row r="72">
@@ -1793,7 +1790,7 @@
         <v>16</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.541502387846087</v>
       </c>
     </row>
     <row r="73">
@@ -1804,7 +1801,7 @@
         <v>16</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.402972632876242</v>
+        <v>-0.177831397744304</v>
       </c>
     </row>
     <row r="74">
@@ -1815,7 +1812,7 @@
         <v>16</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.212102541352453</v>
+        <v>-0.547327150921881</v>
       </c>
     </row>
     <row r="75">
@@ -1837,7 +1834,7 @@
         <v>16</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.202244107761481</v>
+        <v>-0.227330311921026</v>
       </c>
     </row>
     <row r="77">
@@ -1848,7 +1845,7 @@
         <v>16</v>
       </c>
       <c r="C77" t="n">
-        <v>0.188890905611332</v>
+        <v>0.074294891794883</v>
       </c>
     </row>
     <row r="78">
@@ -1859,7 +1856,7 @@
         <v>16</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.895593580200462</v>
       </c>
     </row>
     <row r="79">
@@ -1881,7 +1878,7 @@
         <v>16</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.693424465928744</v>
+        <v>-0.112204359803032</v>
       </c>
     </row>
     <row r="81">
@@ -1892,7 +1889,7 @@
         <v>16</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.259599745786723</v>
+        <v>-0.23758768062703</v>
       </c>
     </row>
     <row r="82">
@@ -1903,7 +1900,7 @@
         <v>16</v>
       </c>
       <c r="C82" t="n">
-        <v>0.0893268630919111</v>
+        <v>-0.0408550596083637</v>
       </c>
     </row>
     <row r="83">
@@ -1914,7 +1911,7 @@
         <v>16</v>
       </c>
       <c r="C83" t="n">
-        <v>-2.94941416228591</v>
+        <v>-0.264493849628434</v>
       </c>
     </row>
     <row r="84">
@@ -1925,7 +1922,7 @@
         <v>16</v>
       </c>
       <c r="C84" t="n">
-        <v>-0.147959183673469</v>
+        <v>-6.00801237751746</v>
       </c>
     </row>
     <row r="85">
@@ -1936,7 +1933,7 @@
         <v>16</v>
       </c>
       <c r="C85" t="n">
-        <v>-0.193187844403814</v>
+        <v>-0.357180328675477</v>
       </c>
     </row>
     <row r="86">
@@ -1947,7 +1944,7 @@
         <v>16</v>
       </c>
       <c r="C86" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.761126486846923</v>
       </c>
     </row>
     <row r="87">
@@ -1958,7 +1955,7 @@
         <v>16</v>
       </c>
       <c r="C87" t="n">
-        <v>-1.49442598926993</v>
+        <v>-0.199775782461246</v>
       </c>
     </row>
     <row r="88">
@@ -1980,7 +1977,7 @@
         <v>16</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.798109497686421</v>
+        <v>-0.967056102942326</v>
       </c>
     </row>
     <row r="90">
@@ -2002,7 +1999,7 @@
         <v>16</v>
       </c>
       <c r="C91" t="n">
-        <v>-1.04287190675604</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="92">
@@ -2013,7 +2010,7 @@
         <v>16</v>
       </c>
       <c r="C92" t="n">
-        <v>-0.37407686032533</v>
+        <v>-1.55808061863203</v>
       </c>
     </row>
     <row r="93">
@@ -2024,7 +2021,7 @@
         <v>16</v>
       </c>
       <c r="C93" t="n">
-        <v>-0.839480257518568</v>
+        <v>-0.871222565990115</v>
       </c>
     </row>
     <row r="94">
@@ -2046,7 +2043,7 @@
         <v>16</v>
       </c>
       <c r="C95" t="n">
-        <v>-0.512923275821721</v>
+        <v>0.0630576579865831</v>
       </c>
     </row>
     <row r="96">
@@ -2057,7 +2054,7 @@
         <v>16</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.855539744118357</v>
+        <v>0.243771875832064</v>
       </c>
     </row>
     <row r="97">
@@ -2068,7 +2065,7 @@
         <v>16</v>
       </c>
       <c r="C97" t="n">
-        <v>-0.271034274796105</v>
+        <v>-0.12299662567725</v>
       </c>
     </row>
     <row r="98">
@@ -2079,7 +2076,7 @@
         <v>16</v>
       </c>
       <c r="C98" t="n">
-        <v>-0.0947300081918885</v>
+        <v>-0.256998344027879</v>
       </c>
     </row>
     <row r="99">
@@ -2090,7 +2087,7 @@
         <v>16</v>
       </c>
       <c r="C99" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.314193070947425</v>
       </c>
     </row>
     <row r="100">
@@ -2101,7 +2098,7 @@
         <v>16</v>
       </c>
       <c r="C100" t="n">
-        <v>-0.228244694545351</v>
+        <v>-0.619579355420243</v>
       </c>
     </row>
     <row r="101">
@@ -2112,7 +2109,7 @@
         <v>16</v>
       </c>
       <c r="C101" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.563104694784658</v>
       </c>
     </row>
     <row r="102">
@@ -2123,7 +2120,7 @@
         <v>16</v>
       </c>
       <c r="C102" t="n">
-        <v>-0.432917920926842</v>
+        <v>-10.9916544446623</v>
       </c>
     </row>
     <row r="103">
@@ -2134,7 +2131,7 @@
         <v>16</v>
       </c>
       <c r="C103" t="n">
-        <v>-0.473339996857729</v>
+        <v>-0.699998696918014</v>
       </c>
     </row>
     <row r="104">
@@ -2156,7 +2153,7 @@
         <v>16</v>
       </c>
       <c r="C105" t="n">
-        <v>-0.296908105484332</v>
+        <v>0.0516153274093588</v>
       </c>
     </row>
     <row r="106">
@@ -2167,7 +2164,7 @@
         <v>16</v>
       </c>
       <c r="C106" t="n">
-        <v>-0.110429533062326</v>
+        <v>0.0958365363448093</v>
       </c>
     </row>
     <row r="107">
@@ -2178,7 +2175,7 @@
         <v>16</v>
       </c>
       <c r="C107" t="n">
-        <v>-0.193794068667165</v>
+        <v>-0.659494572318514</v>
       </c>
     </row>
     <row r="108">
@@ -2189,7 +2186,7 @@
         <v>16</v>
       </c>
       <c r="C108" t="n">
-        <v>-0.391404366182582</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="109">
@@ -2200,7 +2197,7 @@
         <v>16</v>
       </c>
       <c r="C109" t="n">
-        <v>0.0451526182727975</v>
+        <v>-0.938836220654007</v>
       </c>
     </row>
     <row r="110">
@@ -2222,7 +2219,7 @@
         <v>16</v>
       </c>
       <c r="C111" t="n">
-        <v>-0.21113976643839</v>
+        <v>-23.6732656473002</v>
       </c>
     </row>
     <row r="112">
@@ -2233,7 +2230,7 @@
         <v>16</v>
       </c>
       <c r="C112" t="n">
-        <v>0.0231051922105276</v>
+        <v>-0.876618173619062</v>
       </c>
     </row>
     <row r="113">
@@ -2266,7 +2263,7 @@
         <v>16</v>
       </c>
       <c r="C115" t="n">
-        <v>-0.635746215773499</v>
+        <v>-0.292430685885215</v>
       </c>
     </row>
     <row r="116">
@@ -2277,7 +2274,7 @@
         <v>16</v>
       </c>
       <c r="C116" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.175991568992585</v>
       </c>
     </row>
     <row r="117">
@@ -2288,7 +2285,7 @@
         <v>16</v>
       </c>
       <c r="C117" t="n">
-        <v>-0.399152855568567</v>
+        <v>-0.263865430624222</v>
       </c>
     </row>
     <row r="118">
@@ -2299,7 +2296,7 @@
         <v>16</v>
       </c>
       <c r="C118" t="n">
-        <v>-0.162822679573721</v>
+        <v>-1.05969053163676</v>
       </c>
     </row>
     <row r="119">
@@ -2321,7 +2318,7 @@
         <v>16</v>
       </c>
       <c r="C120" t="n">
-        <v>-0.182114454670906</v>
+        <v>-0.265229161949125</v>
       </c>
     </row>
     <row r="121">
@@ -2332,7 +2329,7 @@
         <v>16</v>
       </c>
       <c r="C121" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.476509579396122</v>
       </c>
     </row>
     <row r="122">
@@ -2343,7 +2340,7 @@
         <v>16</v>
       </c>
       <c r="C122" t="n">
-        <v>-0.310733994168149</v>
+        <v>-0.187728346489999</v>
       </c>
     </row>
     <row r="123">
@@ -2365,7 +2362,7 @@
         <v>16</v>
       </c>
       <c r="C124" t="n">
-        <v>-0.244696401252213</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="125">
@@ -2376,7 +2373,7 @@
         <v>16</v>
       </c>
       <c r="C125" t="n">
-        <v>-0.164301135693624</v>
+        <v>-0.107713475251431</v>
       </c>
     </row>
     <row r="126">
@@ -2387,7 +2384,7 @@
         <v>16</v>
       </c>
       <c r="C126" t="n">
-        <v>-0.19792861215547</v>
+        <v>-0.216302244400653</v>
       </c>
     </row>
     <row r="127">
@@ -2398,7 +2395,7 @@
         <v>16</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.166731901100681</v>
+        <v>-0.557954194297503</v>
       </c>
     </row>
     <row r="128">
@@ -2409,7 +2406,7 @@
         <v>16</v>
       </c>
       <c r="C128" t="n">
-        <v>-0.438335942011047</v>
+        <v>-0.646658680243122</v>
       </c>
     </row>
     <row r="129">
@@ -2420,7 +2417,7 @@
         <v>16</v>
       </c>
       <c r="C129" t="n">
-        <v>-2.11404684013689</v>
+        <v>-4.32723247050128</v>
       </c>
     </row>
     <row r="130">
@@ -2431,7 +2428,7 @@
         <v>16</v>
       </c>
       <c r="C130" t="n">
-        <v>-0.727155110655691</v>
+        <v>-0.0903976072700123</v>
       </c>
     </row>
     <row r="131">
@@ -2442,7 +2439,7 @@
         <v>16</v>
       </c>
       <c r="C131" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.403007389483265</v>
       </c>
     </row>
     <row r="132">
@@ -2453,7 +2450,7 @@
         <v>16</v>
       </c>
       <c r="C132" t="n">
-        <v>-0.211645789884233</v>
+        <v>-1.13152969151829</v>
       </c>
     </row>
     <row r="133">
@@ -2475,7 +2472,7 @@
         <v>16</v>
       </c>
       <c r="C134" t="n">
-        <v>-0.14795918367347</v>
+        <v>-3.21097976831496</v>
       </c>
     </row>
     <row r="135">
@@ -2486,7 +2483,7 @@
         <v>16</v>
       </c>
       <c r="C135" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.310459129286268</v>
       </c>
     </row>
     <row r="136">
@@ -2497,7 +2494,7 @@
         <v>16</v>
       </c>
       <c r="C136" t="n">
-        <v>-0.257804364551437</v>
+        <v>-0.245670988599895</v>
       </c>
     </row>
     <row r="137">
@@ -2508,7 +2505,7 @@
         <v>16</v>
       </c>
       <c r="C137" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.453025611676278</v>
       </c>
     </row>
     <row r="138">
@@ -2519,7 +2516,7 @@
         <v>16</v>
       </c>
       <c r="C138" t="n">
-        <v>-0.223603950013569</v>
+        <v>-0.456049500138131</v>
       </c>
     </row>
     <row r="139">
@@ -2541,7 +2538,7 @@
         <v>16</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.150771739396558</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="141">
@@ -2563,7 +2560,7 @@
         <v>16</v>
       </c>
       <c r="C142" t="n">
-        <v>-0.298198072980585</v>
+        <v>-0.567125477177961</v>
       </c>
     </row>
     <row r="143">
@@ -2574,7 +2571,7 @@
         <v>16</v>
       </c>
       <c r="C143" t="n">
-        <v>-0.0548243794946581</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="144">
@@ -2596,7 +2593,7 @@
         <v>16</v>
       </c>
       <c r="C145" t="n">
-        <v>-0.640006125285644</v>
+        <v>-0.957560940956527</v>
       </c>
     </row>
     <row r="146">
@@ -2607,7 +2604,7 @@
         <v>16</v>
       </c>
       <c r="C146" t="n">
-        <v>-1.02434375042552</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="147">
@@ -2618,7 +2615,7 @@
         <v>16</v>
       </c>
       <c r="C147" t="n">
-        <v>-0.826381621024685</v>
+        <v>-0.183613750800861</v>
       </c>
     </row>
     <row r="148">
@@ -2629,7 +2626,7 @@
         <v>16</v>
       </c>
       <c r="C148" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.322853637472438</v>
       </c>
     </row>
     <row r="149">
@@ -2640,7 +2637,7 @@
         <v>16</v>
       </c>
       <c r="C149" t="n">
-        <v>-0.404048571704655</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="150">
@@ -2673,7 +2670,7 @@
         <v>16</v>
       </c>
       <c r="C152" t="n">
-        <v>-0.119409997627143</v>
+        <v>-0.920844064238275</v>
       </c>
     </row>
     <row r="153">
@@ -2684,7 +2681,7 @@
         <v>16</v>
       </c>
       <c r="C153" t="n">
-        <v>-0.238305524618071</v>
+        <v>-0.178550097199338</v>
       </c>
     </row>
     <row r="154">
@@ -2695,7 +2692,7 @@
         <v>16</v>
       </c>
       <c r="C154" t="n">
-        <v>-0.241938380517668</v>
+        <v>-3.52310508120814</v>
       </c>
     </row>
     <row r="155">
@@ -2706,7 +2703,7 @@
         <v>16</v>
       </c>
       <c r="C155" t="n">
-        <v>-0.502837643533993</v>
+        <v>-0.292029078980202</v>
       </c>
     </row>
     <row r="156">
@@ -2717,7 +2714,7 @@
         <v>16</v>
       </c>
       <c r="C156" t="n">
-        <v>-0.404835151023269</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="157">
@@ -2728,7 +2725,7 @@
         <v>16</v>
       </c>
       <c r="C157" t="n">
-        <v>0.351609184059349</v>
+        <v>-0.60481540099199</v>
       </c>
     </row>
     <row r="158">
@@ -2739,7 +2736,7 @@
         <v>16</v>
       </c>
       <c r="C158" t="n">
-        <v>-0.196061563079438</v>
+        <v>-4.55374230663795</v>
       </c>
     </row>
     <row r="159">
@@ -2761,7 +2758,7 @@
         <v>16</v>
       </c>
       <c r="C160" t="n">
-        <v>-0.253826765409849</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="161">
@@ -2783,7 +2780,7 @@
         <v>16</v>
       </c>
       <c r="C162" t="n">
-        <v>-1.35611655269252</v>
+        <v>-0.246713866697412</v>
       </c>
     </row>
     <row r="163">
@@ -2794,7 +2791,7 @@
         <v>16</v>
       </c>
       <c r="C163" t="n">
-        <v>-0.251409961743454</v>
+        <v>-1.60164430806044</v>
       </c>
     </row>
     <row r="164">
@@ -2816,7 +2813,7 @@
         <v>16</v>
       </c>
       <c r="C165" t="n">
-        <v>-0.236140899884034</v>
+        <v>-0.90546009235922</v>
       </c>
     </row>
     <row r="166">
@@ -2838,7 +2835,7 @@
         <v>16</v>
       </c>
       <c r="C167" t="n">
-        <v>-0.199737781737552</v>
+        <v>-0.23957011191573</v>
       </c>
     </row>
     <row r="168">
@@ -2849,7 +2846,7 @@
         <v>16</v>
       </c>
       <c r="C168" t="n">
-        <v>-0.343799155598478</v>
+        <v>-0.626822636198868</v>
       </c>
     </row>
     <row r="169">
@@ -2860,7 +2857,7 @@
         <v>16</v>
       </c>
       <c r="C169" t="n">
-        <v>-1.93455665308833</v>
+        <v>-0.223426083141099</v>
       </c>
     </row>
     <row r="170">
@@ -2871,7 +2868,7 @@
         <v>16</v>
       </c>
       <c r="C170" t="n">
-        <v>-0.156284811399556</v>
+        <v>-0.464490088730625</v>
       </c>
     </row>
     <row r="171">
@@ -2882,7 +2879,7 @@
         <v>16</v>
       </c>
       <c r="C171" t="n">
-        <v>-0.169959076931148</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="172">
@@ -2893,7 +2890,7 @@
         <v>16</v>
       </c>
       <c r="C172" t="n">
-        <v>-1.95175609286471</v>
+        <v>-21.5099294661898</v>
       </c>
     </row>
     <row r="173">
@@ -2904,7 +2901,7 @@
         <v>16</v>
       </c>
       <c r="C173" t="n">
-        <v>-0.162393719176769</v>
+        <v>-2.01687679855856</v>
       </c>
     </row>
     <row r="174">
@@ -2915,7 +2912,7 @@
         <v>16</v>
       </c>
       <c r="C174" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.428018051817633</v>
       </c>
     </row>
     <row r="175">
@@ -2937,7 +2934,7 @@
         <v>16</v>
       </c>
       <c r="C176" t="n">
-        <v>-0.363661807151539</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="177">
@@ -2948,7 +2945,7 @@
         <v>16</v>
       </c>
       <c r="C177" t="n">
-        <v>-0.190470803520606</v>
+        <v>-0.187181935648846</v>
       </c>
     </row>
     <row r="178">
@@ -2992,7 +2989,7 @@
         <v>16</v>
       </c>
       <c r="C181" t="n">
-        <v>-0.39471265787026</v>
+        <v>-0.764250600728079</v>
       </c>
     </row>
     <row r="182">
@@ -3003,7 +3000,7 @@
         <v>16</v>
       </c>
       <c r="C182" t="n">
-        <v>-2.23025361115958</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="183">
@@ -3014,7 +3011,7 @@
         <v>16</v>
       </c>
       <c r="C183" t="n">
-        <v>-0.347246296981376</v>
+        <v>-0.632580355944244</v>
       </c>
     </row>
     <row r="184">
@@ -3025,7 +3022,7 @@
         <v>16</v>
       </c>
       <c r="C184" t="n">
-        <v>-0.19690219707166</v>
+        <v>-0.169449693660503</v>
       </c>
     </row>
     <row r="185">
@@ -3036,7 +3033,7 @@
         <v>16</v>
       </c>
       <c r="C185" t="n">
-        <v>-0.0460676529090045</v>
+        <v>0.254983644266688</v>
       </c>
     </row>
     <row r="186">
@@ -3047,7 +3044,7 @@
         <v>16</v>
       </c>
       <c r="C186" t="n">
-        <v>-0.404582439946285</v>
+        <v>-1.91995192810707</v>
       </c>
     </row>
     <row r="187">
@@ -3058,7 +3055,7 @@
         <v>16</v>
       </c>
       <c r="C187" t="n">
-        <v>-0.463985209779359</v>
+        <v>-0.469925697518264</v>
       </c>
     </row>
     <row r="188">
@@ -3069,7 +3066,7 @@
         <v>16</v>
       </c>
       <c r="C188" t="n">
-        <v>-0.360008372425674</v>
+        <v>-0.507931706689943</v>
       </c>
     </row>
     <row r="189">
@@ -3080,7 +3077,7 @@
         <v>16</v>
       </c>
       <c r="C189" t="n">
-        <v>-0.0477428276619705</v>
+        <v>-1.88284028526747</v>
       </c>
     </row>
     <row r="190">
@@ -3091,7 +3088,7 @@
         <v>16</v>
       </c>
       <c r="C190" t="n">
-        <v>-0.551430851242001</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="191">
@@ -3102,7 +3099,7 @@
         <v>16</v>
       </c>
       <c r="C191" t="n">
-        <v>-0.0373812950129566</v>
+        <v>-0.528002480071822</v>
       </c>
     </row>
     <row r="192">
@@ -3113,7 +3110,7 @@
         <v>16</v>
       </c>
       <c r="C192" t="n">
-        <v>-0.337788912887998</v>
+        <v>-0.298379947250694</v>
       </c>
     </row>
     <row r="193">
@@ -3124,7 +3121,7 @@
         <v>16</v>
       </c>
       <c r="C193" t="n">
-        <v>-0.158718149702153</v>
+        <v>-1.43547581011212</v>
       </c>
     </row>
     <row r="194">
@@ -3135,7 +3132,7 @@
         <v>16</v>
       </c>
       <c r="C194" t="n">
-        <v>-0.305456803664538</v>
+        <v>-0.177517912842491</v>
       </c>
     </row>
     <row r="195">
@@ -3146,7 +3143,7 @@
         <v>16</v>
       </c>
       <c r="C195" t="n">
-        <v>-0.160206822101483</v>
+        <v>-0.197020378591777</v>
       </c>
     </row>
     <row r="196">
@@ -3157,7 +3154,7 @@
         <v>16</v>
       </c>
       <c r="C196" t="n">
-        <v>-2.22867279052589</v>
+        <v>-1.98741751039682</v>
       </c>
     </row>
     <row r="197">
@@ -3179,7 +3176,7 @@
         <v>16</v>
       </c>
       <c r="C198" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.309624415572195</v>
       </c>
     </row>
     <row r="199">
@@ -3190,7 +3187,7 @@
         <v>16</v>
       </c>
       <c r="C199" t="n">
-        <v>-0.14795918367347</v>
+        <v>-2.27642925851888</v>
       </c>
     </row>
     <row r="200">
@@ -3201,7 +3198,7 @@
         <v>16</v>
       </c>
       <c r="C200" t="n">
-        <v>-0.336491794381148</v>
+        <v>-0.559632691673144</v>
       </c>
     </row>
     <row r="201">
@@ -3223,7 +3220,7 @@
         <v>16</v>
       </c>
       <c r="C202" t="n">
-        <v>-2.28399049232249</v>
+        <v>-0.211063381354762</v>
       </c>
     </row>
     <row r="203">
@@ -3234,7 +3231,7 @@
         <v>16</v>
       </c>
       <c r="C203" t="n">
-        <v>-0.35039212160886</v>
+        <v>-0.0670082097757212</v>
       </c>
     </row>
     <row r="204">
@@ -3245,7 +3242,7 @@
         <v>16</v>
       </c>
       <c r="C204" t="n">
-        <v>-0.13459306900621</v>
+        <v>-4.78673438124336</v>
       </c>
     </row>
     <row r="205">
@@ -3267,7 +3264,7 @@
         <v>16</v>
       </c>
       <c r="C206" t="n">
-        <v>-0.339596203074176</v>
+        <v>-0.264503040752035</v>
       </c>
     </row>
     <row r="207">
@@ -3278,7 +3275,7 @@
         <v>16</v>
       </c>
       <c r="C207" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.703937848396751</v>
       </c>
     </row>
     <row r="208">
@@ -3289,7 +3286,7 @@
         <v>16</v>
       </c>
       <c r="C208" t="n">
-        <v>-0.189768739964898</v>
+        <v>-0.19569246581746</v>
       </c>
     </row>
     <row r="209">
@@ -3300,7 +3297,7 @@
         <v>16</v>
       </c>
       <c r="C209" t="n">
-        <v>-0.440467043768164</v>
+        <v>-0.389692498444616</v>
       </c>
     </row>
     <row r="210">
@@ -3322,7 +3319,7 @@
         <v>16</v>
       </c>
       <c r="C211" t="n">
-        <v>-0.422589387611207</v>
+        <v>-0.376602310834165</v>
       </c>
     </row>
     <row r="212">
@@ -3333,7 +3330,7 @@
         <v>16</v>
       </c>
       <c r="C212" t="n">
-        <v>-0.198709451997709</v>
+        <v>-1.03999343002384</v>
       </c>
     </row>
     <row r="213">
@@ -3344,7 +3341,7 @@
         <v>16</v>
       </c>
       <c r="C213" t="n">
-        <v>-0.176981168753523</v>
+        <v>-0.803789419938253</v>
       </c>
     </row>
     <row r="214">
@@ -3355,7 +3352,7 @@
         <v>16</v>
       </c>
       <c r="C214" t="n">
-        <v>-0.388795772324293</v>
+        <v>-0.537121732429168</v>
       </c>
     </row>
     <row r="215">
@@ -3377,7 +3374,7 @@
         <v>16</v>
       </c>
       <c r="C216" t="n">
-        <v>-2.44982517520207</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="217">
@@ -3399,7 +3396,7 @@
         <v>16</v>
       </c>
       <c r="C218" t="n">
-        <v>-0.434161646749733</v>
+        <v>-0.355215784934718</v>
       </c>
     </row>
     <row r="219">
@@ -3410,7 +3407,7 @@
         <v>16</v>
       </c>
       <c r="C219" t="n">
-        <v>-0.321945751969325</v>
+        <v>-0.66025261156133</v>
       </c>
     </row>
     <row r="220">
@@ -3421,7 +3418,7 @@
         <v>16</v>
       </c>
       <c r="C220" t="n">
-        <v>-0.239608172165667</v>
+        <v>-0.232722489714322</v>
       </c>
     </row>
     <row r="221">
@@ -3432,7 +3429,7 @@
         <v>16</v>
       </c>
       <c r="C221" t="n">
-        <v>-0.846995701759539</v>
+        <v>-0.182901008297399</v>
       </c>
     </row>
     <row r="222">
@@ -3454,7 +3451,7 @@
         <v>16</v>
       </c>
       <c r="C223" t="n">
-        <v>-0.175241701372888</v>
+        <v>-0.128456830311638</v>
       </c>
     </row>
     <row r="224">
@@ -3465,7 +3462,7 @@
         <v>16</v>
       </c>
       <c r="C224" t="n">
-        <v>-0.14795918367347</v>
+        <v>-5.56595415899992</v>
       </c>
     </row>
     <row r="225">
@@ -3476,7 +3473,7 @@
         <v>16</v>
       </c>
       <c r="C225" t="n">
-        <v>-1.5773574230223</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="226">
@@ -3487,7 +3484,7 @@
         <v>16</v>
       </c>
       <c r="C226" t="n">
-        <v>-1.71326202507562</v>
+        <v>-0.0484701567839914</v>
       </c>
     </row>
     <row r="227">
@@ -3520,7 +3517,7 @@
         <v>16</v>
       </c>
       <c r="C229" t="n">
-        <v>-0.326523289280479</v>
+        <v>-0.276456105467918</v>
       </c>
     </row>
     <row r="230">
@@ -3542,7 +3539,7 @@
         <v>16</v>
       </c>
       <c r="C231" t="n">
-        <v>0.0649305711137257</v>
+        <v>0.273486582441389</v>
       </c>
     </row>
     <row r="232">
@@ -3575,7 +3572,7 @@
         <v>16</v>
       </c>
       <c r="C234" t="n">
-        <v>-0.356390709317045</v>
+        <v>-0.335696176766459</v>
       </c>
     </row>
     <row r="235">
@@ -3586,7 +3583,7 @@
         <v>16</v>
       </c>
       <c r="C235" t="n">
-        <v>-0.336743200457027</v>
+        <v>-0.439771319398772</v>
       </c>
     </row>
     <row r="236">
@@ -3597,7 +3594,7 @@
         <v>16</v>
       </c>
       <c r="C236" t="n">
-        <v>-0.280204303680169</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="237">
@@ -3608,7 +3605,7 @@
         <v>16</v>
       </c>
       <c r="C237" t="n">
-        <v>-0.165431100622386</v>
+        <v>-0.754684123083113</v>
       </c>
     </row>
     <row r="238">
@@ -3652,7 +3649,7 @@
         <v>16</v>
       </c>
       <c r="C241" t="n">
-        <v>-0.227481842500969</v>
+        <v>-0.331883168804015</v>
       </c>
     </row>
     <row r="242">
@@ -3685,7 +3682,7 @@
         <v>16</v>
       </c>
       <c r="C244" t="n">
-        <v>-0.232413591439468</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="245">
@@ -3696,7 +3693,7 @@
         <v>16</v>
       </c>
       <c r="C245" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.215633821059518</v>
       </c>
     </row>
     <row r="246">
@@ -3707,7 +3704,7 @@
         <v>16</v>
       </c>
       <c r="C246" t="n">
-        <v>-0.305004684364535</v>
+        <v>-0.354515923801128</v>
       </c>
     </row>
     <row r="247">
@@ -3718,7 +3715,7 @@
         <v>16</v>
       </c>
       <c r="C247" t="n">
-        <v>-1.80260872769174</v>
+        <v>-0.726470080279085</v>
       </c>
     </row>
     <row r="248">
@@ -3729,7 +3726,7 @@
         <v>16</v>
       </c>
       <c r="C248" t="n">
-        <v>-0.252703593575575</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="249">
@@ -3740,7 +3737,7 @@
         <v>16</v>
       </c>
       <c r="C249" t="n">
-        <v>-0.44134719026151</v>
+        <v>-0.38719217116169</v>
       </c>
     </row>
     <row r="250">
@@ -3762,7 +3759,7 @@
         <v>16</v>
       </c>
       <c r="C251" t="n">
-        <v>-0.729363571063824</v>
+        <v>-0.415603192120476</v>
       </c>
     </row>
     <row r="252">
@@ -3795,7 +3792,7 @@
         <v>16</v>
       </c>
       <c r="C254" t="n">
-        <v>-0.604901368826689</v>
+        <v>-0.326123865919923</v>
       </c>
     </row>
     <row r="255">
@@ -3817,7 +3814,7 @@
         <v>16</v>
       </c>
       <c r="C256" t="n">
-        <v>-4.04304375180586</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="257">
@@ -3839,7 +3836,7 @@
         <v>16</v>
       </c>
       <c r="C258" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.555774206607122</v>
       </c>
     </row>
     <row r="259">
@@ -3850,7 +3847,7 @@
         <v>16</v>
       </c>
       <c r="C259" t="n">
-        <v>-0.348650409827554</v>
+        <v>-0.239560170627898</v>
       </c>
     </row>
     <row r="260">
@@ -3861,7 +3858,7 @@
         <v>16</v>
       </c>
       <c r="C260" t="n">
-        <v>-0.257412520605694</v>
+        <v>-0.162761683394052</v>
       </c>
     </row>
     <row r="261">
@@ -3894,7 +3891,7 @@
         <v>16</v>
       </c>
       <c r="C263" t="n">
-        <v>-0.237186800182348</v>
+        <v>-0.226900502667102</v>
       </c>
     </row>
     <row r="264">
@@ -3905,7 +3902,7 @@
         <v>16</v>
       </c>
       <c r="C264" t="n">
-        <v>-0.520830544623524</v>
+        <v>-0.372795434437182</v>
       </c>
     </row>
     <row r="265">
@@ -3916,7 +3913,7 @@
         <v>16</v>
       </c>
       <c r="C265" t="n">
-        <v>-0.468755451619781</v>
+        <v>-0.223861191023538</v>
       </c>
     </row>
     <row r="266">
@@ -3927,7 +3924,7 @@
         <v>16</v>
       </c>
       <c r="C266" t="n">
-        <v>-0.253556319102128</v>
+        <v>-4.93948099009097</v>
       </c>
     </row>
     <row r="267">
@@ -3938,7 +3935,7 @@
         <v>16</v>
       </c>
       <c r="C267" t="n">
-        <v>-0.379947457788499</v>
+        <v>-0.8459142394268</v>
       </c>
     </row>
     <row r="268">
@@ -3949,7 +3946,7 @@
         <v>16</v>
       </c>
       <c r="C268" t="n">
-        <v>-0.237473317485664</v>
+        <v>-0.324348210104652</v>
       </c>
     </row>
     <row r="269">
@@ -3960,7 +3957,7 @@
         <v>16</v>
       </c>
       <c r="C269" t="n">
-        <v>-4.52866306049379</v>
+        <v>-0.77567756958465</v>
       </c>
     </row>
     <row r="270">
@@ -3971,7 +3968,7 @@
         <v>16</v>
       </c>
       <c r="C270" t="n">
-        <v>-1.34116491672514</v>
+        <v>-1.20472637748343</v>
       </c>
     </row>
     <row r="271">
@@ -3993,7 +3990,7 @@
         <v>16</v>
       </c>
       <c r="C272" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.579000844695178</v>
       </c>
     </row>
     <row r="273">
@@ -4004,7 +4001,7 @@
         <v>16</v>
       </c>
       <c r="C273" t="n">
-        <v>-0.386827934432395</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="274">
@@ -4015,7 +4012,7 @@
         <v>16</v>
       </c>
       <c r="C274" t="n">
-        <v>-0.171785101788237</v>
+        <v>-0.190351206844271</v>
       </c>
     </row>
     <row r="275">
@@ -4037,7 +4034,7 @@
         <v>16</v>
       </c>
       <c r="C276" t="n">
-        <v>-0.154943335120902</v>
+        <v>-1.02409358219349</v>
       </c>
     </row>
     <row r="277">
@@ -4081,7 +4078,7 @@
         <v>16</v>
       </c>
       <c r="C280" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.188762890267978</v>
       </c>
     </row>
     <row r="281">
@@ -4092,7 +4089,7 @@
         <v>16</v>
       </c>
       <c r="C281" t="n">
-        <v>0.131579885668736</v>
+        <v>0.372986478685961</v>
       </c>
     </row>
     <row r="282">
@@ -4103,7 +4100,7 @@
         <v>16</v>
       </c>
       <c r="C282" t="n">
-        <v>0.122010390431471</v>
+        <v>0.0829575665265574</v>
       </c>
     </row>
     <row r="283">
@@ -4114,7 +4111,7 @@
         <v>16</v>
       </c>
       <c r="C283" t="n">
-        <v>-0.177046359048588</v>
+        <v>-0.274533235020108</v>
       </c>
     </row>
     <row r="284">
@@ -4136,7 +4133,7 @@
         <v>16</v>
       </c>
       <c r="C285" t="n">
-        <v>-1.50090444583853</v>
+        <v>-0.631521631333721</v>
       </c>
     </row>
     <row r="286">
@@ -4147,7 +4144,7 @@
         <v>16</v>
       </c>
       <c r="C286" t="n">
-        <v>-0.428316061516493</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="287">
@@ -4158,7 +4155,7 @@
         <v>16</v>
       </c>
       <c r="C287" t="n">
-        <v>-0.51447705842189</v>
+        <v>-0.952972495965889</v>
       </c>
     </row>
     <row r="288">
@@ -4169,7 +4166,7 @@
         <v>16</v>
       </c>
       <c r="C288" t="n">
-        <v>-2.00586457790224</v>
+        <v>-14.2876768327017</v>
       </c>
     </row>
     <row r="289">
@@ -4180,7 +4177,7 @@
         <v>16</v>
       </c>
       <c r="C289" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.321280004276239</v>
       </c>
     </row>
     <row r="290">
@@ -4191,7 +4188,7 @@
         <v>16</v>
       </c>
       <c r="C290" t="n">
-        <v>-2.24432842049543</v>
+        <v>-0.467998587538768</v>
       </c>
     </row>
     <row r="291">
@@ -4202,7 +4199,7 @@
         <v>16</v>
       </c>
       <c r="C291" t="n">
-        <v>-0.406198954018561</v>
+        <v>-0.570261244307854</v>
       </c>
     </row>
     <row r="292">
@@ -4213,7 +4210,7 @@
         <v>16</v>
       </c>
       <c r="C292" t="n">
-        <v>-0.283222703393397</v>
+        <v>-0.222477372405801</v>
       </c>
     </row>
     <row r="293">
@@ -4224,7 +4221,7 @@
         <v>16</v>
       </c>
       <c r="C293" t="n">
-        <v>-0.708023381009354</v>
+        <v>-0.733666937826725</v>
       </c>
     </row>
     <row r="294">
@@ -4235,7 +4232,7 @@
         <v>16</v>
       </c>
       <c r="C294" t="n">
-        <v>-0.147959183673469</v>
+        <v>-14.4683540034899</v>
       </c>
     </row>
     <row r="295">
@@ -4246,7 +4243,7 @@
         <v>16</v>
       </c>
       <c r="C295" t="n">
-        <v>-0.949134178550539</v>
+        <v>-0.170374242202099</v>
       </c>
     </row>
     <row r="296">
@@ -4257,7 +4254,7 @@
         <v>16</v>
       </c>
       <c r="C296" t="n">
-        <v>-0.301801441039968</v>
+        <v>-1.18319004508653</v>
       </c>
     </row>
     <row r="297">
@@ -4279,7 +4276,7 @@
         <v>16</v>
       </c>
       <c r="C298" t="n">
-        <v>-0.291412388360938</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="299">
@@ -4290,7 +4287,7 @@
         <v>16</v>
       </c>
       <c r="C299" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.337551097160163</v>
       </c>
     </row>
     <row r="300">
@@ -4301,7 +4298,7 @@
         <v>16</v>
       </c>
       <c r="C300" t="n">
-        <v>-0.28582150615755</v>
+        <v>-0.168444383841269</v>
       </c>
     </row>
     <row r="301">
@@ -4312,7 +4309,7 @@
         <v>16</v>
       </c>
       <c r="C301" t="n">
-        <v>-0.409750397999217</v>
+        <v>-1.22504727586297</v>
       </c>
     </row>
     <row r="302">
@@ -4323,7 +4320,7 @@
         <v>16</v>
       </c>
       <c r="C302" t="n">
-        <v>-0.399486636255778</v>
+        <v>-1.0346371102888</v>
       </c>
     </row>
     <row r="303">
@@ -4334,7 +4331,7 @@
         <v>16</v>
       </c>
       <c r="C303" t="n">
-        <v>-0.71436139628344</v>
+        <v>-0.998786056555457</v>
       </c>
     </row>
     <row r="304">
@@ -4345,7 +4342,7 @@
         <v>16</v>
       </c>
       <c r="C304" t="n">
-        <v>-0.380243646336666</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="305">
@@ -4356,7 +4353,7 @@
         <v>16</v>
       </c>
       <c r="C305" t="n">
-        <v>-0.150862563110734</v>
+        <v>-0.174446856567006</v>
       </c>
     </row>
     <row r="306">
@@ -4367,7 +4364,7 @@
         <v>16</v>
       </c>
       <c r="C306" t="n">
-        <v>0.244895760126163</v>
+        <v>0.279079153729623</v>
       </c>
     </row>
     <row r="307">
@@ -4378,7 +4375,7 @@
         <v>16</v>
       </c>
       <c r="C307" t="n">
-        <v>-0.346575352493012</v>
+        <v>-0.64547098173781</v>
       </c>
     </row>
     <row r="308">
@@ -4389,7 +4386,7 @@
         <v>16</v>
       </c>
       <c r="C308" t="n">
-        <v>-0.257044732642753</v>
+        <v>-4.13705864780915</v>
       </c>
     </row>
     <row r="309">
@@ -4400,7 +4397,7 @@
         <v>16</v>
       </c>
       <c r="C309" t="n">
-        <v>-0.20829993319674</v>
+        <v>0.931969746154189</v>
       </c>
     </row>
     <row r="310">
@@ -4411,7 +4408,7 @@
         <v>16</v>
       </c>
       <c r="C310" t="n">
-        <v>-0.14795918367347</v>
+        <v>-19.6043463585229</v>
       </c>
     </row>
     <row r="311">
@@ -4422,7 +4419,7 @@
         <v>16</v>
       </c>
       <c r="C311" t="n">
-        <v>-0.273084562166376</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="312">
@@ -4433,7 +4430,7 @@
         <v>16</v>
       </c>
       <c r="C312" t="n">
-        <v>-0.189037090580712</v>
+        <v>-0.180204482424264</v>
       </c>
     </row>
     <row r="313">
@@ -4444,7 +4441,7 @@
         <v>16</v>
       </c>
       <c r="C313" t="n">
-        <v>-0.190141855265239</v>
+        <v>-0.194370558066513</v>
       </c>
     </row>
     <row r="314">
@@ -4455,7 +4452,7 @@
         <v>16</v>
       </c>
       <c r="C314" t="n">
-        <v>-0.7914117600565</v>
+        <v>-1.40170251446474</v>
       </c>
     </row>
     <row r="315">
@@ -4466,7 +4463,7 @@
         <v>16</v>
       </c>
       <c r="C315" t="n">
-        <v>-0.343982062184429</v>
+        <v>-1.01251110652833</v>
       </c>
     </row>
     <row r="316">
@@ -4477,7 +4474,7 @@
         <v>16</v>
       </c>
       <c r="C316" t="n">
-        <v>-0.381695502570615</v>
+        <v>-0.174124959546051</v>
       </c>
     </row>
     <row r="317">
@@ -4488,7 +4485,7 @@
         <v>16</v>
       </c>
       <c r="C317" t="n">
-        <v>-1.60480228151716</v>
+        <v>-0.242451948466712</v>
       </c>
     </row>
     <row r="318">
@@ -4510,7 +4507,7 @@
         <v>16</v>
       </c>
       <c r="C319" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.298835740640274</v>
       </c>
     </row>
     <row r="320">
@@ -4521,7 +4518,7 @@
         <v>16</v>
       </c>
       <c r="C320" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.812822650357246</v>
       </c>
     </row>
     <row r="321">
@@ -4543,7 +4540,7 @@
         <v>16</v>
       </c>
       <c r="C322" t="n">
-        <v>-0.265530207030813</v>
+        <v>-0.518032096485612</v>
       </c>
     </row>
     <row r="323">
@@ -4565,7 +4562,7 @@
         <v>16</v>
       </c>
       <c r="C324" t="n">
-        <v>-0.147959183673469</v>
+        <v>-2.14122665746958</v>
       </c>
     </row>
     <row r="325">
@@ -4587,7 +4584,7 @@
         <v>16</v>
       </c>
       <c r="C326" t="n">
-        <v>-0.384367302417987</v>
+        <v>-22.1831231054943</v>
       </c>
     </row>
     <row r="327">
@@ -4598,7 +4595,7 @@
         <v>16</v>
       </c>
       <c r="C327" t="n">
-        <v>-0.184226364362065</v>
+        <v>-0.156586583201961</v>
       </c>
     </row>
     <row r="328">
@@ -4609,7 +4606,7 @@
         <v>16</v>
       </c>
       <c r="C328" t="n">
-        <v>-0.601807545671584</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="329">
@@ -4620,7 +4617,7 @@
         <v>16</v>
       </c>
       <c r="C329" t="n">
-        <v>-0.762481070447032</v>
+        <v>-0.651955885472444</v>
       </c>
     </row>
     <row r="330">
@@ -4631,7 +4628,7 @@
         <v>16</v>
       </c>
       <c r="C330" t="n">
-        <v>-0.944934009398439</v>
+        <v>-0.771757543443383</v>
       </c>
     </row>
     <row r="331">
@@ -4642,7 +4639,7 @@
         <v>16</v>
       </c>
       <c r="C331" t="n">
-        <v>-0.535110238339806</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="332">
@@ -4653,7 +4650,7 @@
         <v>16</v>
       </c>
       <c r="C332" t="n">
-        <v>-0.057504704587334</v>
+        <v>-0.268971824295665</v>
       </c>
     </row>
     <row r="333">
@@ -4675,7 +4672,7 @@
         <v>16</v>
       </c>
       <c r="C334" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.99043782879228</v>
       </c>
     </row>
     <row r="335">
@@ -4686,7 +4683,7 @@
         <v>16</v>
       </c>
       <c r="C335" t="n">
-        <v>-0.22165377902945</v>
+        <v>-0.0808961598673241</v>
       </c>
     </row>
     <row r="336">
@@ -4697,7 +4694,7 @@
         <v>16</v>
       </c>
       <c r="C336" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.379601124247227</v>
       </c>
     </row>
     <row r="337">
@@ -4719,7 +4716,7 @@
         <v>16</v>
       </c>
       <c r="C338" t="n">
-        <v>-0.0424593881317867</v>
+        <v>0.0393532494212316</v>
       </c>
     </row>
     <row r="339">
@@ -4730,7 +4727,7 @@
         <v>16</v>
       </c>
       <c r="C339" t="n">
-        <v>-0.317205372668617</v>
+        <v>-0.374710362716249</v>
       </c>
     </row>
     <row r="340">
@@ -4752,7 +4749,7 @@
         <v>16</v>
       </c>
       <c r="C341" t="n">
-        <v>-0.34830013800274</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="342">
@@ -4763,7 +4760,7 @@
         <v>16</v>
       </c>
       <c r="C342" t="n">
-        <v>-0.189438827385654</v>
+        <v>-0.436651808896133</v>
       </c>
     </row>
     <row r="343">
@@ -4774,7 +4771,7 @@
         <v>16</v>
       </c>
       <c r="C343" t="n">
-        <v>-0.638268197081107</v>
+        <v>-0.444825899143195</v>
       </c>
     </row>
     <row r="344">
@@ -4785,7 +4782,7 @@
         <v>16</v>
       </c>
       <c r="C344" t="n">
-        <v>-0.230602966075833</v>
+        <v>-0.767113577493817</v>
       </c>
     </row>
     <row r="345">
@@ -4796,7 +4793,7 @@
         <v>16</v>
       </c>
       <c r="C345" t="n">
-        <v>0.431232989688202</v>
+        <v>0.52721431538438</v>
       </c>
     </row>
     <row r="346">
@@ -4807,7 +4804,7 @@
         <v>16</v>
       </c>
       <c r="C346" t="n">
-        <v>-3.38775416902253</v>
+        <v>-1.65004257856136</v>
       </c>
     </row>
     <row r="347">
@@ -4829,7 +4826,7 @@
         <v>16</v>
       </c>
       <c r="C348" t="n">
-        <v>-0.264873475438438</v>
+        <v>-0.302370912037403</v>
       </c>
     </row>
     <row r="349">
@@ -4840,7 +4837,7 @@
         <v>16</v>
       </c>
       <c r="C349" t="n">
-        <v>-0.00448065566288514</v>
+        <v>-0.339411186493501</v>
       </c>
     </row>
     <row r="350">
@@ -4862,7 +4859,7 @@
         <v>16</v>
       </c>
       <c r="C351" t="n">
-        <v>-0.283368477463685</v>
+        <v>-1.77881236243487</v>
       </c>
     </row>
     <row r="352">
@@ -4884,7 +4881,7 @@
         <v>16</v>
       </c>
       <c r="C353" t="n">
-        <v>-0.221697297680409</v>
+        <v>-0.441806032579441</v>
       </c>
     </row>
     <row r="354">
@@ -4895,7 +4892,7 @@
         <v>16</v>
       </c>
       <c r="C354" t="n">
-        <v>-0.182709914288189</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="355">
@@ -4906,7 +4903,7 @@
         <v>16</v>
       </c>
       <c r="C355" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.32939450326332</v>
       </c>
     </row>
     <row r="356">
@@ -4917,7 +4914,7 @@
         <v>16</v>
       </c>
       <c r="C356" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.155796876006481</v>
       </c>
     </row>
     <row r="357">
@@ -4928,7 +4925,7 @@
         <v>16</v>
       </c>
       <c r="C357" t="n">
-        <v>0.550070083826559</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="358">
@@ -4961,7 +4958,7 @@
         <v>16</v>
       </c>
       <c r="C360" t="n">
-        <v>-0.228129741100974</v>
+        <v>-1.02340286973847</v>
       </c>
     </row>
     <row r="361">
@@ -4972,7 +4969,7 @@
         <v>16</v>
       </c>
       <c r="C361" t="n">
-        <v>-0.427062089976695</v>
+        <v>-0.260585941565958</v>
       </c>
     </row>
     <row r="362">
@@ -4983,7 +4980,7 @@
         <v>16</v>
       </c>
       <c r="C362" t="n">
-        <v>-1.23924983922832</v>
+        <v>-0.167162028541395</v>
       </c>
     </row>
     <row r="363">
@@ -4994,7 +4991,7 @@
         <v>16</v>
       </c>
       <c r="C363" t="n">
-        <v>-0.330720972556437</v>
+        <v>-0.399663885439039</v>
       </c>
     </row>
     <row r="364">
@@ -5016,7 +5013,7 @@
         <v>16</v>
       </c>
       <c r="C365" t="n">
-        <v>-0.416496281699183</v>
+        <v>-0.979690770741568</v>
       </c>
     </row>
     <row r="366">
@@ -5027,7 +5024,7 @@
         <v>16</v>
       </c>
       <c r="C366" t="n">
-        <v>-0.492884751828219</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="367">
@@ -5049,7 +5046,7 @@
         <v>16</v>
       </c>
       <c r="C368" t="n">
-        <v>-0.312861128052964</v>
+        <v>-0.208820448415192</v>
       </c>
     </row>
     <row r="369">
@@ -5060,7 +5057,7 @@
         <v>16</v>
       </c>
       <c r="C369" t="n">
-        <v>-0.390436855080929</v>
+        <v>-0.394704948340435</v>
       </c>
     </row>
     <row r="370">
@@ -5071,7 +5068,7 @@
         <v>16</v>
       </c>
       <c r="C370" t="n">
-        <v>-0.201727431602809</v>
+        <v>-0.183736321967649</v>
       </c>
     </row>
     <row r="371">
@@ -5082,7 +5079,7 @@
         <v>16</v>
       </c>
       <c r="C371" t="n">
-        <v>-0.337238576848809</v>
+        <v>-1.19708255010724</v>
       </c>
     </row>
     <row r="372">
@@ -5137,7 +5134,7 @@
         <v>16</v>
       </c>
       <c r="C376" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.421692716603332</v>
       </c>
     </row>
     <row r="377">
@@ -5170,7 +5167,7 @@
         <v>16</v>
       </c>
       <c r="C379" t="n">
-        <v>-0.147959183673469</v>
+        <v>-20.0344778061065</v>
       </c>
     </row>
     <row r="380">
@@ -5181,7 +5178,7 @@
         <v>16</v>
       </c>
       <c r="C380" t="n">
-        <v>-1.62720154903519</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="381">
@@ -5214,7 +5211,7 @@
         <v>16</v>
       </c>
       <c r="C383" t="n">
-        <v>-0.13773463248832</v>
+        <v>-0.373147205694866</v>
       </c>
     </row>
     <row r="384">
@@ -5236,7 +5233,7 @@
         <v>16</v>
       </c>
       <c r="C385" t="n">
-        <v>0.0153749437081819</v>
+        <v>0.144472181197069</v>
       </c>
     </row>
     <row r="386">
@@ -5247,7 +5244,7 @@
         <v>16</v>
       </c>
       <c r="C386" t="n">
-        <v>-6.20104069723563</v>
+        <v>-1.92583653416809</v>
       </c>
     </row>
     <row r="387">
@@ -5258,7 +5255,7 @@
         <v>16</v>
       </c>
       <c r="C387" t="n">
-        <v>-1.44795464968822</v>
+        <v>-0.248382929879809</v>
       </c>
     </row>
     <row r="388">
@@ -5269,7 +5266,7 @@
         <v>16</v>
       </c>
       <c r="C388" t="n">
-        <v>-0.238843749343385</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="389">
@@ -5280,7 +5277,7 @@
         <v>16</v>
       </c>
       <c r="C389" t="n">
-        <v>0.202482310563152</v>
+        <v>-1.33909525790447</v>
       </c>
     </row>
     <row r="390">
@@ -5291,7 +5288,7 @@
         <v>16</v>
       </c>
       <c r="C390" t="n">
-        <v>-0.821243472218491</v>
+        <v>-2.180358849146</v>
       </c>
     </row>
     <row r="391">
@@ -5302,7 +5299,7 @@
         <v>16</v>
       </c>
       <c r="C391" t="n">
-        <v>-0.194906233492769</v>
+        <v>0.0770766531642133</v>
       </c>
     </row>
     <row r="392">
@@ -5313,7 +5310,7 @@
         <v>16</v>
       </c>
       <c r="C392" t="n">
-        <v>-0.159223860668343</v>
+        <v>-0.140918095897172</v>
       </c>
     </row>
     <row r="393">
@@ -5324,7 +5321,7 @@
         <v>16</v>
       </c>
       <c r="C393" t="n">
-        <v>-0.264781058021869</v>
+        <v>-0.455329096227994</v>
       </c>
     </row>
     <row r="394">
@@ -5335,7 +5332,7 @@
         <v>16</v>
       </c>
       <c r="C394" t="n">
-        <v>-0.306797262749771</v>
+        <v>-0.348997495776407</v>
       </c>
     </row>
     <row r="395">
@@ -5346,7 +5343,7 @@
         <v>16</v>
       </c>
       <c r="C395" t="n">
-        <v>-0.075436755453895</v>
+        <v>-0.0331959526098493</v>
       </c>
     </row>
     <row r="396">
@@ -5357,7 +5354,7 @@
         <v>16</v>
       </c>
       <c r="C396" t="n">
-        <v>-0.566158234480615</v>
+        <v>-0.370750342947505</v>
       </c>
     </row>
     <row r="397">
@@ -5368,7 +5365,7 @@
         <v>16</v>
       </c>
       <c r="C397" t="n">
-        <v>-1.68326411179008</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="398">
@@ -5379,7 +5376,7 @@
         <v>16</v>
       </c>
       <c r="C398" t="n">
-        <v>-0.403113904433593</v>
+        <v>-0.196959607114194</v>
       </c>
     </row>
     <row r="399">
@@ -5390,7 +5387,7 @@
         <v>16</v>
       </c>
       <c r="C399" t="n">
-        <v>-0.223908802226275</v>
+        <v>-0.786033362630142</v>
       </c>
     </row>
     <row r="400">
@@ -5401,7 +5398,7 @@
         <v>16</v>
       </c>
       <c r="C400" t="n">
-        <v>-0.610549750069058</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="401">
@@ -5423,7 +5420,7 @@
         <v>16</v>
       </c>
       <c r="C402" t="n">
-        <v>-0.147959183673469</v>
+        <v>-4.17304211635808</v>
       </c>
     </row>
     <row r="403">
@@ -5434,7 +5431,7 @@
         <v>16</v>
       </c>
       <c r="C403" t="n">
-        <v>-0.194235997287872</v>
+        <v>-0.145942353717586</v>
       </c>
     </row>
     <row r="404">
@@ -5445,7 +5442,7 @@
         <v>16</v>
       </c>
       <c r="C404" t="n">
-        <v>-0.0884764482393356</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="405">
@@ -5467,7 +5464,7 @@
         <v>16</v>
       </c>
       <c r="C406" t="n">
-        <v>-0.173841310076407</v>
+        <v>-0.209326049677169</v>
       </c>
     </row>
     <row r="407">
@@ -5478,7 +5475,7 @@
         <v>16</v>
       </c>
       <c r="C407" t="n">
-        <v>-0.147959183673469</v>
+        <v>-5.57652773969624</v>
       </c>
     </row>
     <row r="408">
@@ -5489,7 +5486,7 @@
         <v>16</v>
       </c>
       <c r="C408" t="n">
-        <v>0.0988333474648924</v>
+        <v>0.0881307414138488</v>
       </c>
     </row>
     <row r="409">
@@ -5500,7 +5497,7 @@
         <v>16</v>
       </c>
       <c r="C409" t="n">
-        <v>-0.267069669548887</v>
+        <v>-0.163253603304585</v>
       </c>
     </row>
     <row r="410">
@@ -5522,7 +5519,7 @@
         <v>16</v>
       </c>
       <c r="C411" t="n">
-        <v>-0.467861013452926</v>
+        <v>-0.469790512568449</v>
       </c>
     </row>
     <row r="412">
@@ -5533,7 +5530,7 @@
         <v>16</v>
       </c>
       <c r="C412" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.39953519080617</v>
       </c>
     </row>
     <row r="413">
@@ -5544,7 +5541,7 @@
         <v>16</v>
       </c>
       <c r="C413" t="n">
-        <v>-0.1583002240495</v>
+        <v>-0.240989355995332</v>
       </c>
     </row>
     <row r="414">
@@ -5555,7 +5552,7 @@
         <v>16</v>
       </c>
       <c r="C414" t="n">
-        <v>-0.248736979719193</v>
+        <v>-0.192815751543275</v>
       </c>
     </row>
     <row r="415">
@@ -5566,7 +5563,7 @@
         <v>16</v>
       </c>
       <c r="C415" t="n">
-        <v>-0.202725478373061</v>
+        <v>-0.176529964958119</v>
       </c>
     </row>
     <row r="416">
@@ -5588,7 +5585,7 @@
         <v>16</v>
       </c>
       <c r="C417" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.405825983606221</v>
       </c>
     </row>
     <row r="418">
@@ -5599,7 +5596,7 @@
         <v>16</v>
       </c>
       <c r="C418" t="n">
-        <v>-0.216366842315301</v>
+        <v>-0.430469097318698</v>
       </c>
     </row>
     <row r="419">
@@ -5610,7 +5607,7 @@
         <v>16</v>
       </c>
       <c r="C419" t="n">
-        <v>-0.168209760485571</v>
+        <v>-1.38443205762989</v>
       </c>
     </row>
     <row r="420">
@@ -5621,7 +5618,7 @@
         <v>16</v>
       </c>
       <c r="C420" t="n">
-        <v>-0.256391955519212</v>
+        <v>-0.243253204700954</v>
       </c>
     </row>
     <row r="421">
@@ -5632,7 +5629,7 @@
         <v>16</v>
       </c>
       <c r="C421" t="n">
-        <v>-0.523444959360932</v>
+        <v>-0.29139860595306</v>
       </c>
     </row>
     <row r="422">
@@ -5654,7 +5651,7 @@
         <v>16</v>
       </c>
       <c r="C423" t="n">
-        <v>-0.169911457513836</v>
+        <v>-0.557569059848395</v>
       </c>
     </row>
     <row r="424">
@@ -5665,7 +5662,7 @@
         <v>16</v>
       </c>
       <c r="C424" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.24412780086594</v>
       </c>
     </row>
     <row r="425">
@@ -5676,7 +5673,7 @@
         <v>16</v>
       </c>
       <c r="C425" t="n">
-        <v>-1.70685407963428</v>
+        <v>-17.8333011599112</v>
       </c>
     </row>
     <row r="426">
@@ -5687,7 +5684,7 @@
         <v>16</v>
       </c>
       <c r="C426" t="n">
-        <v>-2.0345875480021</v>
+        <v>-0.162150985545821</v>
       </c>
     </row>
     <row r="427">
@@ -5709,7 +5706,7 @@
         <v>16</v>
       </c>
       <c r="C428" t="n">
-        <v>-0.36850023291818</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="429">
@@ -5720,7 +5717,7 @@
         <v>16</v>
       </c>
       <c r="C429" t="n">
-        <v>-0.251182243092388</v>
+        <v>-0.268172832073332</v>
       </c>
     </row>
     <row r="430">
@@ -5742,7 +5739,7 @@
         <v>16</v>
       </c>
       <c r="C431" t="n">
-        <v>-0.0965300219810759</v>
+        <v>0.0271544632926825</v>
       </c>
     </row>
     <row r="432">
@@ -5775,7 +5772,7 @@
         <v>16</v>
       </c>
       <c r="C434" t="n">
-        <v>-0.598515518654907</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="435">
@@ -5786,7 +5783,7 @@
         <v>16</v>
       </c>
       <c r="C435" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.347129227859202</v>
       </c>
     </row>
     <row r="436">
@@ -5797,7 +5794,7 @@
         <v>16</v>
       </c>
       <c r="C436" t="n">
-        <v>-0.403307368299122</v>
+        <v>-0.245031678842219</v>
       </c>
     </row>
     <row r="437">
@@ -5808,7 +5805,7 @@
         <v>16</v>
       </c>
       <c r="C437" t="n">
-        <v>-0.568037919485241</v>
+        <v>-0.0166138229967132</v>
       </c>
     </row>
     <row r="438">
@@ -5852,7 +5849,7 @@
         <v>16</v>
       </c>
       <c r="C441" t="n">
-        <v>-0.167916596420657</v>
+        <v>-0.191456109394971</v>
       </c>
     </row>
     <row r="442">
@@ -5885,7 +5882,7 @@
         <v>16</v>
       </c>
       <c r="C444" t="n">
-        <v>-0.488349611101257</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="445">
@@ -5896,7 +5893,7 @@
         <v>16</v>
       </c>
       <c r="C445" t="n">
-        <v>-0.320953065519508</v>
+        <v>-0.420991182292099</v>
       </c>
     </row>
     <row r="446">
@@ -5907,7 +5904,7 @@
         <v>16</v>
       </c>
       <c r="C446" t="n">
-        <v>-0.365487653973941</v>
+        <v>-0.132935843873357</v>
       </c>
     </row>
     <row r="447">
@@ -5918,7 +5915,7 @@
         <v>16</v>
       </c>
       <c r="C447" t="n">
-        <v>-0.182994801745273</v>
+        <v>0.108263092790229</v>
       </c>
     </row>
     <row r="448">
@@ -5929,7 +5926,7 @@
         <v>16</v>
       </c>
       <c r="C448" t="n">
-        <v>-0.485560947361768</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="449">
@@ -5940,7 +5937,7 @@
         <v>16</v>
       </c>
       <c r="C449" t="n">
-        <v>-0.556644287205454</v>
+        <v>-0.960549082173359</v>
       </c>
     </row>
     <row r="450">
@@ -5984,7 +5981,7 @@
         <v>16</v>
       </c>
       <c r="C453" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.181701887124468</v>
       </c>
     </row>
     <row r="454">
@@ -5995,7 +5992,7 @@
         <v>16</v>
       </c>
       <c r="C454" t="n">
-        <v>-0.270063967795488</v>
+        <v>-0.390550749321779</v>
       </c>
     </row>
     <row r="455">
@@ -6006,7 +6003,7 @@
         <v>16</v>
       </c>
       <c r="C455" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.762790913452043</v>
       </c>
     </row>
     <row r="456">
@@ -6017,7 +6014,7 @@
         <v>16</v>
       </c>
       <c r="C456" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.905231457096562</v>
       </c>
     </row>
     <row r="457">
@@ -6028,7 +6025,7 @@
         <v>16</v>
       </c>
       <c r="C457" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.37364138350774</v>
       </c>
     </row>
     <row r="458">
@@ -6039,7 +6036,7 @@
         <v>16</v>
       </c>
       <c r="C458" t="n">
-        <v>-0.477481894860532</v>
+        <v>-0.44902435755349</v>
       </c>
     </row>
     <row r="459">
@@ -6050,7 +6047,7 @@
         <v>16</v>
       </c>
       <c r="C459" t="n">
-        <v>-0.153559483747621</v>
+        <v>-0.278278339337751</v>
       </c>
     </row>
     <row r="460">
@@ -6061,7 +6058,7 @@
         <v>16</v>
       </c>
       <c r="C460" t="n">
-        <v>-0.35903326793214</v>
+        <v>-0.396453055888096</v>
       </c>
     </row>
     <row r="461">
@@ -6072,7 +6069,7 @@
         <v>16</v>
       </c>
       <c r="C461" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.54403638147545</v>
       </c>
     </row>
     <row r="462">
@@ -6094,7 +6091,7 @@
         <v>16</v>
       </c>
       <c r="C463" t="n">
-        <v>-0.197393959624155</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="464">
@@ -6105,7 +6102,7 @@
         <v>16</v>
       </c>
       <c r="C464" t="n">
-        <v>-1.36579312932667</v>
+        <v>-0.384021434142513</v>
       </c>
     </row>
     <row r="465">
@@ -6116,7 +6113,7 @@
         <v>16</v>
       </c>
       <c r="C465" t="n">
-        <v>-0.34808379899418</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="466">
@@ -6127,7 +6124,7 @@
         <v>16</v>
       </c>
       <c r="C466" t="n">
-        <v>-0.714524653801146</v>
+        <v>-0.462489733225914</v>
       </c>
     </row>
     <row r="467">
@@ -6138,7 +6135,7 @@
         <v>16</v>
       </c>
       <c r="C467" t="n">
-        <v>-0.370799140000173</v>
+        <v>-1.05611532877248</v>
       </c>
     </row>
     <row r="468">
@@ -6149,7 +6146,7 @@
         <v>16</v>
       </c>
       <c r="C468" t="n">
-        <v>-0.363848656637863</v>
+        <v>-0.207522062269781</v>
       </c>
     </row>
     <row r="469">
@@ -6160,7 +6157,7 @@
         <v>16</v>
       </c>
       <c r="C469" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.596827049694631</v>
       </c>
     </row>
     <row r="470">
@@ -6171,7 +6168,7 @@
         <v>16</v>
       </c>
       <c r="C470" t="n">
-        <v>-0.147959183673469</v>
+        <v>-5.6222977598153</v>
       </c>
     </row>
     <row r="471">
@@ -6193,7 +6190,7 @@
         <v>16</v>
       </c>
       <c r="C472" t="n">
-        <v>-0.194276242906464</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="473">
@@ -6204,7 +6201,7 @@
         <v>16</v>
       </c>
       <c r="C473" t="n">
-        <v>-0.158258606201567</v>
+        <v>-0.281762204842838</v>
       </c>
     </row>
     <row r="474">
@@ -6215,7 +6212,7 @@
         <v>16</v>
       </c>
       <c r="C474" t="n">
-        <v>-0.183042650344425</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="475">
@@ -6237,7 +6234,7 @@
         <v>16</v>
       </c>
       <c r="C476" t="n">
-        <v>-0.222324055389931</v>
+        <v>-0.248056848093957</v>
       </c>
     </row>
     <row r="477">
@@ -6281,7 +6278,7 @@
         <v>16</v>
       </c>
       <c r="C480" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.306506216227537</v>
       </c>
     </row>
     <row r="481">
@@ -6292,7 +6289,7 @@
         <v>16</v>
       </c>
       <c r="C481" t="n">
-        <v>0.232709921316343</v>
+        <v>0.330208975712065</v>
       </c>
     </row>
     <row r="482">
@@ -6303,7 +6300,7 @@
         <v>16</v>
       </c>
       <c r="C482" t="n">
-        <v>0.207142768197285</v>
+        <v>-0.61814526581183</v>
       </c>
     </row>
     <row r="483">
@@ -6314,7 +6311,7 @@
         <v>16</v>
       </c>
       <c r="C483" t="n">
-        <v>-0.146808048209499</v>
+        <v>-0.193629635956758</v>
       </c>
     </row>
     <row r="484">
@@ -6325,7 +6322,7 @@
         <v>16</v>
       </c>
       <c r="C484" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.08542022451466</v>
       </c>
     </row>
     <row r="485">
@@ -6336,7 +6333,7 @@
         <v>16</v>
       </c>
       <c r="C485" t="n">
-        <v>-0.147959183673469</v>
+        <v>0.0682977252653933</v>
       </c>
     </row>
     <row r="486">
@@ -6347,7 +6344,7 @@
         <v>16</v>
       </c>
       <c r="C486" t="n">
-        <v>-0.312250427534314</v>
+        <v>-0.63324653786426</v>
       </c>
     </row>
     <row r="487">
@@ -6358,7 +6355,7 @@
         <v>16</v>
       </c>
       <c r="C487" t="n">
-        <v>-0.23732487175759</v>
+        <v>-0.49854894926152</v>
       </c>
     </row>
     <row r="488">
@@ -6391,7 +6388,7 @@
         <v>16</v>
       </c>
       <c r="C490" t="n">
-        <v>-2.68977978597372</v>
+        <v>-0.479522451486926</v>
       </c>
     </row>
     <row r="491">
@@ -6402,7 +6399,7 @@
         <v>16</v>
       </c>
       <c r="C491" t="n">
-        <v>-0.175840234399841</v>
+        <v>-1.3323855137515</v>
       </c>
     </row>
     <row r="492">
@@ -6413,7 +6410,7 @@
         <v>16</v>
       </c>
       <c r="C492" t="n">
-        <v>-0.179358895098733</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="493">
@@ -6424,7 +6421,7 @@
         <v>16</v>
       </c>
       <c r="C493" t="n">
-        <v>-0.679899943184122</v>
+        <v>-0.487430014806417</v>
       </c>
     </row>
     <row r="494">
@@ -6446,7 +6443,7 @@
         <v>16</v>
       </c>
       <c r="C495" t="n">
-        <v>-1.22652581738711</v>
+        <v>-0.424601488256231</v>
       </c>
     </row>
     <row r="496">
@@ -6479,7 +6476,7 @@
         <v>16</v>
       </c>
       <c r="C498" t="n">
-        <v>-0.220500531215378</v>
+        <v>-0.513192085415972</v>
       </c>
     </row>
     <row r="499">
@@ -6490,7 +6487,7 @@
         <v>16</v>
       </c>
       <c r="C499" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.184427814410039</v>
       </c>
     </row>
     <row r="500">
@@ -6501,7 +6498,7 @@
         <v>16</v>
       </c>
       <c r="C500" t="n">
-        <v>-0.194535371019291</v>
+        <v>-0.259194036071509</v>
       </c>
     </row>
     <row r="501">
@@ -6512,7 +6509,7 @@
         <v>16</v>
       </c>
       <c r="C501" t="n">
-        <v>-0.147959183673469</v>
+        <v>-4.3190547652631</v>
       </c>
     </row>
     <row r="502">
@@ -6523,7 +6520,7 @@
         <v>16</v>
       </c>
       <c r="C502" t="n">
-        <v>-0.672592318515309</v>
+        <v>-0.536934254183484</v>
       </c>
     </row>
     <row r="503">
@@ -6534,7 +6531,7 @@
         <v>16</v>
       </c>
       <c r="C503" t="n">
-        <v>-1.72486857001923</v>
+        <v>-0.804067089512878</v>
       </c>
     </row>
     <row r="504">
@@ -6545,7 +6542,7 @@
         <v>16</v>
       </c>
       <c r="C504" t="n">
-        <v>-0.172149399911975</v>
+        <v>-0.798766111946842</v>
       </c>
     </row>
     <row r="505">
@@ -6556,7 +6553,7 @@
         <v>16</v>
       </c>
       <c r="C505" t="n">
-        <v>0.103863705916156</v>
+        <v>-0.140434259419422</v>
       </c>
     </row>
     <row r="506">
@@ -6567,7 +6564,7 @@
         <v>16</v>
       </c>
       <c r="C506" t="n">
-        <v>0.0818116342132905</v>
+        <v>0.125422190071523</v>
       </c>
     </row>
     <row r="507">
@@ -6578,7 +6575,7 @@
         <v>16</v>
       </c>
       <c r="C507" t="n">
-        <v>-0.169999635412211</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="508">
@@ -6600,7 +6597,7 @@
         <v>16</v>
       </c>
       <c r="C509" t="n">
-        <v>-0.576717141139215</v>
+        <v>-2.01586819042327</v>
       </c>
     </row>
     <row r="510">
@@ -6611,7 +6608,7 @@
         <v>16</v>
       </c>
       <c r="C510" t="n">
-        <v>-0.147959183673469</v>
+        <v>-20.847575907079</v>
       </c>
     </row>
     <row r="511">
@@ -6633,7 +6630,7 @@
         <v>16</v>
       </c>
       <c r="C512" t="n">
-        <v>-0.265676483805367</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="513">
@@ -6644,7 +6641,7 @@
         <v>16</v>
       </c>
       <c r="C513" t="n">
-        <v>-0.185544819171298</v>
+        <v>-0.199506389594721</v>
       </c>
     </row>
     <row r="514">
@@ -6655,7 +6652,7 @@
         <v>16</v>
       </c>
       <c r="C514" t="n">
-        <v>-1.06654891750361</v>
+        <v>-0.225342375911307</v>
       </c>
     </row>
     <row r="515">
@@ -6666,7 +6663,7 @@
         <v>16</v>
       </c>
       <c r="C515" t="n">
-        <v>-0.190932694732515</v>
+        <v>-1.20986111146094</v>
       </c>
     </row>
     <row r="516">
@@ -6677,7 +6674,7 @@
         <v>16</v>
       </c>
       <c r="C516" t="n">
-        <v>-0.151434573219553</v>
+        <v>-0.132042746130387</v>
       </c>
     </row>
     <row r="517">
@@ -6688,7 +6685,7 @@
         <v>16</v>
       </c>
       <c r="C517" t="n">
-        <v>-0.525456046337005</v>
+        <v>-0.467386950552655</v>
       </c>
     </row>
     <row r="518">
@@ -6699,7 +6696,7 @@
         <v>16</v>
       </c>
       <c r="C518" t="n">
-        <v>-0.157989274946895</v>
+        <v>-0.152868940754946</v>
       </c>
     </row>
     <row r="519">
@@ -6710,7 +6707,7 @@
         <v>16</v>
       </c>
       <c r="C519" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.291772923146819</v>
       </c>
     </row>
     <row r="520">
@@ -6721,7 +6718,7 @@
         <v>16</v>
       </c>
       <c r="C520" t="n">
-        <v>-0.14795918367347</v>
+        <v>-2.07954779893095</v>
       </c>
     </row>
     <row r="521">
@@ -6743,7 +6740,7 @@
         <v>16</v>
       </c>
       <c r="C522" t="n">
-        <v>-0.41424408691135</v>
+        <v>-0.186832377967687</v>
       </c>
     </row>
     <row r="523">
@@ -6765,7 +6762,7 @@
         <v>16</v>
       </c>
       <c r="C524" t="n">
-        <v>-0.215247841083024</v>
+        <v>-0.189291171297544</v>
       </c>
     </row>
     <row r="525">
@@ -6776,7 +6773,7 @@
         <v>16</v>
       </c>
       <c r="C525" t="n">
-        <v>-0.16994365689904</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="526">
@@ -6787,7 +6784,7 @@
         <v>16</v>
       </c>
       <c r="C526" t="n">
-        <v>-0.147959183673469</v>
+        <v>-26.6394332015564</v>
       </c>
     </row>
     <row r="527">
@@ -6798,7 +6795,7 @@
         <v>16</v>
       </c>
       <c r="C527" t="n">
-        <v>-0.184393512103479</v>
+        <v>-0.159001521413231</v>
       </c>
     </row>
     <row r="528">
@@ -6809,7 +6806,7 @@
         <v>16</v>
       </c>
       <c r="C528" t="n">
-        <v>-0.147959183673469</v>
+        <v>-3.8673137922579</v>
       </c>
     </row>
     <row r="529">
@@ -6820,7 +6817,7 @@
         <v>16</v>
       </c>
       <c r="C529" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.51583916809669</v>
       </c>
     </row>
     <row r="530">
@@ -6831,7 +6828,7 @@
         <v>16</v>
       </c>
       <c r="C530" t="n">
-        <v>-0.642217655052298</v>
+        <v>-0.667274387389422</v>
       </c>
     </row>
     <row r="531">
@@ -6842,7 +6839,7 @@
         <v>16</v>
       </c>
       <c r="C531" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.01734525769838</v>
       </c>
     </row>
     <row r="532">
@@ -6853,7 +6850,7 @@
         <v>16</v>
       </c>
       <c r="C532" t="n">
-        <v>-0.180181714524078</v>
+        <v>-0.26948306440865</v>
       </c>
     </row>
     <row r="533">
@@ -6864,7 +6861,7 @@
         <v>16</v>
       </c>
       <c r="C533" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.391974390052468</v>
       </c>
     </row>
     <row r="534">
@@ -6875,7 +6872,7 @@
         <v>16</v>
       </c>
       <c r="C534" t="n">
-        <v>-0.147959183673469</v>
+        <v>0.272728590292903</v>
       </c>
     </row>
     <row r="535">
@@ -6886,7 +6883,7 @@
         <v>16</v>
       </c>
       <c r="C535" t="n">
-        <v>-0.193827384095656</v>
+        <v>-0.505919020162602</v>
       </c>
     </row>
     <row r="536">
@@ -6919,7 +6916,7 @@
         <v>16</v>
       </c>
       <c r="C538" t="n">
-        <v>-0.183929464423463</v>
+        <v>-0.193329644589252</v>
       </c>
     </row>
     <row r="539">
@@ -6941,7 +6938,7 @@
         <v>16</v>
       </c>
       <c r="C540" t="n">
-        <v>-0.827188451149622</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="541">
@@ -6952,7 +6949,7 @@
         <v>16</v>
       </c>
       <c r="C541" t="n">
-        <v>-0.475803086022331</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="542">
@@ -6963,7 +6960,7 @@
         <v>16</v>
       </c>
       <c r="C542" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.177336912637472</v>
       </c>
     </row>
     <row r="543">
@@ -6974,7 +6971,7 @@
         <v>16</v>
       </c>
       <c r="C543" t="n">
-        <v>-0.347505007877463</v>
+        <v>-0.880000793104417</v>
       </c>
     </row>
     <row r="544">
@@ -6985,7 +6982,7 @@
         <v>16</v>
       </c>
       <c r="C544" t="n">
-        <v>-0.156981683330884</v>
+        <v>-0.154816327770696</v>
       </c>
     </row>
     <row r="545">
@@ -6996,7 +6993,7 @@
         <v>16</v>
       </c>
       <c r="C545" t="n">
-        <v>0.278422332818936</v>
+        <v>0.403012925678177</v>
       </c>
     </row>
     <row r="546">
@@ -7007,7 +7004,7 @@
         <v>16</v>
       </c>
       <c r="C546" t="n">
-        <v>-0.26304743282132</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="547">
@@ -7018,7 +7015,7 @@
         <v>16</v>
       </c>
       <c r="C547" t="n">
-        <v>-0.176655521079402</v>
+        <v>-0.148750418021653</v>
       </c>
     </row>
     <row r="548">
@@ -7029,7 +7026,7 @@
         <v>16</v>
       </c>
       <c r="C548" t="n">
-        <v>-0.307286753667002</v>
+        <v>-0.326268870033527</v>
       </c>
     </row>
     <row r="549">
@@ -7040,7 +7037,7 @@
         <v>16</v>
       </c>
       <c r="C549" t="n">
-        <v>-0.136497583181725</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="550">
@@ -7062,7 +7059,7 @@
         <v>16</v>
       </c>
       <c r="C551" t="n">
-        <v>-0.249775411883707</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="552">
@@ -7073,7 +7070,7 @@
         <v>16</v>
       </c>
       <c r="C552" t="n">
-        <v>-0.537247782748508</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="553">
@@ -7084,7 +7081,7 @@
         <v>16</v>
       </c>
       <c r="C553" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.7647442554019</v>
       </c>
     </row>
     <row r="554">
@@ -7095,7 +7092,7 @@
         <v>16</v>
       </c>
       <c r="C554" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.6006216935595</v>
       </c>
     </row>
     <row r="555">
@@ -7117,7 +7114,7 @@
         <v>16</v>
       </c>
       <c r="C556" t="n">
-        <v>-0.703323350638408</v>
+        <v>-0.457452930176099</v>
       </c>
     </row>
     <row r="557">
@@ -7128,7 +7125,7 @@
         <v>16</v>
       </c>
       <c r="C557" t="n">
-        <v>0.326496158039584</v>
+        <v>-0.348752361298917</v>
       </c>
     </row>
     <row r="558">
@@ -7150,7 +7147,7 @@
         <v>16</v>
       </c>
       <c r="C559" t="n">
-        <v>-0.147959183673469</v>
+        <v>-5.59054836147167</v>
       </c>
     </row>
     <row r="560">
@@ -7161,7 +7158,7 @@
         <v>16</v>
       </c>
       <c r="C560" t="n">
-        <v>-0.261088550488414</v>
+        <v>-0.804506765150864</v>
       </c>
     </row>
     <row r="561">
@@ -7172,7 +7169,7 @@
         <v>16</v>
       </c>
       <c r="C561" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.24421781235481</v>
       </c>
     </row>
     <row r="562">
@@ -7183,7 +7180,7 @@
         <v>16</v>
       </c>
       <c r="C562" t="n">
-        <v>-0.460719940296112</v>
+        <v>-0.259971822660846</v>
       </c>
     </row>
     <row r="563">
@@ -7194,7 +7191,7 @@
         <v>16</v>
       </c>
       <c r="C563" t="n">
-        <v>-0.303517533193547</v>
+        <v>-0.549825121948355</v>
       </c>
     </row>
     <row r="564">
@@ -7216,7 +7213,7 @@
         <v>16</v>
       </c>
       <c r="C565" t="n">
-        <v>-0.871540164077386</v>
+        <v>-0.308055768262472</v>
       </c>
     </row>
     <row r="566">
@@ -7249,7 +7246,7 @@
         <v>16</v>
       </c>
       <c r="C568" t="n">
-        <v>-0.194634780900413</v>
+        <v>-0.189681139990741</v>
       </c>
     </row>
     <row r="569">
@@ -7260,7 +7257,7 @@
         <v>16</v>
       </c>
       <c r="C569" t="n">
-        <v>-0.393456580789155</v>
+        <v>-0.505221543010167</v>
       </c>
     </row>
     <row r="570">
@@ -7271,7 +7268,7 @@
         <v>16</v>
       </c>
       <c r="C570" t="n">
-        <v>-0.282905132973583</v>
+        <v>-0.902155788853388</v>
       </c>
     </row>
     <row r="571">
@@ -7282,7 +7279,7 @@
         <v>16</v>
       </c>
       <c r="C571" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.08511856201441</v>
       </c>
     </row>
     <row r="572">
@@ -7304,7 +7301,7 @@
         <v>16</v>
       </c>
       <c r="C573" t="n">
-        <v>-0.266261091908785</v>
+        <v>-0.355212402370719</v>
       </c>
     </row>
     <row r="574">
@@ -7315,7 +7312,7 @@
         <v>16</v>
       </c>
       <c r="C574" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.180168821963357</v>
       </c>
     </row>
     <row r="575">
@@ -7337,7 +7334,7 @@
         <v>16</v>
       </c>
       <c r="C576" t="n">
-        <v>-7.84004012155785</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="577">
@@ -7370,7 +7367,7 @@
         <v>16</v>
       </c>
       <c r="C579" t="n">
-        <v>-0.147959183673469</v>
+        <v>-23.1693847526941</v>
       </c>
     </row>
     <row r="580">
@@ -7381,7 +7378,7 @@
         <v>16</v>
       </c>
       <c r="C580" t="n">
-        <v>-2.08663108560805</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="581">
@@ -7403,7 +7400,7 @@
         <v>16</v>
       </c>
       <c r="C582" t="n">
-        <v>-0.175228378785837</v>
+        <v>-0.192518075741658</v>
       </c>
     </row>
     <row r="583">
@@ -7414,7 +7411,7 @@
         <v>16</v>
       </c>
       <c r="C583" t="n">
-        <v>-0.114690620648868</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="584">
@@ -7436,7 +7433,7 @@
         <v>16</v>
       </c>
       <c r="C585" t="n">
-        <v>-0.147345150408392</v>
+        <v>-0.128038902393697</v>
       </c>
     </row>
     <row r="586">
@@ -7447,7 +7444,7 @@
         <v>16</v>
       </c>
       <c r="C586" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.13424494378437</v>
       </c>
     </row>
     <row r="587">
@@ -7458,7 +7455,7 @@
         <v>16</v>
       </c>
       <c r="C587" t="n">
-        <v>-0.353495121163812</v>
+        <v>0.0414898258335566</v>
       </c>
     </row>
     <row r="588">
@@ -7469,7 +7466,7 @@
         <v>16</v>
       </c>
       <c r="C588" t="n">
-        <v>-0.209756821274612</v>
+        <v>-0.158058341109245</v>
       </c>
     </row>
     <row r="589">
@@ -7480,7 +7477,7 @@
         <v>16</v>
       </c>
       <c r="C589" t="n">
-        <v>0.256847101563129</v>
+        <v>-0.190011864478605</v>
       </c>
     </row>
     <row r="590">
@@ -7491,7 +7488,7 @@
         <v>16</v>
       </c>
       <c r="C590" t="n">
-        <v>-0.343288063046186</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="591">
@@ -7502,7 +7499,7 @@
         <v>16</v>
       </c>
       <c r="C591" t="n">
-        <v>-0.269657409474193</v>
+        <v>-0.964061963388095</v>
       </c>
     </row>
     <row r="592">
@@ -7513,7 +7510,7 @@
         <v>16</v>
       </c>
       <c r="C592" t="n">
-        <v>-1.03128607464123</v>
+        <v>-0.856786641236324</v>
       </c>
     </row>
     <row r="593">
@@ -7524,7 +7521,7 @@
         <v>16</v>
       </c>
       <c r="C593" t="n">
-        <v>-0.236966078989223</v>
+        <v>-0.472579957381485</v>
       </c>
     </row>
     <row r="594">
@@ -7535,7 +7532,7 @@
         <v>16</v>
       </c>
       <c r="C594" t="n">
-        <v>-0.330309909885345</v>
+        <v>-0.306243135173937</v>
       </c>
     </row>
     <row r="595">
@@ -7546,7 +7543,7 @@
         <v>16</v>
       </c>
       <c r="C595" t="n">
-        <v>0.371926169455429</v>
+        <v>0.389355096742782</v>
       </c>
     </row>
     <row r="596">
@@ -7557,7 +7554,7 @@
         <v>16</v>
       </c>
       <c r="C596" t="n">
-        <v>-0.196766019518091</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="597">
@@ -7590,7 +7587,7 @@
         <v>16</v>
       </c>
       <c r="C599" t="n">
-        <v>-0.202648699531758</v>
+        <v>-0.194022524073856</v>
       </c>
     </row>
     <row r="600">
@@ -7601,7 +7598,7 @@
         <v>16</v>
       </c>
       <c r="C600" t="n">
-        <v>-0.56563955939194</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="601">
@@ -7623,7 +7620,7 @@
         <v>16</v>
       </c>
       <c r="C602" t="n">
-        <v>0.062610768611212</v>
+        <v>-0.345998674751434</v>
       </c>
     </row>
     <row r="603">
@@ -7645,7 +7642,7 @@
         <v>16</v>
       </c>
       <c r="C604" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.116725997287914</v>
       </c>
     </row>
     <row r="605">
@@ -7667,7 +7664,7 @@
         <v>16</v>
       </c>
       <c r="C606" t="n">
-        <v>-3.11014162380978</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="607">
@@ -7678,7 +7675,7 @@
         <v>16</v>
       </c>
       <c r="C607" t="n">
-        <v>-0.254015518636985</v>
+        <v>-0.254511157854613</v>
       </c>
     </row>
     <row r="608">
@@ -7689,7 +7686,7 @@
         <v>16</v>
       </c>
       <c r="C608" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.2594096328729</v>
       </c>
     </row>
     <row r="609">
@@ -7700,7 +7697,7 @@
         <v>16</v>
       </c>
       <c r="C609" t="n">
-        <v>-0.0738266182328544</v>
+        <v>-0.136188261593989</v>
       </c>
     </row>
     <row r="610">
@@ -7711,7 +7708,7 @@
         <v>16</v>
       </c>
       <c r="C610" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.321963102073704</v>
       </c>
     </row>
     <row r="611">
@@ -7722,7 +7719,7 @@
         <v>16</v>
       </c>
       <c r="C611" t="n">
-        <v>-0.299304867042471</v>
+        <v>-0.248888433013544</v>
       </c>
     </row>
     <row r="612">
@@ -7733,7 +7730,7 @@
         <v>16</v>
       </c>
       <c r="C612" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.52394235130424</v>
       </c>
     </row>
     <row r="613">
@@ -7744,7 +7741,7 @@
         <v>16</v>
       </c>
       <c r="C613" t="n">
-        <v>-0.157428813039793</v>
+        <v>-0.263653520310678</v>
       </c>
     </row>
     <row r="614">
@@ -7755,7 +7752,7 @@
         <v>16</v>
       </c>
       <c r="C614" t="n">
-        <v>-0.254311613981601</v>
+        <v>-0.22862609420578</v>
       </c>
     </row>
     <row r="615">
@@ -7766,7 +7763,7 @@
         <v>16</v>
       </c>
       <c r="C615" t="n">
-        <v>-0.30675700016438</v>
+        <v>-0.0319724562923165</v>
       </c>
     </row>
     <row r="616">
@@ -7777,7 +7774,7 @@
         <v>16</v>
       </c>
       <c r="C616" t="n">
-        <v>-0.870183901047968</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="617">
@@ -7788,7 +7785,7 @@
         <v>16</v>
       </c>
       <c r="C617" t="n">
-        <v>-0.147959183673469</v>
+        <v>-15.7091713078769</v>
       </c>
     </row>
     <row r="618">
@@ -7810,7 +7807,7 @@
         <v>16</v>
       </c>
       <c r="C619" t="n">
-        <v>-0.359655786408193</v>
+        <v>-0.171850882046449</v>
       </c>
     </row>
     <row r="620">
@@ -7821,7 +7818,7 @@
         <v>16</v>
       </c>
       <c r="C620" t="n">
-        <v>-0.0508599057598138</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="621">
@@ -7843,7 +7840,7 @@
         <v>16</v>
       </c>
       <c r="C622" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.127494932911549</v>
       </c>
     </row>
     <row r="623">
@@ -7865,7 +7862,7 @@
         <v>16</v>
       </c>
       <c r="C624" t="n">
-        <v>-0.57268537169844</v>
+        <v>-0.715227951121763</v>
       </c>
     </row>
     <row r="625">
@@ -7887,7 +7884,7 @@
         <v>16</v>
       </c>
       <c r="C626" t="n">
-        <v>-0.706749305392266</v>
+        <v>-1.96542557968813</v>
       </c>
     </row>
     <row r="627">
@@ -7898,7 +7895,7 @@
         <v>16</v>
       </c>
       <c r="C627" t="n">
-        <v>-0.758324483117998</v>
+        <v>-0.573486777919273</v>
       </c>
     </row>
     <row r="628">
@@ -7909,7 +7906,7 @@
         <v>16</v>
       </c>
       <c r="C628" t="n">
-        <v>-0.557727105974765</v>
+        <v>-0.57137781469737</v>
       </c>
     </row>
     <row r="629">
@@ -7920,7 +7917,7 @@
         <v>16</v>
       </c>
       <c r="C629" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.540484463049659</v>
       </c>
     </row>
     <row r="630">
@@ -7953,7 +7950,7 @@
         <v>16</v>
       </c>
       <c r="C632" t="n">
-        <v>-0.234819217458697</v>
+        <v>-0.679855633423469</v>
       </c>
     </row>
     <row r="633">
@@ -7975,7 +7972,7 @@
         <v>16</v>
       </c>
       <c r="C634" t="n">
-        <v>-0.27116518052392</v>
+        <v>-0.202430306578587</v>
       </c>
     </row>
     <row r="635">
@@ -7997,7 +7994,7 @@
         <v>16</v>
       </c>
       <c r="C636" t="n">
-        <v>-0.544656987764201</v>
+        <v>-0.196840957969508</v>
       </c>
     </row>
     <row r="637">
@@ -8008,7 +8005,7 @@
         <v>16</v>
       </c>
       <c r="C637" t="n">
-        <v>-0.352568578942442</v>
+        <v>-0.358770220339286</v>
       </c>
     </row>
     <row r="638">
@@ -8019,7 +8016,7 @@
         <v>16</v>
       </c>
       <c r="C638" t="n">
-        <v>-0.28382433051268</v>
+        <v>-0.125494277809002</v>
       </c>
     </row>
     <row r="639">
@@ -8041,7 +8038,7 @@
         <v>16</v>
       </c>
       <c r="C640" t="n">
-        <v>-0.318489075239528</v>
+        <v>-1.24287787591454</v>
       </c>
     </row>
     <row r="641">
@@ -8052,7 +8049,7 @@
         <v>16</v>
       </c>
       <c r="C641" t="n">
-        <v>-0.43874649942051</v>
+        <v>-0.345015299240758</v>
       </c>
     </row>
     <row r="642">
@@ -8063,7 +8060,7 @@
         <v>16</v>
       </c>
       <c r="C642" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.96490144014728</v>
       </c>
     </row>
     <row r="643">
@@ -8085,7 +8082,7 @@
         <v>16</v>
       </c>
       <c r="C644" t="n">
-        <v>-0.147959183673469</v>
+        <v>0.311621810724292</v>
       </c>
     </row>
     <row r="645">
@@ -8096,7 +8093,7 @@
         <v>16</v>
       </c>
       <c r="C645" t="n">
-        <v>-0.341972641719245</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="646">
@@ -8107,7 +8104,7 @@
         <v>16</v>
       </c>
       <c r="C646" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.5201463216196</v>
       </c>
     </row>
     <row r="647">
@@ -8118,7 +8115,7 @@
         <v>16</v>
       </c>
       <c r="C647" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.66566135247285</v>
       </c>
     </row>
     <row r="648">
@@ -8129,7 +8126,7 @@
         <v>16</v>
       </c>
       <c r="C648" t="n">
-        <v>-0.323501786767949</v>
+        <v>-3.38828459819451</v>
       </c>
     </row>
     <row r="649">
@@ -8140,7 +8137,7 @@
         <v>16</v>
       </c>
       <c r="C649" t="n">
-        <v>-0.344540222631954</v>
+        <v>0.0777977759009089</v>
       </c>
     </row>
     <row r="650">
@@ -8184,7 +8181,7 @@
         <v>16</v>
       </c>
       <c r="C653" t="n">
-        <v>-0.312587752604381</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="654">
@@ -8217,7 +8214,7 @@
         <v>16</v>
       </c>
       <c r="C656" t="n">
-        <v>-0.529404185885108</v>
+        <v>-0.4876587369418</v>
       </c>
     </row>
     <row r="657">
@@ -8228,7 +8225,7 @@
         <v>16</v>
       </c>
       <c r="C657" t="n">
-        <v>-0.147959183673469</v>
+        <v>-8.21549372624242</v>
       </c>
     </row>
     <row r="658">
@@ -8250,7 +8247,7 @@
         <v>16</v>
       </c>
       <c r="C659" t="n">
-        <v>-1.07267932168436</v>
+        <v>-0.246245940955435</v>
       </c>
     </row>
     <row r="660">
@@ -8272,7 +8269,7 @@
         <v>16</v>
       </c>
       <c r="C661" t="n">
-        <v>-0.262411013407476</v>
+        <v>-1.39920139953929</v>
       </c>
     </row>
     <row r="662">
@@ -8283,7 +8280,7 @@
         <v>16</v>
       </c>
       <c r="C662" t="n">
-        <v>-0.260801659353019</v>
+        <v>-0.399575365359956</v>
       </c>
     </row>
     <row r="663">
@@ -8294,7 +8291,7 @@
         <v>16</v>
       </c>
       <c r="C663" t="n">
-        <v>-0.774926525078343</v>
+        <v>-0.512209552142761</v>
       </c>
     </row>
     <row r="664">
@@ -8327,7 +8324,7 @@
         <v>16</v>
       </c>
       <c r="C666" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.22031142616031</v>
       </c>
     </row>
     <row r="667">
@@ -8338,7 +8335,7 @@
         <v>16</v>
       </c>
       <c r="C667" t="n">
-        <v>-0.548543160760232</v>
+        <v>-0.430591343599656</v>
       </c>
     </row>
     <row r="668">
@@ -8349,7 +8346,7 @@
         <v>16</v>
       </c>
       <c r="C668" t="n">
-        <v>-0.275104483953398</v>
+        <v>-0.974879844590673</v>
       </c>
     </row>
     <row r="669">
@@ -8360,7 +8357,7 @@
         <v>16</v>
       </c>
       <c r="C669" t="n">
-        <v>-0.183187700159362</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="670">
@@ -8382,7 +8379,7 @@
         <v>16</v>
       </c>
       <c r="C671" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.122305210168426</v>
       </c>
     </row>
     <row r="672">
@@ -8393,7 +8390,7 @@
         <v>16</v>
       </c>
       <c r="C672" t="n">
-        <v>-0.203729016182871</v>
+        <v>-0.207554404040923</v>
       </c>
     </row>
     <row r="673">
@@ -8404,7 +8401,7 @@
         <v>16</v>
       </c>
       <c r="C673" t="n">
-        <v>-0.344949189321879</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="674">
@@ -8415,7 +8412,7 @@
         <v>16</v>
       </c>
       <c r="C674" t="n">
-        <v>-0.147959183673469</v>
+        <v>-7.9120147483998</v>
       </c>
     </row>
     <row r="675">
@@ -8426,7 +8423,7 @@
         <v>16</v>
       </c>
       <c r="C675" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.826351197473218</v>
       </c>
     </row>
     <row r="676">
@@ -8437,7 +8434,7 @@
         <v>16</v>
       </c>
       <c r="C676" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.355830848045322</v>
       </c>
     </row>
     <row r="677">
@@ -8448,7 +8445,7 @@
         <v>16</v>
       </c>
       <c r="C677" t="n">
-        <v>-0.344357364219139</v>
+        <v>-0.667708617111835</v>
       </c>
     </row>
     <row r="678">
@@ -8459,7 +8456,7 @@
         <v>16</v>
       </c>
       <c r="C678" t="n">
-        <v>-0.399699500649571</v>
+        <v>-2.82683518193394</v>
       </c>
     </row>
     <row r="679">
@@ -8481,7 +8478,7 @@
         <v>16</v>
       </c>
       <c r="C680" t="n">
-        <v>-0.166425787239487</v>
+        <v>-0.370816909774234</v>
       </c>
     </row>
     <row r="681">
@@ -8492,7 +8489,7 @@
         <v>16</v>
       </c>
       <c r="C681" t="n">
-        <v>-1.98273111825228</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="682">
@@ -8503,7 +8500,7 @@
         <v>16</v>
       </c>
       <c r="C682" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.177664474700503</v>
       </c>
     </row>
     <row r="683">
@@ -8514,7 +8511,7 @@
         <v>16</v>
       </c>
       <c r="C683" t="n">
-        <v>-0.25562144597609</v>
+        <v>-0.0404517974751106</v>
       </c>
     </row>
     <row r="684">
@@ -8525,7 +8522,7 @@
         <v>16</v>
       </c>
       <c r="C684" t="n">
-        <v>-0.166576159211986</v>
+        <v>-0.212111820405761</v>
       </c>
     </row>
     <row r="685">
@@ -8536,7 +8533,7 @@
         <v>16</v>
       </c>
       <c r="C685" t="n">
-        <v>-0.799483423687868</v>
+        <v>-0.311902032520417</v>
       </c>
     </row>
     <row r="686">
@@ -8547,7 +8544,7 @@
         <v>16</v>
       </c>
       <c r="C686" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.297270169180504</v>
       </c>
     </row>
     <row r="687">
@@ -8558,7 +8555,7 @@
         <v>16</v>
       </c>
       <c r="C687" t="n">
-        <v>-0.147661418347254</v>
+        <v>-0.156941479983974</v>
       </c>
     </row>
     <row r="688">
@@ -8569,7 +8566,7 @@
         <v>16</v>
       </c>
       <c r="C688" t="n">
-        <v>-0.422168081658836</v>
+        <v>-3.58164920852504</v>
       </c>
     </row>
     <row r="689">
@@ -8580,7 +8577,7 @@
         <v>16</v>
       </c>
       <c r="C689" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.43236986356898</v>
       </c>
     </row>
     <row r="690">
@@ -8591,7 +8588,7 @@
         <v>16</v>
       </c>
       <c r="C690" t="n">
-        <v>-0.89314799593687</v>
+        <v>-0.296964966149398</v>
       </c>
     </row>
     <row r="691">
@@ -8602,7 +8599,7 @@
         <v>16</v>
       </c>
       <c r="C691" t="n">
-        <v>-2.08223279772791</v>
+        <v>-0.428565845286919</v>
       </c>
     </row>
     <row r="692">
@@ -8613,7 +8610,7 @@
         <v>16</v>
       </c>
       <c r="C692" t="n">
-        <v>-0.35351949121629</v>
+        <v>-0.514333064435526</v>
       </c>
     </row>
     <row r="693">
@@ -8646,7 +8643,7 @@
         <v>16</v>
       </c>
       <c r="C695" t="n">
-        <v>-0.168455123221891</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="696">
@@ -8657,7 +8654,7 @@
         <v>16</v>
       </c>
       <c r="C696" t="n">
-        <v>-0.208854181333222</v>
+        <v>-0.249143716365203</v>
       </c>
     </row>
     <row r="697">
@@ -8668,7 +8665,7 @@
         <v>16</v>
       </c>
       <c r="C697" t="n">
-        <v>-0.745032127922396</v>
+        <v>-0.652884313902269</v>
       </c>
     </row>
     <row r="698">
@@ -8679,7 +8676,7 @@
         <v>16</v>
       </c>
       <c r="C698" t="n">
-        <v>-0.57381794644468</v>
+        <v>-0.0267995244579939</v>
       </c>
     </row>
     <row r="699">
@@ -8690,7 +8687,7 @@
         <v>16</v>
       </c>
       <c r="C699" t="n">
-        <v>-0.808497673488477</v>
+        <v>-0.505899483422336</v>
       </c>
     </row>
     <row r="700">
@@ -8723,7 +8720,7 @@
         <v>16</v>
       </c>
       <c r="C702" t="n">
-        <v>-0.253766780653892</v>
+        <v>-0.195336751486746</v>
       </c>
     </row>
     <row r="703">
@@ -8734,7 +8731,7 @@
         <v>16</v>
       </c>
       <c r="C703" t="n">
-        <v>-0.14795918367347</v>
+        <v>-4.93740714864805</v>
       </c>
     </row>
     <row r="704">
@@ -8756,7 +8753,7 @@
         <v>16</v>
       </c>
       <c r="C705" t="n">
-        <v>-0.51216203647642</v>
+        <v>-16.5632793773478</v>
       </c>
     </row>
     <row r="706">
@@ -8767,7 +8764,7 @@
         <v>16</v>
       </c>
       <c r="C706" t="n">
-        <v>-2.58827120899146</v>
+        <v>-0.113233649209652</v>
       </c>
     </row>
     <row r="707">
@@ -8778,7 +8775,7 @@
         <v>16</v>
       </c>
       <c r="C707" t="n">
-        <v>-0.792696730841373</v>
+        <v>-0.0223979148889584</v>
       </c>
     </row>
     <row r="708">
@@ -8789,7 +8786,7 @@
         <v>16</v>
       </c>
       <c r="C708" t="n">
-        <v>-0.427504252226901</v>
+        <v>-0.156838063221614</v>
       </c>
     </row>
     <row r="709">
@@ -8800,7 +8797,7 @@
         <v>16</v>
       </c>
       <c r="C709" t="n">
-        <v>-4.07723852915852</v>
+        <v>-1.29701926994738</v>
       </c>
     </row>
     <row r="710">
@@ -8811,7 +8808,7 @@
         <v>16</v>
       </c>
       <c r="C710" t="n">
-        <v>-0.831470836405109</v>
+        <v>-0.425670267835951</v>
       </c>
     </row>
     <row r="711">
@@ -8822,7 +8819,7 @@
         <v>16</v>
       </c>
       <c r="C711" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.129323211289464</v>
       </c>
     </row>
     <row r="712">
@@ -8833,7 +8830,7 @@
         <v>16</v>
       </c>
       <c r="C712" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.1820309236029</v>
       </c>
     </row>
     <row r="713">
@@ -8877,7 +8874,7 @@
         <v>16</v>
       </c>
       <c r="C716" t="n">
-        <v>-0.462810962447934</v>
+        <v>-0.490082499178592</v>
       </c>
     </row>
     <row r="717">
@@ -8899,7 +8896,7 @@
         <v>16</v>
       </c>
       <c r="C718" t="n">
-        <v>-0.323546436709462</v>
+        <v>-0.029394950892605</v>
       </c>
     </row>
     <row r="719">
@@ -8921,7 +8918,7 @@
         <v>16</v>
       </c>
       <c r="C720" t="n">
-        <v>-5.69874467407918</v>
+        <v>-1.21584634327912</v>
       </c>
     </row>
     <row r="721">
@@ -8932,7 +8929,7 @@
         <v>16</v>
       </c>
       <c r="C721" t="n">
-        <v>-0.399669652389935</v>
+        <v>-0.773154264025638</v>
       </c>
     </row>
     <row r="722">
@@ -8943,7 +8940,7 @@
         <v>16</v>
       </c>
       <c r="C722" t="n">
-        <v>-0.265991334216276</v>
+        <v>-0.450746042578093</v>
       </c>
     </row>
     <row r="723">
@@ -8965,7 +8962,7 @@
         <v>16</v>
       </c>
       <c r="C724" t="n">
-        <v>-0.14795918367347</v>
+        <v>-3.6519047089296</v>
       </c>
     </row>
     <row r="725">
@@ -8976,7 +8973,7 @@
         <v>16</v>
       </c>
       <c r="C725" t="n">
-        <v>-0.191732602767699</v>
+        <v>-0.0371544159133739</v>
       </c>
     </row>
     <row r="726">
@@ -8987,7 +8984,7 @@
         <v>16</v>
       </c>
       <c r="C726" t="n">
-        <v>-0.218745885779348</v>
+        <v>-0.20572267655963</v>
       </c>
     </row>
     <row r="727">
@@ -9009,7 +9006,7 @@
         <v>16</v>
       </c>
       <c r="C728" t="n">
-        <v>-0.581002077770974</v>
+        <v>-0.675132055191014</v>
       </c>
     </row>
     <row r="729">
@@ -9020,7 +9017,7 @@
         <v>16</v>
       </c>
       <c r="C729" t="n">
-        <v>-0.249448571108166</v>
+        <v>-0.321789959642762</v>
       </c>
     </row>
     <row r="730">
@@ -9031,7 +9028,7 @@
         <v>16</v>
       </c>
       <c r="C730" t="n">
-        <v>0.549773282548502</v>
+        <v>0.684242444207181</v>
       </c>
     </row>
     <row r="731">
@@ -9042,7 +9039,7 @@
         <v>16</v>
       </c>
       <c r="C731" t="n">
-        <v>-0.147959183673469</v>
+        <v>-14.8039476688024</v>
       </c>
     </row>
     <row r="732">
@@ -9053,7 +9050,7 @@
         <v>16</v>
       </c>
       <c r="C732" t="n">
-        <v>-0.147959183673469</v>
+        <v>-2.67852906675139</v>
       </c>
     </row>
     <row r="733">
@@ -9075,7 +9072,7 @@
         <v>16</v>
       </c>
       <c r="C734" t="n">
-        <v>-0.147959183673469</v>
+        <v>-25.8180048660856</v>
       </c>
     </row>
     <row r="735">
@@ -9086,7 +9083,7 @@
         <v>16</v>
       </c>
       <c r="C735" t="n">
-        <v>-0.373591641768227</v>
+        <v>-0.412470992884515</v>
       </c>
     </row>
     <row r="736">
@@ -9108,7 +9105,7 @@
         <v>16</v>
       </c>
       <c r="C737" t="n">
-        <v>-1.60058353486172</v>
+        <v>-0.275014221501264</v>
       </c>
     </row>
     <row r="738">
@@ -9119,7 +9116,7 @@
         <v>16</v>
       </c>
       <c r="C738" t="n">
-        <v>-0.501771218719754</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="739">
@@ -9130,7 +9127,7 @@
         <v>16</v>
       </c>
       <c r="C739" t="n">
-        <v>-0.14795918367347</v>
+        <v>-5.75567759499019</v>
       </c>
     </row>
     <row r="740">
@@ -9196,7 +9193,7 @@
         <v>16</v>
       </c>
       <c r="C745" t="n">
-        <v>0.0340663855676001</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="746">
@@ -9207,7 +9204,7 @@
         <v>16</v>
       </c>
       <c r="C746" t="n">
-        <v>-0.490261664956339</v>
+        <v>-0.373731523442074</v>
       </c>
     </row>
     <row r="747">
@@ -9229,7 +9226,7 @@
         <v>16</v>
       </c>
       <c r="C748" t="n">
-        <v>-0.405827789808213</v>
+        <v>-0.250837501859454</v>
       </c>
     </row>
     <row r="749">
@@ -9240,7 +9237,7 @@
         <v>16</v>
       </c>
       <c r="C749" t="n">
-        <v>-0.345999517933908</v>
+        <v>-0.29856619479475</v>
       </c>
     </row>
     <row r="750">
@@ -9251,7 +9248,7 @@
         <v>16</v>
       </c>
       <c r="C750" t="n">
-        <v>-0.162489320214274</v>
+        <v>-0.204628753608664</v>
       </c>
     </row>
     <row r="751">
@@ -9262,7 +9259,7 @@
         <v>16</v>
       </c>
       <c r="C751" t="n">
-        <v>-0.588191490303634</v>
+        <v>0.800771472673544</v>
       </c>
     </row>
     <row r="752">
@@ -9273,7 +9270,7 @@
         <v>16</v>
       </c>
       <c r="C752" t="n">
-        <v>-0.64885550158803</v>
+        <v>-2.18205811259467</v>
       </c>
     </row>
     <row r="753">
@@ -9295,7 +9292,7 @@
         <v>16</v>
       </c>
       <c r="C754" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.676659476577339</v>
       </c>
     </row>
     <row r="755">
@@ -9306,7 +9303,7 @@
         <v>16</v>
       </c>
       <c r="C755" t="n">
-        <v>-0.187592857535511</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="756">
@@ -9317,7 +9314,7 @@
         <v>16</v>
       </c>
       <c r="C756" t="n">
-        <v>-1.46129003365615</v>
+        <v>-0.250268792100381</v>
       </c>
     </row>
     <row r="757">
@@ -9328,7 +9325,7 @@
         <v>16</v>
       </c>
       <c r="C757" t="n">
-        <v>-0.386769850461454</v>
+        <v>-0.921974030762859</v>
       </c>
     </row>
     <row r="758">
@@ -9339,7 +9336,7 @@
         <v>16</v>
       </c>
       <c r="C758" t="n">
-        <v>-1.49996458932729</v>
+        <v>-0.401239163164129</v>
       </c>
     </row>
     <row r="759">
@@ -9350,7 +9347,7 @@
         <v>16</v>
       </c>
       <c r="C759" t="n">
-        <v>-0.224206239930989</v>
+        <v>-0.426496111107865</v>
       </c>
     </row>
     <row r="760">
@@ -9361,7 +9358,7 @@
         <v>16</v>
       </c>
       <c r="C760" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.134894684114795</v>
       </c>
     </row>
     <row r="761">
@@ -9383,7 +9380,7 @@
         <v>16</v>
       </c>
       <c r="C762" t="n">
-        <v>-0.445043052544346</v>
+        <v>-0.279208834300531</v>
       </c>
     </row>
     <row r="763">
@@ -9394,7 +9391,7 @@
         <v>16</v>
       </c>
       <c r="C763" t="n">
-        <v>-0.512243871632144</v>
+        <v>0.031274526517078</v>
       </c>
     </row>
     <row r="764">
@@ -9405,7 +9402,7 @@
         <v>16</v>
       </c>
       <c r="C764" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.387759591012103</v>
       </c>
     </row>
     <row r="765">
@@ -9427,7 +9424,7 @@
         <v>16</v>
       </c>
       <c r="C766" t="n">
-        <v>-0.371551292210688</v>
+        <v>-0.402973135010863</v>
       </c>
     </row>
     <row r="767">
@@ -9438,7 +9435,7 @@
         <v>16</v>
       </c>
       <c r="C767" t="n">
-        <v>-0.21689594930555</v>
+        <v>-14.5319676836102</v>
       </c>
     </row>
     <row r="768">
@@ -9449,7 +9446,7 @@
         <v>16</v>
       </c>
       <c r="C768" t="n">
-        <v>-0.119754134941247</v>
+        <v>-0.132323835482259</v>
       </c>
     </row>
     <row r="769">
@@ -9460,7 +9457,7 @@
         <v>16</v>
       </c>
       <c r="C769" t="n">
-        <v>-2.43270683796415</v>
+        <v>-2.07855770487432</v>
       </c>
     </row>
     <row r="770">
@@ -9482,7 +9479,7 @@
         <v>16</v>
       </c>
       <c r="C771" t="n">
-        <v>-0.544993578337441</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="772">
@@ -9493,7 +9490,7 @@
         <v>16</v>
       </c>
       <c r="C772" t="n">
-        <v>0.337807945567038</v>
+        <v>-0.608321383607434</v>
       </c>
     </row>
     <row r="773">
@@ -9504,7 +9501,7 @@
         <v>16</v>
       </c>
       <c r="C773" t="n">
-        <v>-0.269359111398635</v>
+        <v>-0.240685842093938</v>
       </c>
     </row>
     <row r="774">
@@ -9537,7 +9534,7 @@
         <v>16</v>
       </c>
       <c r="C776" t="n">
-        <v>-0.473622769940898</v>
+        <v>-1.87991693482266</v>
       </c>
     </row>
     <row r="777">
@@ -9548,7 +9545,7 @@
         <v>16</v>
       </c>
       <c r="C777" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.33400268696701</v>
       </c>
     </row>
     <row r="778">
@@ -9559,7 +9556,7 @@
         <v>16</v>
       </c>
       <c r="C778" t="n">
-        <v>-0.144812068504585</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="779">
@@ -9570,7 +9567,7 @@
         <v>16</v>
       </c>
       <c r="C779" t="n">
-        <v>0.158142409473155</v>
+        <v>0.0263580581272775</v>
       </c>
     </row>
     <row r="780">
@@ -9581,7 +9578,7 @@
         <v>16</v>
       </c>
       <c r="C780" t="n">
-        <v>-0.46588023967544</v>
+        <v>-0.265823325145732</v>
       </c>
     </row>
     <row r="781">
@@ -9592,7 +9589,7 @@
         <v>16</v>
       </c>
       <c r="C781" t="n">
-        <v>-0.124247788621025</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="782">
@@ -9625,7 +9622,7 @@
         <v>16</v>
       </c>
       <c r="C784" t="n">
-        <v>-0.206173014271072</v>
+        <v>-0.19225411233086</v>
       </c>
     </row>
     <row r="785">
@@ -9636,7 +9633,7 @@
         <v>16</v>
       </c>
       <c r="C785" t="n">
-        <v>-0.652276440787884</v>
+        <v>-0.536307656049944</v>
       </c>
     </row>
     <row r="786">
@@ -9647,7 +9644,7 @@
         <v>16</v>
       </c>
       <c r="C786" t="n">
-        <v>-0.146865955115545</v>
+        <v>-0.103154522705191</v>
       </c>
     </row>
     <row r="787">
@@ -9658,7 +9655,7 @@
         <v>16</v>
       </c>
       <c r="C787" t="n">
-        <v>-0.374491187015196</v>
+        <v>-0.44354550305851</v>
       </c>
     </row>
     <row r="788">
@@ -9669,7 +9666,7 @@
         <v>16</v>
       </c>
       <c r="C788" t="n">
-        <v>-0.537125714503732</v>
+        <v>-0.230277808556327</v>
       </c>
     </row>
     <row r="789">
@@ -9680,7 +9677,7 @@
         <v>16</v>
       </c>
       <c r="C789" t="n">
-        <v>-0.63596977015033</v>
+        <v>-0.37148026755865</v>
       </c>
     </row>
     <row r="790">
@@ -9691,7 +9688,7 @@
         <v>16</v>
       </c>
       <c r="C790" t="n">
-        <v>-0.227430565355829</v>
+        <v>-0.217468915876712</v>
       </c>
     </row>
     <row r="791">
@@ -9713,7 +9710,7 @@
         <v>16</v>
       </c>
       <c r="C792" t="n">
-        <v>-0.186750351442142</v>
+        <v>-0.16558824219664</v>
       </c>
     </row>
     <row r="793">
@@ -9724,7 +9721,7 @@
         <v>16</v>
       </c>
       <c r="C793" t="n">
-        <v>-0.768373689633352</v>
+        <v>-0.900495942298557</v>
       </c>
     </row>
     <row r="794">
@@ -9735,7 +9732,7 @@
         <v>16</v>
       </c>
       <c r="C794" t="n">
-        <v>-1.07100839651175</v>
+        <v>-0.797257266750119</v>
       </c>
     </row>
     <row r="795">
@@ -9746,7 +9743,7 @@
         <v>16</v>
       </c>
       <c r="C795" t="n">
-        <v>-0.87742209399807</v>
+        <v>-1.27272664264539</v>
       </c>
     </row>
     <row r="796">
@@ -9757,7 +9754,7 @@
         <v>16</v>
       </c>
       <c r="C796" t="n">
-        <v>-0.650871210240899</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="797">
@@ -9768,7 +9765,7 @@
         <v>16</v>
       </c>
       <c r="C797" t="n">
-        <v>-0.781302314180149</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="798">
@@ -9779,7 +9776,7 @@
         <v>16</v>
       </c>
       <c r="C798" t="n">
-        <v>-0.869222750541393</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="799">
@@ -9812,7 +9809,7 @@
         <v>16</v>
       </c>
       <c r="C801" t="n">
-        <v>-0.158969210729809</v>
+        <v>-0.676705216560042</v>
       </c>
     </row>
     <row r="802">
@@ -9823,7 +9820,7 @@
         <v>16</v>
       </c>
       <c r="C802" t="n">
-        <v>-0.195122206637826</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="803">
@@ -9834,7 +9831,7 @@
         <v>16</v>
       </c>
       <c r="C803" t="n">
-        <v>-0.20306450710671</v>
+        <v>-0.213537031488956</v>
       </c>
     </row>
     <row r="804">
@@ -9845,7 +9842,7 @@
         <v>16</v>
       </c>
       <c r="C804" t="n">
-        <v>-0.803606406473956</v>
+        <v>-0.811372466522072</v>
       </c>
     </row>
     <row r="805">
@@ -9878,7 +9875,7 @@
         <v>16</v>
       </c>
       <c r="C807" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.568699921584224</v>
       </c>
     </row>
     <row r="808">
@@ -9889,7 +9886,7 @@
         <v>16</v>
       </c>
       <c r="C808" t="n">
-        <v>0.348012609701177</v>
+        <v>0.232064377226946</v>
       </c>
     </row>
     <row r="809">
@@ -9900,7 +9897,7 @@
         <v>16</v>
       </c>
       <c r="C809" t="n">
-        <v>-0.240093603315068</v>
+        <v>-0.246463336036121</v>
       </c>
     </row>
     <row r="810">
@@ -9922,7 +9919,7 @@
         <v>16</v>
       </c>
       <c r="C811" t="n">
-        <v>-0.220097652633231</v>
+        <v>-0.559829393818986</v>
       </c>
     </row>
     <row r="812">
@@ -9933,7 +9930,7 @@
         <v>16</v>
       </c>
       <c r="C812" t="n">
-        <v>-0.331724269353282</v>
+        <v>0.214847013540754</v>
       </c>
     </row>
     <row r="813">
@@ -9955,7 +9952,7 @@
         <v>16</v>
       </c>
       <c r="C814" t="n">
-        <v>-0.44502051997188</v>
+        <v>-1.21711060549574</v>
       </c>
     </row>
     <row r="815">
@@ -9966,7 +9963,7 @@
         <v>16</v>
       </c>
       <c r="C815" t="n">
-        <v>-0.147959183673469</v>
+        <v>-3.91198470579373</v>
       </c>
     </row>
     <row r="816">
@@ -9977,7 +9974,7 @@
         <v>16</v>
       </c>
       <c r="C816" t="n">
-        <v>-0.0838833307153815</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="817">
@@ -9999,7 +9996,7 @@
         <v>16</v>
       </c>
       <c r="C818" t="n">
-        <v>-0.147959183673469</v>
+        <v>0.887506205044813</v>
       </c>
     </row>
     <row r="819">
@@ -10010,7 +10007,7 @@
         <v>16</v>
       </c>
       <c r="C819" t="n">
-        <v>0.212976756339753</v>
+        <v>-0.0479510890123589</v>
       </c>
     </row>
     <row r="820">
@@ -10021,7 +10018,7 @@
         <v>16</v>
       </c>
       <c r="C820" t="n">
-        <v>0.242570469150973</v>
+        <v>0.237183401243853</v>
       </c>
     </row>
     <row r="821">
@@ -10032,7 +10029,7 @@
         <v>16</v>
       </c>
       <c r="C821" t="n">
-        <v>-0.411623988058352</v>
+        <v>-0.636110669503676</v>
       </c>
     </row>
     <row r="822">
@@ -10043,7 +10040,7 @@
         <v>16</v>
       </c>
       <c r="C822" t="n">
-        <v>-0.179327987639422</v>
+        <v>-0.17443391522724</v>
       </c>
     </row>
     <row r="823">
@@ -10076,7 +10073,7 @@
         <v>16</v>
       </c>
       <c r="C825" t="n">
-        <v>-0.427267386097637</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="826">
@@ -10087,7 +10084,7 @@
         <v>16</v>
       </c>
       <c r="C826" t="n">
-        <v>-0.184400128649524</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="827">
@@ -10109,7 +10106,7 @@
         <v>16</v>
       </c>
       <c r="C828" t="n">
-        <v>-0.472228981698103</v>
+        <v>-0.400742149526132</v>
       </c>
     </row>
     <row r="829">
@@ -10120,7 +10117,7 @@
         <v>16</v>
       </c>
       <c r="C829" t="n">
-        <v>-0.685273983099998</v>
+        <v>-2.8829329143256</v>
       </c>
     </row>
     <row r="830">
@@ -10131,7 +10128,7 @@
         <v>16</v>
       </c>
       <c r="C830" t="n">
-        <v>-0.187997312483523</v>
+        <v>-0.630031632857853</v>
       </c>
     </row>
     <row r="831">
@@ -10142,7 +10139,7 @@
         <v>16</v>
       </c>
       <c r="C831" t="n">
-        <v>-0.25681559966517</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="832">
@@ -10153,7 +10150,7 @@
         <v>16</v>
       </c>
       <c r="C832" t="n">
-        <v>-1.06537136297836</v>
+        <v>-4.32484786778972</v>
       </c>
     </row>
     <row r="833">
@@ -10164,7 +10161,7 @@
         <v>16</v>
       </c>
       <c r="C833" t="n">
-        <v>-0.1205061258609</v>
+        <v>-1.53618828544234</v>
       </c>
     </row>
     <row r="834">
@@ -10186,7 +10183,7 @@
         <v>16</v>
       </c>
       <c r="C835" t="n">
-        <v>-0.161088195775027</v>
+        <v>-0.489576485247522</v>
       </c>
     </row>
     <row r="836">
@@ -10197,7 +10194,7 @@
         <v>16</v>
       </c>
       <c r="C836" t="n">
-        <v>-0.346804504427277</v>
+        <v>-0.130522455744303</v>
       </c>
     </row>
     <row r="837">
@@ -10208,7 +10205,7 @@
         <v>16</v>
       </c>
       <c r="C837" t="n">
-        <v>-0.902909951154954</v>
+        <v>-0.184351984879691</v>
       </c>
     </row>
     <row r="838">
@@ -10219,7 +10216,7 @@
         <v>16</v>
       </c>
       <c r="C838" t="n">
-        <v>-0.203152821678272</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="839">
@@ -10230,7 +10227,7 @@
         <v>16</v>
       </c>
       <c r="C839" t="n">
-        <v>-0.833055184983864</v>
+        <v>-0.177316271903541</v>
       </c>
     </row>
     <row r="840">
@@ -10274,7 +10271,7 @@
         <v>16</v>
       </c>
       <c r="C843" t="n">
-        <v>-3.46224999904232</v>
+        <v>-0.173421564128493</v>
       </c>
     </row>
     <row r="844">
@@ -10285,7 +10282,7 @@
         <v>16</v>
       </c>
       <c r="C844" t="n">
-        <v>-0.431364949876516</v>
+        <v>-0.673506788695627</v>
       </c>
     </row>
     <row r="845">
@@ -10296,7 +10293,7 @@
         <v>16</v>
       </c>
       <c r="C845" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.564367773709628</v>
       </c>
     </row>
     <row r="846">
@@ -10307,7 +10304,7 @@
         <v>16</v>
       </c>
       <c r="C846" t="n">
-        <v>0.102128619126272</v>
+        <v>-0.479034957015549</v>
       </c>
     </row>
     <row r="847">
@@ -10318,7 +10315,7 @@
         <v>16</v>
       </c>
       <c r="C847" t="n">
-        <v>-0.783860224526059</v>
+        <v>-0.373829635480192</v>
       </c>
     </row>
     <row r="848">
@@ -10329,7 +10326,7 @@
         <v>16</v>
       </c>
       <c r="C848" t="n">
-        <v>-0.187958499397961</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="849">
@@ -10340,7 +10337,7 @@
         <v>16</v>
       </c>
       <c r="C849" t="n">
-        <v>-0.160678203696113</v>
+        <v>-1.06924668502854</v>
       </c>
     </row>
     <row r="850">
@@ -10362,7 +10359,7 @@
         <v>16</v>
       </c>
       <c r="C851" t="n">
-        <v>0.0421861726609746</v>
+        <v>0.19408513448704</v>
       </c>
     </row>
     <row r="852">
@@ -10373,7 +10370,7 @@
         <v>16</v>
       </c>
       <c r="C852" t="n">
-        <v>-0.450530916869752</v>
+        <v>-0.348159727075916</v>
       </c>
     </row>
     <row r="853">
@@ -10395,7 +10392,7 @@
         <v>16</v>
       </c>
       <c r="C854" t="n">
-        <v>-0.917829672292644</v>
+        <v>-1.55180095359131</v>
       </c>
     </row>
     <row r="855">
@@ -10406,7 +10403,7 @@
         <v>16</v>
       </c>
       <c r="C855" t="n">
-        <v>-0.572741047243782</v>
+        <v>-0.211900830739544</v>
       </c>
     </row>
     <row r="856">
@@ -10417,7 +10414,7 @@
         <v>16</v>
       </c>
       <c r="C856" t="n">
-        <v>-1.56112692953479</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="857">
@@ -10428,7 +10425,7 @@
         <v>16</v>
       </c>
       <c r="C857" t="n">
-        <v>-0.23077127173405</v>
+        <v>-0.327617454151907</v>
       </c>
     </row>
     <row r="858">
@@ -10450,7 +10447,7 @@
         <v>16</v>
       </c>
       <c r="C859" t="n">
-        <v>-0.204040032938931</v>
+        <v>-0.185918488926181</v>
       </c>
     </row>
     <row r="860">
@@ -10461,7 +10458,7 @@
         <v>16</v>
       </c>
       <c r="C860" t="n">
-        <v>-0.177819640817899</v>
+        <v>-0.179542081935616</v>
       </c>
     </row>
     <row r="861">
@@ -10472,7 +10469,7 @@
         <v>16</v>
       </c>
       <c r="C861" t="n">
-        <v>-0.147959183673469</v>
+        <v>-2.15345446640055</v>
       </c>
     </row>
     <row r="862">
@@ -10494,7 +10491,7 @@
         <v>16</v>
       </c>
       <c r="C863" t="n">
-        <v>-0.718605309431446</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="864">
@@ -10505,7 +10502,7 @@
         <v>16</v>
       </c>
       <c r="C864" t="n">
-        <v>-0.14795918367347</v>
+        <v>-3.28584135006694</v>
       </c>
     </row>
     <row r="865">
@@ -10516,7 +10513,7 @@
         <v>16</v>
       </c>
       <c r="C865" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.728085320718954</v>
       </c>
     </row>
     <row r="866">
@@ -10538,7 +10535,7 @@
         <v>16</v>
       </c>
       <c r="C867" t="n">
-        <v>0.44046446698977</v>
+        <v>-0.112994570586344</v>
       </c>
     </row>
     <row r="868">
@@ -10549,7 +10546,7 @@
         <v>16</v>
       </c>
       <c r="C868" t="n">
-        <v>-0.450064901089312</v>
+        <v>0.417868704602985</v>
       </c>
     </row>
     <row r="869">
@@ -10560,7 +10557,7 @@
         <v>16</v>
       </c>
       <c r="C869" t="n">
-        <v>-0.942340556185405</v>
+        <v>-0.254860973307854</v>
       </c>
     </row>
     <row r="870">
@@ -10571,7 +10568,7 @@
         <v>16</v>
       </c>
       <c r="C870" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.448887002751464</v>
       </c>
     </row>
     <row r="871">
@@ -10593,7 +10590,7 @@
         <v>16</v>
       </c>
       <c r="C872" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.463676222871622</v>
       </c>
     </row>
     <row r="873">
@@ -10626,7 +10623,7 @@
         <v>16</v>
       </c>
       <c r="C875" t="n">
-        <v>-0.289939031261878</v>
+        <v>-1.01338829434236</v>
       </c>
     </row>
     <row r="876">
@@ -10637,7 +10634,7 @@
         <v>16</v>
       </c>
       <c r="C876" t="n">
-        <v>-0.34219027198621</v>
+        <v>-0.212353094031669</v>
       </c>
     </row>
     <row r="877">
@@ -10648,7 +10645,7 @@
         <v>16</v>
       </c>
       <c r="C877" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.19998578098516</v>
       </c>
     </row>
     <row r="878">
@@ -10659,7 +10656,7 @@
         <v>16</v>
       </c>
       <c r="C878" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.810794022347065</v>
       </c>
     </row>
     <row r="879">
@@ -10670,7 +10667,7 @@
         <v>16</v>
       </c>
       <c r="C879" t="n">
-        <v>-1.58068087569728</v>
+        <v>-0.154720677388646</v>
       </c>
     </row>
     <row r="880">
@@ -10681,7 +10678,7 @@
         <v>16</v>
       </c>
       <c r="C880" t="n">
-        <v>-0.147106615938533</v>
+        <v>-0.228222051212237</v>
       </c>
     </row>
     <row r="881">
@@ -10692,7 +10689,7 @@
         <v>16</v>
       </c>
       <c r="C881" t="n">
-        <v>-0.255029835726458</v>
+        <v>-0.599623190689466</v>
       </c>
     </row>
     <row r="882">
@@ -10703,7 +10700,7 @@
         <v>16</v>
       </c>
       <c r="C882" t="n">
-        <v>-0.267341743376404</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="883">
@@ -10725,7 +10722,7 @@
         <v>16</v>
       </c>
       <c r="C884" t="n">
-        <v>-0.819880424055824</v>
+        <v>-31.7810126347739</v>
       </c>
     </row>
     <row r="885">
@@ -10736,7 +10733,7 @@
         <v>16</v>
       </c>
       <c r="C885" t="n">
-        <v>-0.432163839043723</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="886">
@@ -10747,7 +10744,7 @@
         <v>16</v>
       </c>
       <c r="C886" t="n">
-        <v>-1.06390558554499</v>
+        <v>-0.153235457706695</v>
       </c>
     </row>
     <row r="887">
@@ -10758,7 +10755,7 @@
         <v>16</v>
       </c>
       <c r="C887" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.24366744306555</v>
       </c>
     </row>
     <row r="888">
@@ -10769,7 +10766,7 @@
         <v>16</v>
       </c>
       <c r="C888" t="n">
-        <v>-0.343799508251566</v>
+        <v>-0.390428504289267</v>
       </c>
     </row>
     <row r="889">
@@ -10780,7 +10777,7 @@
         <v>16</v>
       </c>
       <c r="C889" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.982615470254166</v>
       </c>
     </row>
     <row r="890">
@@ -10802,7 +10799,7 @@
         <v>16</v>
       </c>
       <c r="C891" t="n">
-        <v>-0.237015621313911</v>
+        <v>-0.42010586608241</v>
       </c>
     </row>
     <row r="892">
@@ -10813,7 +10810,7 @@
         <v>16</v>
       </c>
       <c r="C892" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.541854143479975</v>
       </c>
     </row>
     <row r="893">
@@ -10824,7 +10821,7 @@
         <v>16</v>
       </c>
       <c r="C893" t="n">
-        <v>-0.226365673416853</v>
+        <v>-0.693526439553385</v>
       </c>
     </row>
     <row r="894">
@@ -10835,7 +10832,7 @@
         <v>16</v>
       </c>
       <c r="C894" t="n">
-        <v>-0.17767638702509</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="895">
@@ -10846,7 +10843,7 @@
         <v>16</v>
       </c>
       <c r="C895" t="n">
-        <v>-0.307278108182758</v>
+        <v>-0.571150085091619</v>
       </c>
     </row>
     <row r="896">
@@ -10857,7 +10854,7 @@
         <v>16</v>
       </c>
       <c r="C896" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.347007645973872</v>
       </c>
     </row>
     <row r="897">
@@ -10879,7 +10876,7 @@
         <v>16</v>
       </c>
       <c r="C898" t="n">
-        <v>-0.172934186890651</v>
+        <v>-0.369100165600414</v>
       </c>
     </row>
     <row r="899">
@@ -10890,7 +10887,7 @@
         <v>16</v>
       </c>
       <c r="C899" t="n">
-        <v>-0.359037864343267</v>
+        <v>-0.517008068749244</v>
       </c>
     </row>
     <row r="900">
@@ -10901,7 +10898,7 @@
         <v>16</v>
       </c>
       <c r="C900" t="n">
-        <v>-0.180762489726838</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="901">
@@ -10923,7 +10920,7 @@
         <v>16</v>
       </c>
       <c r="C902" t="n">
-        <v>-0.368249581363559</v>
+        <v>-1.47200283710528</v>
       </c>
     </row>
     <row r="903">
@@ -10934,7 +10931,7 @@
         <v>16</v>
       </c>
       <c r="C903" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.685977518640898</v>
       </c>
     </row>
     <row r="904">
@@ -10945,7 +10942,7 @@
         <v>16</v>
       </c>
       <c r="C904" t="n">
-        <v>0.0017862796420971</v>
+        <v>-0.0157317076455072</v>
       </c>
     </row>
     <row r="905">
@@ -10967,7 +10964,7 @@
         <v>16</v>
       </c>
       <c r="C906" t="n">
-        <v>-0.329298265866124</v>
+        <v>-0.23821121742184</v>
       </c>
     </row>
     <row r="907">
@@ -10989,7 +10986,7 @@
         <v>16</v>
       </c>
       <c r="C908" t="n">
-        <v>-0.287727335284196</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="909">
@@ -11000,7 +10997,7 @@
         <v>16</v>
       </c>
       <c r="C909" t="n">
-        <v>-0.683885611939028</v>
+        <v>-0.159692216982136</v>
       </c>
     </row>
     <row r="910">
@@ -11011,7 +11008,7 @@
         <v>16</v>
       </c>
       <c r="C910" t="n">
-        <v>-0.635552847418489</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="911">
@@ -11022,7 +11019,7 @@
         <v>16</v>
       </c>
       <c r="C911" t="n">
-        <v>-0.205086595157349</v>
+        <v>-0.209058111237796</v>
       </c>
     </row>
     <row r="912">
@@ -11033,7 +11030,7 @@
         <v>16</v>
       </c>
       <c r="C912" t="n">
-        <v>-0.326783044889259</v>
+        <v>-1.13970036935354</v>
       </c>
     </row>
     <row r="913">
@@ -11044,7 +11041,7 @@
         <v>16</v>
       </c>
       <c r="C913" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.488291750970074</v>
       </c>
     </row>
     <row r="914">
@@ -11055,7 +11052,7 @@
         <v>16</v>
       </c>
       <c r="C914" t="n">
-        <v>-1.19991300979619</v>
+        <v>-0.778964580343438</v>
       </c>
     </row>
     <row r="915">
@@ -11066,7 +11063,7 @@
         <v>16</v>
       </c>
       <c r="C915" t="n">
-        <v>-0.18138582355708</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="916">
@@ -11077,7 +11074,7 @@
         <v>16</v>
       </c>
       <c r="C916" t="n">
-        <v>-0.784540297325275</v>
+        <v>-1.78791433564161</v>
       </c>
     </row>
     <row r="917">
@@ -11088,7 +11085,7 @@
         <v>16</v>
       </c>
       <c r="C917" t="n">
-        <v>-1.74955484293722</v>
+        <v>-0.17646846035271</v>
       </c>
     </row>
     <row r="918">
@@ -11099,7 +11096,7 @@
         <v>16</v>
       </c>
       <c r="C918" t="n">
-        <v>-0.759849013253343</v>
+        <v>-0.970052997505928</v>
       </c>
     </row>
     <row r="919">
@@ -11110,7 +11107,7 @@
         <v>16</v>
       </c>
       <c r="C919" t="n">
-        <v>-0.393061832134632</v>
+        <v>-10.852087894367</v>
       </c>
     </row>
     <row r="920">
@@ -11121,7 +11118,7 @@
         <v>16</v>
       </c>
       <c r="C920" t="n">
-        <v>-0.147959183673469</v>
+        <v>-23.6860661858328</v>
       </c>
     </row>
     <row r="921">
@@ -11143,7 +11140,7 @@
         <v>16</v>
       </c>
       <c r="C922" t="n">
-        <v>-0.498525834044405</v>
+        <v>-0.411100896904694</v>
       </c>
     </row>
     <row r="923">
@@ -11154,7 +11151,7 @@
         <v>16</v>
       </c>
       <c r="C923" t="n">
-        <v>-0.258606671219328</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="924">
@@ -11198,7 +11195,7 @@
         <v>16</v>
       </c>
       <c r="C927" t="n">
-        <v>0.0730593610542775</v>
+        <v>-0.0331508257564708</v>
       </c>
     </row>
     <row r="928">
@@ -11209,7 +11206,7 @@
         <v>16</v>
       </c>
       <c r="C928" t="n">
-        <v>-0.280658627041534</v>
+        <v>-7.47928946979955</v>
       </c>
     </row>
     <row r="929">
@@ -11242,7 +11239,7 @@
         <v>16</v>
       </c>
       <c r="C931" t="n">
-        <v>0.490634529422749</v>
+        <v>-0.151673047091337</v>
       </c>
     </row>
     <row r="932">
@@ -11264,7 +11261,7 @@
         <v>16</v>
       </c>
       <c r="C933" t="n">
-        <v>-0.102608253866142</v>
+        <v>0.0899109310904229</v>
       </c>
     </row>
     <row r="934">
@@ -11275,7 +11272,7 @@
         <v>16</v>
       </c>
       <c r="C934" t="n">
-        <v>-0.258746311851332</v>
+        <v>-0.350675819082591</v>
       </c>
     </row>
     <row r="935">
@@ -11286,7 +11283,7 @@
         <v>16</v>
       </c>
       <c r="C935" t="n">
-        <v>-0.165294829812543</v>
+        <v>-0.19434505314998</v>
       </c>
     </row>
     <row r="936">
@@ -11297,7 +11294,7 @@
         <v>16</v>
       </c>
       <c r="C936" t="n">
-        <v>-0.168839657073742</v>
+        <v>-0.115732196872793</v>
       </c>
     </row>
     <row r="937">
@@ -11308,7 +11305,7 @@
         <v>16</v>
       </c>
       <c r="C937" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.572112729835522</v>
       </c>
     </row>
     <row r="938">
@@ -11319,7 +11316,7 @@
         <v>16</v>
       </c>
       <c r="C938" t="n">
-        <v>0.126670181201126</v>
+        <v>-1.17533748749226</v>
       </c>
     </row>
     <row r="939">
@@ -11341,7 +11338,7 @@
         <v>16</v>
       </c>
       <c r="C940" t="n">
-        <v>-2.9960968203072</v>
+        <v>-1.78235149167191</v>
       </c>
     </row>
     <row r="941">
@@ -11352,7 +11349,7 @@
         <v>16</v>
       </c>
       <c r="C941" t="n">
-        <v>-0.153281982450573</v>
+        <v>-0.116715205585497</v>
       </c>
     </row>
     <row r="942">
@@ -11363,7 +11360,7 @@
         <v>16</v>
       </c>
       <c r="C942" t="n">
-        <v>-0.1205377399465</v>
+        <v>-0.197661405122286</v>
       </c>
     </row>
     <row r="943">
@@ -11374,7 +11371,7 @@
         <v>16</v>
       </c>
       <c r="C943" t="n">
-        <v>-0.71658274329082</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="944">
@@ -11385,7 +11382,7 @@
         <v>16</v>
       </c>
       <c r="C944" t="n">
-        <v>-4.31450041072002</v>
+        <v>-0.693494409665083</v>
       </c>
     </row>
     <row r="945">
@@ -11396,7 +11393,7 @@
         <v>16</v>
       </c>
       <c r="C945" t="n">
-        <v>-1.61446629580197</v>
+        <v>-0.272024029253962</v>
       </c>
     </row>
     <row r="946">
@@ -11418,7 +11415,7 @@
         <v>16</v>
       </c>
       <c r="C947" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.556096525213472</v>
       </c>
     </row>
     <row r="948">
@@ -11429,7 +11426,7 @@
         <v>16</v>
       </c>
       <c r="C948" t="n">
-        <v>-0.380672294271142</v>
+        <v>-0.612242319165228</v>
       </c>
     </row>
     <row r="949">
@@ -11440,7 +11437,7 @@
         <v>16</v>
       </c>
       <c r="C949" t="n">
-        <v>-0.159840639756052</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="950">
@@ -11462,7 +11459,7 @@
         <v>16</v>
       </c>
       <c r="C951" t="n">
-        <v>0.0344176138871674</v>
+        <v>-0.0840703537827479</v>
       </c>
     </row>
     <row r="952">
@@ -11473,7 +11470,7 @@
         <v>16</v>
       </c>
       <c r="C952" t="n">
-        <v>-0.201248572186228</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="953">
@@ -11484,7 +11481,7 @@
         <v>16</v>
       </c>
       <c r="C953" t="n">
-        <v>-0.333711512756353</v>
+        <v>-0.352660129078468</v>
       </c>
     </row>
     <row r="954">
@@ -11506,7 +11503,7 @@
         <v>16</v>
       </c>
       <c r="C955" t="n">
-        <v>-0.446502782686572</v>
+        <v>-0.408216285643404</v>
       </c>
     </row>
     <row r="956">
@@ -11517,7 +11514,7 @@
         <v>16</v>
       </c>
       <c r="C956" t="n">
-        <v>-1.61007999615591</v>
+        <v>-0.500317361161734</v>
       </c>
     </row>
     <row r="957">
@@ -11528,7 +11525,7 @@
         <v>16</v>
       </c>
       <c r="C957" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.0845852184536424</v>
       </c>
     </row>
     <row r="958">
@@ -11539,7 +11536,7 @@
         <v>16</v>
       </c>
       <c r="C958" t="n">
-        <v>-0.715394370299909</v>
+        <v>-0.28526233141629</v>
       </c>
     </row>
     <row r="959">
@@ -11550,7 +11547,7 @@
         <v>16</v>
       </c>
       <c r="C959" t="n">
-        <v>-0.191795762709618</v>
+        <v>0.276320150438324</v>
       </c>
     </row>
     <row r="960">
@@ -11561,7 +11558,7 @@
         <v>16</v>
       </c>
       <c r="C960" t="n">
-        <v>-0.506161939550551</v>
+        <v>-0.291978123942164</v>
       </c>
     </row>
     <row r="961">
@@ -11583,7 +11580,7 @@
         <v>16</v>
       </c>
       <c r="C962" t="n">
-        <v>-0.418110949308578</v>
+        <v>-0.514107429460137</v>
       </c>
     </row>
     <row r="963">
@@ -11605,7 +11602,7 @@
         <v>16</v>
       </c>
       <c r="C964" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.161937023021743</v>
       </c>
     </row>
     <row r="965">
@@ -11616,7 +11613,7 @@
         <v>16</v>
       </c>
       <c r="C965" t="n">
-        <v>-0.483247462814409</v>
+        <v>-0.328095969807812</v>
       </c>
     </row>
     <row r="966">
@@ -11638,7 +11635,7 @@
         <v>16</v>
       </c>
       <c r="C967" t="n">
-        <v>-0.140498025625283</v>
+        <v>-0.150126249635252</v>
       </c>
     </row>
     <row r="968">
@@ -11671,7 +11668,7 @@
         <v>16</v>
       </c>
       <c r="C970" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.16942639231355</v>
       </c>
     </row>
     <row r="971">
@@ -11682,7 +11679,7 @@
         <v>16</v>
       </c>
       <c r="C971" t="n">
-        <v>-0.206806084665708</v>
+        <v>-0.231788478522749</v>
       </c>
     </row>
     <row r="972">
@@ -11693,7 +11690,7 @@
         <v>16</v>
       </c>
       <c r="C972" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.198599056742469</v>
       </c>
     </row>
     <row r="973">
@@ -11704,7 +11701,7 @@
         <v>16</v>
       </c>
       <c r="C973" t="n">
-        <v>-1.31955483243523</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="974">
@@ -11715,7 +11712,7 @@
         <v>16</v>
       </c>
       <c r="C974" t="n">
-        <v>-0.228600230799227</v>
+        <v>-0.902548966225986</v>
       </c>
     </row>
     <row r="975">
@@ -11726,7 +11723,7 @@
         <v>16</v>
       </c>
       <c r="C975" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.597417728084342</v>
       </c>
     </row>
     <row r="976">
@@ -11748,7 +11745,7 @@
         <v>16</v>
       </c>
       <c r="C977" t="n">
-        <v>-0.438935938557039</v>
+        <v>-0.357418003568567</v>
       </c>
     </row>
     <row r="978">
@@ -11759,7 +11756,7 @@
         <v>16</v>
       </c>
       <c r="C978" t="n">
-        <v>-0.823790124057335</v>
+        <v>-0.153397647886526</v>
       </c>
     </row>
     <row r="979">
@@ -11770,7 +11767,7 @@
         <v>16</v>
       </c>
       <c r="C979" t="n">
-        <v>-2.063604188385</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="980">
@@ -11781,7 +11778,7 @@
         <v>16</v>
       </c>
       <c r="C980" t="n">
-        <v>-0.161326179727744</v>
+        <v>-0.160469824878479</v>
       </c>
     </row>
     <row r="981">
@@ -11792,7 +11789,7 @@
         <v>16</v>
       </c>
       <c r="C981" t="n">
-        <v>-0.304898790684272</v>
+        <v>0.281693751110398</v>
       </c>
     </row>
     <row r="982">
@@ -11814,7 +11811,7 @@
         <v>16</v>
       </c>
       <c r="C983" t="n">
-        <v>-0.213060603628604</v>
+        <v>-0.219672142221611</v>
       </c>
     </row>
     <row r="984">
@@ -11825,7 +11822,7 @@
         <v>16</v>
       </c>
       <c r="C984" t="n">
-        <v>-0.177252335444892</v>
+        <v>-0.222971397403218</v>
       </c>
     </row>
     <row r="985">
@@ -11836,7 +11833,7 @@
         <v>16</v>
       </c>
       <c r="C985" t="n">
-        <v>0.00249778625049057</v>
+        <v>-6.76487473753415</v>
       </c>
     </row>
     <row r="986">
@@ -11847,7 +11844,7 @@
         <v>16</v>
       </c>
       <c r="C986" t="n">
-        <v>-0.856024187582498</v>
+        <v>-0.381093214470194</v>
       </c>
     </row>
     <row r="987">
@@ -11858,7 +11855,7 @@
         <v>16</v>
       </c>
       <c r="C987" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.15889497150442</v>
       </c>
     </row>
     <row r="988">
@@ -11869,7 +11866,7 @@
         <v>16</v>
       </c>
       <c r="C988" t="n">
-        <v>0.0859903002457154</v>
+        <v>-0.940996475834329</v>
       </c>
     </row>
     <row r="989">
@@ -11880,7 +11877,7 @@
         <v>16</v>
       </c>
       <c r="C989" t="n">
-        <v>-0.192665794466126</v>
+        <v>-0.776788185516849</v>
       </c>
     </row>
     <row r="990">
@@ -11891,7 +11888,7 @@
         <v>16</v>
       </c>
       <c r="C990" t="n">
-        <v>-0.313096139637281</v>
+        <v>-0.0669780369211996</v>
       </c>
     </row>
     <row r="991">
@@ -11902,7 +11899,7 @@
         <v>16</v>
       </c>
       <c r="C991" t="n">
-        <v>-1.70670149102466</v>
+        <v>-0.608884893521818</v>
       </c>
     </row>
     <row r="992">
@@ -11913,7 +11910,7 @@
         <v>16</v>
       </c>
       <c r="C992" t="n">
-        <v>-2.59694521866719</v>
+        <v>-1.01831548946425</v>
       </c>
     </row>
     <row r="993">
@@ -11924,7 +11921,7 @@
         <v>16</v>
       </c>
       <c r="C993" t="n">
-        <v>-0.285910277376703</v>
+        <v>-0.33700498339881</v>
       </c>
     </row>
     <row r="994">
@@ -11946,7 +11943,7 @@
         <v>16</v>
       </c>
       <c r="C995" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.157573173848645</v>
       </c>
     </row>
     <row r="996">
@@ -11957,7 +11954,7 @@
         <v>16</v>
       </c>
       <c r="C996" t="n">
-        <v>-0.190663104872208</v>
+        <v>-0.0729623477447789</v>
       </c>
     </row>
     <row r="997">
@@ -11968,7 +11965,7 @@
         <v>16</v>
       </c>
       <c r="C997" t="n">
-        <v>-0.430903614204537</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="998">
@@ -11979,7 +11976,7 @@
         <v>16</v>
       </c>
       <c r="C998" t="n">
-        <v>-2.55760875424383</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="999">
@@ -11990,7 +11987,7 @@
         <v>16</v>
       </c>
       <c r="C999" t="n">
-        <v>-1.33220166347683</v>
+        <v>-0.522574887782383</v>
       </c>
     </row>
     <row r="1000">
@@ -12001,7 +11998,7 @@
         <v>16</v>
       </c>
       <c r="C1000" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.149887118404349</v>
       </c>
     </row>
     <row r="1001">
@@ -12023,7 +12020,7 @@
         <v>16</v>
       </c>
       <c r="C1002" t="n">
-        <v>-0.573540983946067</v>
+        <v>-0.947271217456592</v>
       </c>
     </row>
     <row r="1003">
@@ -12034,7 +12031,7 @@
         <v>16</v>
       </c>
       <c r="C1003" t="n">
-        <v>-0.241788849675661</v>
+        <v>-0.226469375704934</v>
       </c>
     </row>
     <row r="1004">
@@ -12045,7 +12042,7 @@
         <v>16</v>
       </c>
       <c r="C1004" t="n">
-        <v>-0.169401927541333</v>
+        <v>-8.79544824607509</v>
       </c>
     </row>
     <row r="1005">
@@ -12056,7 +12053,7 @@
         <v>16</v>
       </c>
       <c r="C1005" t="n">
-        <v>-0.322626319567221</v>
+        <v>-0.35294325308786</v>
       </c>
     </row>
     <row r="1006">
@@ -12067,7 +12064,7 @@
         <v>16</v>
       </c>
       <c r="C1006" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.539997680486975</v>
       </c>
     </row>
     <row r="1007">
@@ -12078,7 +12075,7 @@
         <v>16</v>
       </c>
       <c r="C1007" t="n">
-        <v>-0.435074134280032</v>
+        <v>-0.871176800963981</v>
       </c>
     </row>
     <row r="1008">
@@ -12100,7 +12097,7 @@
         <v>16</v>
       </c>
       <c r="C1009" t="n">
-        <v>-0.462283990523441</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1010">
@@ -12122,7 +12119,7 @@
         <v>16</v>
       </c>
       <c r="C1011" t="n">
-        <v>-0.14022993975239</v>
+        <v>0.101605352757221</v>
       </c>
     </row>
     <row r="1012">
@@ -12144,7 +12141,7 @@
         <v>16</v>
       </c>
       <c r="C1013" t="n">
-        <v>-0.188682260678134</v>
+        <v>-0.209074317874919</v>
       </c>
     </row>
     <row r="1014">
@@ -12155,7 +12152,7 @@
         <v>16</v>
       </c>
       <c r="C1014" t="n">
-        <v>-0.478350753279448</v>
+        <v>-17.7678855061825</v>
       </c>
     </row>
     <row r="1015">
@@ -12166,7 +12163,7 @@
         <v>16</v>
       </c>
       <c r="C1015" t="n">
-        <v>-0.406830027565071</v>
+        <v>-0.180421732154026</v>
       </c>
     </row>
     <row r="1016">
@@ -12177,7 +12174,7 @@
         <v>16</v>
       </c>
       <c r="C1016" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.594894575846888</v>
       </c>
     </row>
     <row r="1017">
@@ -12199,7 +12196,7 @@
         <v>16</v>
       </c>
       <c r="C1018" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.251803556380952</v>
       </c>
     </row>
     <row r="1019">
@@ -12221,7 +12218,7 @@
         <v>16</v>
       </c>
       <c r="C1020" t="n">
-        <v>-0.792794016006207</v>
+        <v>-3.85723703595715</v>
       </c>
     </row>
     <row r="1021">
@@ -12232,7 +12229,7 @@
         <v>16</v>
       </c>
       <c r="C1021" t="n">
-        <v>-1.39956123047792</v>
+        <v>-1.46141405021199</v>
       </c>
     </row>
     <row r="1022">
@@ -12254,7 +12251,7 @@
         <v>16</v>
       </c>
       <c r="C1023" t="n">
-        <v>-0.216704850633416</v>
+        <v>-0.580177250254438</v>
       </c>
     </row>
     <row r="1024">
@@ -12265,7 +12262,7 @@
         <v>16</v>
       </c>
       <c r="C1024" t="n">
-        <v>-0.344839345271796</v>
+        <v>-0.224406348823394</v>
       </c>
     </row>
     <row r="1025">
@@ -12276,7 +12273,7 @@
         <v>16</v>
       </c>
       <c r="C1025" t="n">
-        <v>-0.406740334176785</v>
+        <v>-0.3757207988301</v>
       </c>
     </row>
     <row r="1026">
@@ -12287,7 +12284,7 @@
         <v>16</v>
       </c>
       <c r="C1026" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.674428136714378</v>
       </c>
     </row>
     <row r="1027">
@@ -12298,7 +12295,7 @@
         <v>16</v>
       </c>
       <c r="C1027" t="n">
-        <v>-0.170601953630785</v>
+        <v>-0.187236687279038</v>
       </c>
     </row>
     <row r="1028">
@@ -12342,7 +12339,7 @@
         <v>16</v>
       </c>
       <c r="C1031" t="n">
-        <v>-0.31008508335053</v>
+        <v>-0.606706691461739</v>
       </c>
     </row>
     <row r="1032">
@@ -12353,7 +12350,7 @@
         <v>16</v>
       </c>
       <c r="C1032" t="n">
-        <v>-0.253548154686325</v>
+        <v>-0.153429183752792</v>
       </c>
     </row>
     <row r="1033">
@@ -12364,7 +12361,7 @@
         <v>16</v>
       </c>
       <c r="C1033" t="n">
-        <v>-0.378463384484374</v>
+        <v>-0.433464100872501</v>
       </c>
     </row>
     <row r="1034">
@@ -12375,7 +12372,7 @@
         <v>16</v>
       </c>
       <c r="C1034" t="n">
-        <v>-4.45981797703319</v>
+        <v>-3.34454230598483</v>
       </c>
     </row>
     <row r="1035">
@@ -12397,7 +12394,7 @@
         <v>16</v>
       </c>
       <c r="C1036" t="n">
-        <v>-0.447036123951597</v>
+        <v>-0.321133808744393</v>
       </c>
     </row>
     <row r="1037">
@@ -12408,7 +12405,7 @@
         <v>16</v>
       </c>
       <c r="C1037" t="n">
-        <v>-0.205604557063767</v>
+        <v>-0.704792553525779</v>
       </c>
     </row>
     <row r="1038">
@@ -12430,7 +12427,7 @@
         <v>16</v>
       </c>
       <c r="C1039" t="n">
-        <v>-0.340709052446598</v>
+        <v>-0.391849255981369</v>
       </c>
     </row>
     <row r="1040">
@@ -12452,7 +12449,7 @@
         <v>16</v>
       </c>
       <c r="C1041" t="n">
-        <v>-0.197164294906639</v>
+        <v>-0.226908583365339</v>
       </c>
     </row>
     <row r="1042">
@@ -12463,7 +12460,7 @@
         <v>16</v>
       </c>
       <c r="C1042" t="n">
-        <v>-0.354035952297336</v>
+        <v>-0.207601091444087</v>
       </c>
     </row>
     <row r="1043">
@@ -12474,7 +12471,7 @@
         <v>16</v>
       </c>
       <c r="C1043" t="n">
-        <v>-0.762456718992115</v>
+        <v>-1.10610458269399</v>
       </c>
     </row>
     <row r="1044">
@@ -12485,7 +12482,7 @@
         <v>16</v>
       </c>
       <c r="C1044" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.78447080913344</v>
       </c>
     </row>
     <row r="1045">
@@ -12496,7 +12493,7 @@
         <v>16</v>
       </c>
       <c r="C1045" t="n">
-        <v>-0.195760728730222</v>
+        <v>-0.7415575894533</v>
       </c>
     </row>
     <row r="1046">
@@ -12518,7 +12515,7 @@
         <v>16</v>
       </c>
       <c r="C1047" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.536861100193687</v>
       </c>
     </row>
     <row r="1048">
@@ -12540,7 +12537,7 @@
         <v>16</v>
       </c>
       <c r="C1049" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.17931278109225</v>
       </c>
     </row>
     <row r="1050">
@@ -12551,7 +12548,7 @@
         <v>16</v>
       </c>
       <c r="C1050" t="n">
-        <v>-0.203019976076636</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1051">
@@ -12562,7 +12559,7 @@
         <v>16</v>
       </c>
       <c r="C1051" t="n">
-        <v>-0.159763313609467</v>
+        <v>-2.08776603136821</v>
       </c>
     </row>
     <row r="1052">
@@ -12584,7 +12581,7 @@
         <v>16</v>
       </c>
       <c r="C1053" t="n">
-        <v>0.0285930676076687</v>
+        <v>-0.142226362431775</v>
       </c>
     </row>
     <row r="1054">
@@ -12595,7 +12592,7 @@
         <v>16</v>
       </c>
       <c r="C1054" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.150213328113066</v>
       </c>
     </row>
     <row r="1055">
@@ -12606,7 +12603,7 @@
         <v>16</v>
       </c>
       <c r="C1055" t="n">
-        <v>-1.95388414707518</v>
+        <v>-6.55835838844432</v>
       </c>
     </row>
     <row r="1056">
@@ -12628,7 +12625,7 @@
         <v>16</v>
       </c>
       <c r="C1057" t="n">
-        <v>-0.159763313609467</v>
+        <v>-37.4483403139395</v>
       </c>
     </row>
     <row r="1058">
@@ -12639,7 +12636,7 @@
         <v>16</v>
       </c>
       <c r="C1058" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.512095367442723</v>
       </c>
     </row>
     <row r="1059">
@@ -12650,7 +12647,7 @@
         <v>16</v>
       </c>
       <c r="C1059" t="n">
-        <v>0.0144628667323404</v>
+        <v>0.126370690039957</v>
       </c>
     </row>
     <row r="1060">
@@ -12683,7 +12680,7 @@
         <v>16</v>
       </c>
       <c r="C1062" t="n">
-        <v>-0.364325467370715</v>
+        <v>-0.22688110194973</v>
       </c>
     </row>
     <row r="1063">
@@ -12694,7 +12691,7 @@
         <v>16</v>
       </c>
       <c r="C1063" t="n">
-        <v>0.142445410243316</v>
+        <v>-0.376402621039694</v>
       </c>
     </row>
     <row r="1064">
@@ -12716,7 +12713,7 @@
         <v>16</v>
       </c>
       <c r="C1065" t="n">
-        <v>-0.159763313609468</v>
+        <v>-1.32881378242697</v>
       </c>
     </row>
     <row r="1066">
@@ -12727,7 +12724,7 @@
         <v>16</v>
       </c>
       <c r="C1066" t="n">
-        <v>-0.412484554414156</v>
+        <v>-0.308014331871481</v>
       </c>
     </row>
     <row r="1067">
@@ -12738,7 +12735,7 @@
         <v>16</v>
       </c>
       <c r="C1067" t="n">
-        <v>-1.66564962903106</v>
+        <v>-2.03754650857264</v>
       </c>
     </row>
     <row r="1068">
@@ -12749,7 +12746,7 @@
         <v>16</v>
       </c>
       <c r="C1068" t="n">
-        <v>-0.280331934876731</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1069">
@@ -12760,7 +12757,7 @@
         <v>16</v>
       </c>
       <c r="C1069" t="n">
-        <v>-0.318478405345315</v>
+        <v>-5.499576334777</v>
       </c>
     </row>
     <row r="1070">
@@ -12771,7 +12768,7 @@
         <v>16</v>
       </c>
       <c r="C1070" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.2357661479177</v>
       </c>
     </row>
     <row r="1071">
@@ -12782,7 +12779,7 @@
         <v>16</v>
       </c>
       <c r="C1071" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.234695653971908</v>
       </c>
     </row>
     <row r="1072">
@@ -12793,7 +12790,7 @@
         <v>16</v>
       </c>
       <c r="C1072" t="n">
-        <v>-0.716929003227059</v>
+        <v>-0.257402642979133</v>
       </c>
     </row>
     <row r="1073">
@@ -12804,7 +12801,7 @@
         <v>16</v>
       </c>
       <c r="C1073" t="n">
-        <v>-0.181183829624939</v>
+        <v>-0.348828490299506</v>
       </c>
     </row>
     <row r="1074">
@@ -12815,7 +12812,7 @@
         <v>16</v>
       </c>
       <c r="C1074" t="n">
-        <v>-0.325824960815077</v>
+        <v>-0.227156398987956</v>
       </c>
     </row>
     <row r="1075">
@@ -12826,7 +12823,7 @@
         <v>16</v>
       </c>
       <c r="C1075" t="n">
-        <v>-0.816373834081315</v>
+        <v>-0.229688804181836</v>
       </c>
     </row>
     <row r="1076">
@@ -12837,7 +12834,7 @@
         <v>16</v>
       </c>
       <c r="C1076" t="n">
-        <v>0.103032031204652</v>
+        <v>-0.0903144361348396</v>
       </c>
     </row>
     <row r="1077">
@@ -12848,7 +12845,7 @@
         <v>16</v>
       </c>
       <c r="C1077" t="n">
-        <v>-0.159763313609468</v>
+        <v>-1.87651674735508</v>
       </c>
     </row>
     <row r="1078">
@@ -12859,7 +12856,7 @@
         <v>16</v>
       </c>
       <c r="C1078" t="n">
-        <v>-0.0467992186659052</v>
+        <v>-4.30829320820977</v>
       </c>
     </row>
     <row r="1079">
@@ -12892,7 +12889,7 @@
         <v>16</v>
       </c>
       <c r="C1081" t="n">
-        <v>-0.159763313609468</v>
+        <v>-6.78208306972284</v>
       </c>
     </row>
     <row r="1082">
@@ -12903,7 +12900,7 @@
         <v>16</v>
       </c>
       <c r="C1082" t="n">
-        <v>-0.26469383710354</v>
+        <v>-2.39678152378149</v>
       </c>
     </row>
     <row r="1083">
@@ -12914,7 +12911,7 @@
         <v>16</v>
       </c>
       <c r="C1083" t="n">
-        <v>-1.02522413473813</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1084">
@@ -12925,7 +12922,7 @@
         <v>16</v>
       </c>
       <c r="C1084" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.311957194042777</v>
       </c>
     </row>
     <row r="1085">
@@ -12947,7 +12944,7 @@
         <v>16</v>
       </c>
       <c r="C1086" t="n">
-        <v>-0.00382005796715013</v>
+        <v>-2.0125979903067</v>
       </c>
     </row>
     <row r="1087">
@@ -12958,7 +12955,7 @@
         <v>16</v>
       </c>
       <c r="C1087" t="n">
-        <v>-0.409680867988852</v>
+        <v>-0.204983235665471</v>
       </c>
     </row>
     <row r="1088">
@@ -12969,7 +12966,7 @@
         <v>16</v>
       </c>
       <c r="C1088" t="n">
-        <v>-0.238640346132291</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1089">
@@ -12980,7 +12977,7 @@
         <v>16</v>
       </c>
       <c r="C1089" t="n">
-        <v>0.116062121976354</v>
+        <v>-0.541117176988586</v>
       </c>
     </row>
     <row r="1090">
@@ -12991,7 +12988,7 @@
         <v>16</v>
       </c>
       <c r="C1090" t="n">
-        <v>-0.234807813325919</v>
+        <v>-0.501019118588358</v>
       </c>
     </row>
     <row r="1091">
@@ -13002,7 +12999,7 @@
         <v>16</v>
       </c>
       <c r="C1091" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.951925402972399</v>
       </c>
     </row>
     <row r="1092">
@@ -13013,7 +13010,7 @@
         <v>16</v>
       </c>
       <c r="C1092" t="n">
-        <v>-2.49342423581051</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1093">
@@ -13035,7 +13032,7 @@
         <v>16</v>
       </c>
       <c r="C1094" t="n">
-        <v>-0.163808666818934</v>
+        <v>-0.464096125616567</v>
       </c>
     </row>
     <row r="1095">
@@ -13046,7 +13043,7 @@
         <v>16</v>
       </c>
       <c r="C1095" t="n">
-        <v>-0.309414143033988</v>
+        <v>-0.649914823102844</v>
       </c>
     </row>
     <row r="1096">
@@ -13068,7 +13065,7 @@
         <v>16</v>
       </c>
       <c r="C1097" t="n">
-        <v>-0.159763313609468</v>
+        <v>-1.4583577821959</v>
       </c>
     </row>
     <row r="1098">
@@ -13079,7 +13076,7 @@
         <v>16</v>
       </c>
       <c r="C1098" t="n">
-        <v>-0.489412282636897</v>
+        <v>-0.653691547642902</v>
       </c>
     </row>
     <row r="1099">
@@ -13090,7 +13087,7 @@
         <v>16</v>
       </c>
       <c r="C1099" t="n">
-        <v>-0.196170158638092</v>
+        <v>-0.55092751641509</v>
       </c>
     </row>
     <row r="1100">
@@ -13112,7 +13109,7 @@
         <v>16</v>
       </c>
       <c r="C1101" t="n">
-        <v>-0.315098225488135</v>
+        <v>-0.745656351494754</v>
       </c>
     </row>
     <row r="1102">
@@ -13123,7 +13120,7 @@
         <v>16</v>
       </c>
       <c r="C1102" t="n">
-        <v>-0.159763313609468</v>
+        <v>-33.8215658910839</v>
       </c>
     </row>
     <row r="1103">
@@ -13134,7 +13131,7 @@
         <v>16</v>
       </c>
       <c r="C1103" t="n">
-        <v>0.166825012347801</v>
+        <v>0.120140640051422</v>
       </c>
     </row>
     <row r="1104">
@@ -13156,7 +13153,7 @@
         <v>16</v>
       </c>
       <c r="C1105" t="n">
-        <v>0.457675479602829</v>
+        <v>0.187275257749295</v>
       </c>
     </row>
     <row r="1106">
@@ -13178,7 +13175,7 @@
         <v>16</v>
       </c>
       <c r="C1107" t="n">
-        <v>-0.241526288075134</v>
+        <v>-1.07735469280592</v>
       </c>
     </row>
     <row r="1108">
@@ -13189,7 +13186,7 @@
         <v>16</v>
       </c>
       <c r="C1108" t="n">
-        <v>-0.330331493305554</v>
+        <v>-9.8939644227996</v>
       </c>
     </row>
     <row r="1109">
@@ -13200,7 +13197,7 @@
         <v>16</v>
       </c>
       <c r="C1109" t="n">
-        <v>-1.66646146239286</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1110">
@@ -13222,7 +13219,7 @@
         <v>16</v>
       </c>
       <c r="C1111" t="n">
-        <v>-0.178614169921388</v>
+        <v>-0.183318863796845</v>
       </c>
     </row>
     <row r="1112">
@@ -13233,7 +13230,7 @@
         <v>16</v>
       </c>
       <c r="C1112" t="n">
-        <v>-0.159763313609468</v>
+        <v>-1.63410742377966</v>
       </c>
     </row>
     <row r="1113">
@@ -13244,7 +13241,7 @@
         <v>16</v>
       </c>
       <c r="C1113" t="n">
-        <v>-0.261700648454371</v>
+        <v>-0.33178437394937</v>
       </c>
     </row>
     <row r="1114">
@@ -13266,7 +13263,7 @@
         <v>16</v>
       </c>
       <c r="C1115" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.175309449278549</v>
       </c>
     </row>
     <row r="1116">
@@ -13288,7 +13285,7 @@
         <v>16</v>
       </c>
       <c r="C1117" t="n">
-        <v>-2.86467923112747</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1118">
@@ -13321,7 +13318,7 @@
         <v>16</v>
       </c>
       <c r="C1120" t="n">
-        <v>-2.33663913747248</v>
+        <v>-3.00621107053604</v>
       </c>
     </row>
     <row r="1121">
@@ -13332,7 +13329,7 @@
         <v>16</v>
       </c>
       <c r="C1121" t="n">
-        <v>-0.638430766237367</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1122">
@@ -13343,7 +13340,7 @@
         <v>16</v>
       </c>
       <c r="C1122" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.36490470485432</v>
       </c>
     </row>
     <row r="1123">
@@ -13354,7 +13351,7 @@
         <v>16</v>
       </c>
       <c r="C1123" t="n">
-        <v>-0.191592056047568</v>
+        <v>-0.56218711910741</v>
       </c>
     </row>
     <row r="1124">
@@ -13365,7 +13362,7 @@
         <v>16</v>
       </c>
       <c r="C1124" t="n">
-        <v>-0.159763313609468</v>
+        <v>-1.03303307364303</v>
       </c>
     </row>
     <row r="1125">
@@ -13387,7 +13384,7 @@
         <v>16</v>
       </c>
       <c r="C1126" t="n">
-        <v>-0.37603776229606</v>
+        <v>-1.06638922613144</v>
       </c>
     </row>
     <row r="1127">
@@ -13398,7 +13395,7 @@
         <v>16</v>
       </c>
       <c r="C1127" t="n">
-        <v>-0.615860732814211</v>
+        <v>0.607643310499422</v>
       </c>
     </row>
     <row r="1128">
@@ -13409,7 +13406,7 @@
         <v>16</v>
       </c>
       <c r="C1128" t="n">
-        <v>-0.159763313609468</v>
+        <v>0.432639946428427</v>
       </c>
     </row>
     <row r="1129">
@@ -13420,7 +13417,7 @@
         <v>16</v>
       </c>
       <c r="C1129" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.164438254518839</v>
       </c>
     </row>
     <row r="1130">
@@ -13431,7 +13428,7 @@
         <v>16</v>
       </c>
       <c r="C1130" t="n">
-        <v>-0.201549016874217</v>
+        <v>-0.167190888493574</v>
       </c>
     </row>
     <row r="1131">
@@ -13442,7 +13439,7 @@
         <v>16</v>
       </c>
       <c r="C1131" t="n">
-        <v>-0.249553372428942</v>
+        <v>-0.266377862282448</v>
       </c>
     </row>
     <row r="1132">
@@ -13453,7 +13450,7 @@
         <v>16</v>
       </c>
       <c r="C1132" t="n">
-        <v>-0.238330501394741</v>
+        <v>-0.213131098962334</v>
       </c>
     </row>
     <row r="1133">
@@ -13464,7 +13461,7 @@
         <v>16</v>
       </c>
       <c r="C1133" t="n">
-        <v>0.732455198450162</v>
+        <v>0.38149053705997</v>
       </c>
     </row>
     <row r="1134">
@@ -13475,7 +13472,7 @@
         <v>16</v>
       </c>
       <c r="C1134" t="n">
-        <v>-0.209052607137943</v>
+        <v>-0.405601488351505</v>
       </c>
     </row>
     <row r="1135">
@@ -13486,7 +13483,7 @@
         <v>16</v>
       </c>
       <c r="C1135" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.282176244802005</v>
       </c>
     </row>
     <row r="1136">
@@ -13508,7 +13505,7 @@
         <v>16</v>
       </c>
       <c r="C1137" t="n">
-        <v>-0.0323394725976527</v>
+        <v>0.257213675085767</v>
       </c>
     </row>
     <row r="1138">
@@ -13530,7 +13527,7 @@
         <v>16</v>
       </c>
       <c r="C1139" t="n">
-        <v>-11.4809886898214</v>
+        <v>-0.935195098405697</v>
       </c>
     </row>
     <row r="1140">
@@ -13541,7 +13538,7 @@
         <v>16</v>
       </c>
       <c r="C1140" t="n">
-        <v>-0.530470682470117</v>
+        <v>-0.223409984887944</v>
       </c>
     </row>
     <row r="1141">
@@ -13552,7 +13549,7 @@
         <v>16</v>
       </c>
       <c r="C1141" t="n">
-        <v>-0.191008212234846</v>
+        <v>-0.158158920760018</v>
       </c>
     </row>
     <row r="1142">
@@ -13563,7 +13560,7 @@
         <v>16</v>
       </c>
       <c r="C1142" t="n">
-        <v>-0.251233685086518</v>
+        <v>-0.130275232576174</v>
       </c>
     </row>
     <row r="1143">
@@ -13585,7 +13582,7 @@
         <v>16</v>
       </c>
       <c r="C1144" t="n">
-        <v>-0.134838212926105</v>
+        <v>-0.278198775970039</v>
       </c>
     </row>
     <row r="1145">
@@ -13596,7 +13593,7 @@
         <v>16</v>
       </c>
       <c r="C1145" t="n">
-        <v>0.230575117011175</v>
+        <v>0.309829418674951</v>
       </c>
     </row>
     <row r="1146">
@@ -13618,7 +13615,7 @@
         <v>16</v>
       </c>
       <c r="C1147" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.19727855250751</v>
       </c>
     </row>
     <row r="1148">
@@ -13629,7 +13626,7 @@
         <v>16</v>
       </c>
       <c r="C1148" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.263557261286244</v>
       </c>
     </row>
     <row r="1149">
@@ -13640,7 +13637,7 @@
         <v>16</v>
       </c>
       <c r="C1149" t="n">
-        <v>-0.332063972449788</v>
+        <v>-0.281884017987395</v>
       </c>
     </row>
     <row r="1150">
@@ -13651,7 +13648,7 @@
         <v>16</v>
       </c>
       <c r="C1150" t="n">
-        <v>-0.615144016111086</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1151">
@@ -13662,7 +13659,7 @@
         <v>16</v>
       </c>
       <c r="C1151" t="n">
-        <v>-0.212831885876419</v>
+        <v>-0.276269731869803</v>
       </c>
     </row>
     <row r="1152">
@@ -13673,7 +13670,7 @@
         <v>16</v>
       </c>
       <c r="C1152" t="n">
-        <v>-0.00406005160288414</v>
+        <v>0.033589904351251</v>
       </c>
     </row>
     <row r="1153">
@@ -13684,7 +13681,7 @@
         <v>16</v>
       </c>
       <c r="C1153" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.209687100860678</v>
       </c>
     </row>
     <row r="1154">
@@ -13706,7 +13703,7 @@
         <v>16</v>
       </c>
       <c r="C1155" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.291926732827188</v>
       </c>
     </row>
     <row r="1156">
@@ -13717,7 +13714,7 @@
         <v>16</v>
       </c>
       <c r="C1156" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.856183989411089</v>
       </c>
     </row>
     <row r="1157">
@@ -13728,7 +13725,7 @@
         <v>16</v>
       </c>
       <c r="C1157" t="n">
-        <v>-0.166897584218277</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1158">
@@ -13739,7 +13736,7 @@
         <v>16</v>
       </c>
       <c r="C1158" t="n">
-        <v>-1.26937339161238</v>
+        <v>0.406094919565925</v>
       </c>
     </row>
     <row r="1159">
@@ -13750,7 +13747,7 @@
         <v>16</v>
       </c>
       <c r="C1159" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.644073739809779</v>
       </c>
     </row>
     <row r="1160">
@@ -13761,7 +13758,7 @@
         <v>16</v>
       </c>
       <c r="C1160" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.306506974366174</v>
       </c>
     </row>
     <row r="1161">
@@ -13772,7 +13769,7 @@
         <v>16</v>
       </c>
       <c r="C1161" t="n">
-        <v>0.383853958550861</v>
+        <v>-1.93698338820914</v>
       </c>
     </row>
     <row r="1162">
@@ -13783,7 +13780,7 @@
         <v>16</v>
       </c>
       <c r="C1162" t="n">
-        <v>-0.20946008907986</v>
+        <v>-0.319910008546274</v>
       </c>
     </row>
     <row r="1163">
@@ -13794,7 +13791,7 @@
         <v>16</v>
       </c>
       <c r="C1163" t="n">
-        <v>-0.218144058998162</v>
+        <v>-3.1397042011735</v>
       </c>
     </row>
     <row r="1164">
@@ -13816,7 +13813,7 @@
         <v>16</v>
       </c>
       <c r="C1165" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.18062966821579</v>
       </c>
     </row>
     <row r="1166">
@@ -13827,7 +13824,7 @@
         <v>16</v>
       </c>
       <c r="C1166" t="n">
-        <v>-0.374604208017981</v>
+        <v>-0.982574181768432</v>
       </c>
     </row>
     <row r="1167">
@@ -13838,7 +13835,7 @@
         <v>16</v>
       </c>
       <c r="C1167" t="n">
-        <v>-0.24782832445343</v>
+        <v>-0.408067119710073</v>
       </c>
     </row>
     <row r="1168">
@@ -13860,7 +13857,7 @@
         <v>16</v>
       </c>
       <c r="C1169" t="n">
-        <v>-0.21974290014657</v>
+        <v>-0.201577974686878</v>
       </c>
     </row>
     <row r="1170">
@@ -13871,7 +13868,7 @@
         <v>16</v>
       </c>
       <c r="C1170" t="n">
-        <v>-0.350353889053615</v>
+        <v>-1.02214345705947</v>
       </c>
     </row>
     <row r="1171">
@@ -13882,7 +13879,7 @@
         <v>16</v>
       </c>
       <c r="C1171" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.266176480308428</v>
       </c>
     </row>
     <row r="1172">
@@ -13893,7 +13890,7 @@
         <v>16</v>
       </c>
       <c r="C1172" t="n">
-        <v>-0.159763313609467</v>
+        <v>-3.44770562634631</v>
       </c>
     </row>
     <row r="1173">
@@ -13904,7 +13901,7 @@
         <v>16</v>
       </c>
       <c r="C1173" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.807885615099611</v>
       </c>
     </row>
     <row r="1174">
@@ -13937,7 +13934,7 @@
         <v>16</v>
       </c>
       <c r="C1176" t="n">
-        <v>-0.159763313609468</v>
+        <v>-7.00948150183746</v>
       </c>
     </row>
     <row r="1177">
@@ -13948,7 +13945,7 @@
         <v>16</v>
       </c>
       <c r="C1177" t="n">
-        <v>-0.180224391894064</v>
+        <v>-0.162980334185041</v>
       </c>
     </row>
     <row r="1178">
@@ -13959,7 +13956,7 @@
         <v>16</v>
       </c>
       <c r="C1178" t="n">
-        <v>0.0157058186155945</v>
+        <v>0.0246391178640876</v>
       </c>
     </row>
     <row r="1179">
@@ -13970,7 +13967,7 @@
         <v>16</v>
       </c>
       <c r="C1179" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.82027952584452</v>
       </c>
     </row>
     <row r="1180">
@@ -13981,7 +13978,7 @@
         <v>16</v>
       </c>
       <c r="C1180" t="n">
-        <v>-0.499262676825729</v>
+        <v>-0.437804355106051</v>
       </c>
     </row>
     <row r="1181">
@@ -13992,7 +13989,7 @@
         <v>16</v>
       </c>
       <c r="C1181" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.207800696043301</v>
       </c>
     </row>
     <row r="1182">
@@ -14003,7 +14000,7 @@
         <v>16</v>
       </c>
       <c r="C1182" t="n">
-        <v>-0.377682300523388</v>
+        <v>-0.799934987915898</v>
       </c>
     </row>
     <row r="1183">
@@ -14014,7 +14011,7 @@
         <v>16</v>
       </c>
       <c r="C1183" t="n">
-        <v>-0.615206075959521</v>
+        <v>-1.50839050590454</v>
       </c>
     </row>
     <row r="1184">
@@ -14025,7 +14022,7 @@
         <v>16</v>
       </c>
       <c r="C1184" t="n">
-        <v>-0.0332113337839299</v>
+        <v>-0.163543577892767</v>
       </c>
     </row>
     <row r="1185">
@@ -14036,7 +14033,7 @@
         <v>16</v>
       </c>
       <c r="C1185" t="n">
-        <v>-0.203693526565432</v>
+        <v>-0.210741855822859</v>
       </c>
     </row>
     <row r="1186">
@@ -14047,7 +14044,7 @@
         <v>16</v>
       </c>
       <c r="C1186" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.164881919359901</v>
       </c>
     </row>
     <row r="1187">
@@ -14058,7 +14055,7 @@
         <v>16</v>
       </c>
       <c r="C1187" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.86184858063944</v>
       </c>
     </row>
     <row r="1188">
@@ -14069,7 +14066,7 @@
         <v>16</v>
       </c>
       <c r="C1188" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.05061966812227</v>
       </c>
     </row>
     <row r="1189">
@@ -14091,7 +14088,7 @@
         <v>16</v>
       </c>
       <c r="C1190" t="n">
-        <v>-0.51751690004316</v>
+        <v>-0.582067328152619</v>
       </c>
     </row>
     <row r="1191">
@@ -14102,7 +14099,7 @@
         <v>16</v>
       </c>
       <c r="C1191" t="n">
-        <v>-0.224544926210222</v>
+        <v>-0.242317605528652</v>
       </c>
     </row>
     <row r="1192">
@@ -14113,7 +14110,7 @@
         <v>16</v>
       </c>
       <c r="C1192" t="n">
-        <v>-0.797828143156154</v>
+        <v>-1.54330410228674</v>
       </c>
     </row>
     <row r="1193">
@@ -14124,7 +14121,7 @@
         <v>16</v>
       </c>
       <c r="C1193" t="n">
-        <v>-0.183112238994813</v>
+        <v>-0.50121679953615</v>
       </c>
     </row>
     <row r="1194">
@@ -14135,7 +14132,7 @@
         <v>16</v>
       </c>
       <c r="C1194" t="n">
-        <v>-0.139313778737219</v>
+        <v>-0.430351557584943</v>
       </c>
     </row>
     <row r="1195">
@@ -14146,7 +14143,7 @@
         <v>16</v>
       </c>
       <c r="C1195" t="n">
-        <v>0.387365838803132</v>
+        <v>-0.457890873995586</v>
       </c>
     </row>
     <row r="1196">
@@ -14157,7 +14154,7 @@
         <v>16</v>
       </c>
       <c r="C1196" t="n">
-        <v>-0.377288625249298</v>
+        <v>-0.0715623050249414</v>
       </c>
     </row>
     <row r="1197">
@@ -14168,7 +14165,7 @@
         <v>16</v>
       </c>
       <c r="C1197" t="n">
-        <v>-0.247105709015522</v>
+        <v>-0.785946374475543</v>
       </c>
     </row>
     <row r="1198">
@@ -14179,7 +14176,7 @@
         <v>16</v>
       </c>
       <c r="C1198" t="n">
-        <v>-2.0257580835637</v>
+        <v>0.0208926799626857</v>
       </c>
     </row>
     <row r="1199">
@@ -14190,7 +14187,7 @@
         <v>16</v>
       </c>
       <c r="C1199" t="n">
-        <v>-0.614903741481576</v>
+        <v>-0.686337893883032</v>
       </c>
     </row>
     <row r="1200">
@@ -14201,7 +14198,7 @@
         <v>16</v>
       </c>
       <c r="C1200" t="n">
-        <v>-0.636049387372341</v>
+        <v>-1.12973720198687</v>
       </c>
     </row>
     <row r="1201">
@@ -14212,7 +14209,7 @@
         <v>16</v>
       </c>
       <c r="C1201" t="n">
-        <v>-0.336654293844148</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
   </sheetData>
@@ -14529,7 +14526,7 @@
         <v>1757.71</v>
       </c>
       <c r="E18" t="n">
-        <v>-3189.41651169198</v>
+        <v>-336.555</v>
       </c>
     </row>
     <row r="19">
@@ -14784,7 +14781,7 @@
         <v>1517.85</v>
       </c>
       <c r="E33" t="n">
-        <v>-2892.78680389659</v>
+        <v>-73.0342857142858</v>
       </c>
     </row>
     <row r="34">
@@ -14954,7 +14951,7 @@
         <v>-2305.05</v>
       </c>
       <c r="E43" t="n">
-        <v>200.03</v>
+        <v>7389.26603878363</v>
       </c>
     </row>
     <row r="44">
@@ -15022,7 +15019,7 @@
         <v>1.706</v>
       </c>
       <c r="E47" t="n">
-        <v>1.84164235896787</v>
+        <v>1.92462999391179</v>
       </c>
     </row>
     <row r="48">
@@ -15039,7 +15036,7 @@
         <v>4.218</v>
       </c>
       <c r="E48" t="n">
-        <v>1.67157060015487</v>
+        <v>1.43522372086928</v>
       </c>
     </row>
     <row r="49">
@@ -15056,7 +15053,7 @@
         <v>1.578</v>
       </c>
       <c r="E49" t="n">
-        <v>1.77066926671606</v>
+        <v>1.90251500219733</v>
       </c>
     </row>
     <row r="50">
@@ -15073,7 +15070,7 @@
         <v>3.683</v>
       </c>
       <c r="E50" t="n">
-        <v>2.13137019975736</v>
+        <v>2.11421620956591</v>
       </c>
     </row>
     <row r="51">
@@ -15090,7 +15087,7 @@
         <v>2.983</v>
       </c>
       <c r="E51" t="n">
-        <v>1.72620785921745</v>
+        <v>1.54470210130364</v>
       </c>
     </row>
     <row r="52">
@@ -15107,7 +15104,7 @@
         <v>2.44</v>
       </c>
       <c r="E52" t="n">
-        <v>2.37372933383791</v>
+        <v>2.47941494153373</v>
       </c>
     </row>
     <row r="53">
@@ -15124,7 +15121,7 @@
         <v>3.879</v>
       </c>
       <c r="E53" t="n">
-        <v>2.26856290294905</v>
+        <v>2.28957268209927</v>
       </c>
     </row>
     <row r="54">
@@ -15141,7 +15138,7 @@
         <v>0.579999999999998</v>
       </c>
       <c r="E54" t="n">
-        <v>1.76126507724521</v>
+        <v>1.73241661914691</v>
       </c>
     </row>
     <row r="55">
@@ -15158,7 +15155,7 @@
         <v>-1.918</v>
       </c>
       <c r="E55" t="n">
-        <v>1.54766151371209</v>
+        <v>1.56646332062041</v>
       </c>
     </row>
     <row r="56">
@@ -15175,7 +15172,7 @@
         <v>0.672000000000001</v>
       </c>
       <c r="E56" t="n">
-        <v>2.06051524335914</v>
+        <v>1.81403553422247</v>
       </c>
     </row>
     <row r="57">
@@ -15192,7 +15189,7 @@
         <v>0.352999999999998</v>
       </c>
       <c r="E57" t="n">
-        <v>1.52410309613687</v>
+        <v>1.59956923032418</v>
       </c>
     </row>
     <row r="58">
@@ -15209,7 +15206,7 @@
         <v>5.08900000000001</v>
       </c>
       <c r="E58" t="n">
-        <v>5.51590684649431</v>
+        <v>3.91468011782095</v>
       </c>
     </row>
     <row r="59">
@@ -15226,7 +15223,7 @@
         <v>0.181000000000001</v>
       </c>
       <c r="E59" t="n">
-        <v>1.4534733589172</v>
+        <v>2.10257142857143</v>
       </c>
     </row>
     <row r="60">
@@ -15243,7 +15240,7 @@
         <v>1.311</v>
       </c>
       <c r="E60" t="n">
-        <v>2.07893922245428</v>
+        <v>2.15115542976972</v>
       </c>
     </row>
     <row r="61">
@@ -15260,7 +15257,7 @@
         <v>2.862</v>
       </c>
       <c r="E61" t="n">
-        <v>1.85290846326792</v>
+        <v>1.83859160812827</v>
       </c>
     </row>
     <row r="62">
@@ -15379,7 +15376,7 @@
         <v>25</v>
       </c>
       <c r="E68" t="n">
-        <v>42.5</v>
+        <v>44.0663484873993</v>
       </c>
     </row>
     <row r="69">
@@ -15498,7 +15495,7 @@
         <v>5</v>
       </c>
       <c r="E75" t="n">
-        <v>46.0266759884041</v>
+        <v>46.305750417851</v>
       </c>
     </row>
     <row r="76">
@@ -15515,7 +15512,7 @@
         <v>89</v>
       </c>
       <c r="E76" t="n">
-        <v>37.9285714285714</v>
+        <v>36.4042643058242</v>
       </c>
     </row>
     <row r="77">
@@ -15617,7 +15614,7 @@
         <v>23</v>
       </c>
       <c r="E82" t="n">
-        <v>8.92307692307692</v>
+        <v>6.67339917498317</v>
       </c>
     </row>
     <row r="83">
@@ -15798,7 +15795,7 @@
         <v>0.0666666666666667</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -15815,7 +15812,7 @@
         <v>0.0666666666666667</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
@@ -15832,7 +15829,7 @@
         <v>0.0666666666666667</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
@@ -15849,7 +15846,7 @@
         <v>0.0666666666666667</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
@@ -15866,7 +15863,7 @@
         <v>0.0666666666666667</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
@@ -15883,7 +15880,7 @@
         <v>0.0666666666666667</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -15900,7 +15897,7 @@
         <v>0.0666666666666667</v>
       </c>
       <c r="E8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
@@ -15917,7 +15914,7 @@
         <v>0.0666666666666667</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
@@ -15934,7 +15931,7 @@
         <v>0.0666666666666667</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
@@ -15942,7 +15939,7 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C11" t="n">
         <v>1</v>
@@ -15959,7 +15956,7 @@
         <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="C12" t="n">
         <v>1</v>
@@ -15976,16 +15973,16 @@
         <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.933333333333333</v>
       </c>
       <c r="E13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
@@ -15993,16 +15990,16 @@
         <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
       <c r="E14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
@@ -16010,7 +16007,7 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C15" t="n">
         <v>1</v>
@@ -16019,7 +16016,7 @@
         <v>0.0666666666666667</v>
       </c>
       <c r="E15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -16027,7 +16024,7 @@
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
@@ -16036,7 +16033,7 @@
         <v>0.0666666666666667</v>
       </c>
       <c r="E16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -16044,16 +16041,16 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.2</v>
       </c>
       <c r="E17" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
@@ -16061,7 +16058,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
@@ -16070,7 +16067,7 @@
         <v>0.0666666666666667</v>
       </c>
       <c r="E18" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
@@ -16078,7 +16075,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C19" t="n">
         <v>1</v>
@@ -16087,7 +16084,7 @@
         <v>0.0666666666666667</v>
       </c>
       <c r="E19" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
@@ -16095,16 +16092,16 @@
         <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="E20" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -16112,16 +16109,16 @@
         <v>16</v>
       </c>
       <c r="B21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="E21" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22">
@@ -16129,16 +16126,16 @@
         <v>16</v>
       </c>
       <c r="B22" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.133333333333333</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="E22" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23">
@@ -16146,16 +16143,16 @@
         <v>16</v>
       </c>
       <c r="B23" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="E23" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24">
@@ -16163,16 +16160,16 @@
         <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="E24" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25">
@@ -16180,16 +16177,16 @@
         <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="E25" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26">
@@ -16197,16 +16194,16 @@
         <v>16</v>
       </c>
       <c r="B26" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="E26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27">
@@ -16214,16 +16211,16 @@
         <v>16</v>
       </c>
       <c r="B27" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="E27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28">
@@ -16231,16 +16228,16 @@
         <v>16</v>
       </c>
       <c r="B28" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="E28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29">
@@ -16248,16 +16245,33 @@
         <v>16</v>
       </c>
       <c r="B29" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="E29" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>16</v>
+      </c>
+      <c r="B30" t="s">
+        <v>53</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+      <c r="E30" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
